--- a/data/umr/Resumen UMR Mayo 2026.xlsx
+++ b/data/umr/Resumen UMR Mayo 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1149CA91-680E-41DF-83AF-5695EBF197A7}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA9E0C3-5DE0-41CA-946C-AF271AD42DF0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4835,50 +4835,11 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4893,6 +4854,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4919,6 +4883,45 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4931,9 +4934,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4962,8 +4962,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -5805,37 +5805,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="348" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="348"/>
-      <c r="C1" s="348"/>
-      <c r="D1" s="348"/>
-      <c r="E1" s="348"/>
-      <c r="F1" s="348"/>
-      <c r="G1" s="348"/>
-      <c r="H1" s="348"/>
-      <c r="I1" s="348"/>
-      <c r="J1" s="348"/>
-      <c r="K1" s="348"/>
-      <c r="L1" s="348"/>
-      <c r="M1" s="348"/>
-      <c r="N1" s="348"/>
-      <c r="O1" s="348"/>
-      <c r="P1" s="348"/>
-      <c r="Q1" s="348"/>
-      <c r="R1" s="348"/>
-      <c r="S1" s="348"/>
-      <c r="T1" s="348"/>
-      <c r="U1" s="348"/>
-      <c r="V1" s="348"/>
-      <c r="W1" s="348"/>
-      <c r="X1" s="348"/>
-      <c r="Y1" s="348"/>
-      <c r="Z1" s="348"/>
-      <c r="AA1" s="348"/>
-      <c r="AB1" s="348"/>
-      <c r="AC1" s="348"/>
+      <c r="A1" s="349" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
+      <c r="H1" s="349"/>
+      <c r="I1" s="349"/>
+      <c r="J1" s="349"/>
+      <c r="K1" s="349"/>
+      <c r="L1" s="349"/>
+      <c r="M1" s="349"/>
+      <c r="N1" s="349"/>
+      <c r="O1" s="349"/>
+      <c r="P1" s="349"/>
+      <c r="Q1" s="349"/>
+      <c r="R1" s="349"/>
+      <c r="S1" s="349"/>
+      <c r="T1" s="349"/>
+      <c r="U1" s="349"/>
+      <c r="V1" s="349"/>
+      <c r="W1" s="349"/>
+      <c r="X1" s="349"/>
+      <c r="Y1" s="349"/>
+      <c r="Z1" s="349"/>
+      <c r="AA1" s="349"/>
+      <c r="AB1" s="349"/>
+      <c r="AC1" s="349"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -10113,37 +10113,37 @@
       <c r="AC46" s="212"/>
     </row>
     <row r="47" spans="1:32" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="348" t="s">
+      <c r="A47" s="349" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="348"/>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
-      <c r="G47" s="348"/>
-      <c r="H47" s="348"/>
-      <c r="I47" s="348"/>
-      <c r="J47" s="348"/>
-      <c r="K47" s="348"/>
-      <c r="L47" s="348"/>
-      <c r="M47" s="348"/>
-      <c r="N47" s="348"/>
-      <c r="O47" s="348"/>
-      <c r="P47" s="348"/>
-      <c r="Q47" s="348"/>
-      <c r="R47" s="348"/>
-      <c r="S47" s="348"/>
-      <c r="T47" s="348"/>
-      <c r="U47" s="348"/>
-      <c r="V47" s="348"/>
-      <c r="W47" s="348"/>
-      <c r="X47" s="348"/>
-      <c r="Y47" s="348"/>
-      <c r="Z47" s="348"/>
-      <c r="AA47" s="348"/>
-      <c r="AB47" s="348"/>
-      <c r="AC47" s="348"/>
+      <c r="B47" s="349"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
+      <c r="G47" s="349"/>
+      <c r="H47" s="349"/>
+      <c r="I47" s="349"/>
+      <c r="J47" s="349"/>
+      <c r="K47" s="349"/>
+      <c r="L47" s="349"/>
+      <c r="M47" s="349"/>
+      <c r="N47" s="349"/>
+      <c r="O47" s="349"/>
+      <c r="P47" s="349"/>
+      <c r="Q47" s="349"/>
+      <c r="R47" s="349"/>
+      <c r="S47" s="349"/>
+      <c r="T47" s="349"/>
+      <c r="U47" s="349"/>
+      <c r="V47" s="349"/>
+      <c r="W47" s="349"/>
+      <c r="X47" s="349"/>
+      <c r="Y47" s="349"/>
+      <c r="Z47" s="349"/>
+      <c r="AA47" s="349"/>
+      <c r="AB47" s="349"/>
+      <c r="AC47" s="349"/>
       <c r="AF47" s="124"/>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
@@ -16261,14 +16261,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="349" t="s">
+      <c r="B2" s="373" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="349"/>
-      <c r="D2" s="350" t="s">
+      <c r="C2" s="373"/>
+      <c r="D2" s="374" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="350"/>
+      <c r="E2" s="374"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -16359,59 +16359,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="349" t="s">
+      <c r="B3" s="373" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="349"/>
-      <c r="D3" s="350" t="s">
+      <c r="C3" s="373"/>
+      <c r="D3" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="350"/>
-      <c r="F3" s="356" t="s">
+      <c r="E3" s="374"/>
+      <c r="F3" s="366" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="356" t="s">
+      <c r="G3" s="366" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="356" t="s">
+      <c r="H3" s="366" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="356" t="s">
+      <c r="I3" s="366" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="356" t="s">
+      <c r="J3" s="366" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="356" t="s">
+      <c r="K3" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="356" t="s">
+      <c r="L3" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="356" t="s">
+      <c r="M3" s="366" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="360" t="s">
+      <c r="N3" s="355" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="360" t="s">
+      <c r="O3" s="355" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="367"/>
-      <c r="Q3" s="368" t="s">
+      <c r="P3" s="354"/>
+      <c r="Q3" s="356" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="369"/>
-      <c r="S3" s="370"/>
-      <c r="T3" s="371" t="s">
+      <c r="R3" s="357"/>
+      <c r="S3" s="358"/>
+      <c r="T3" s="359" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="372"/>
-      <c r="V3" s="373"/>
-      <c r="W3" s="365" t="s">
+      <c r="U3" s="360"/>
+      <c r="V3" s="361"/>
+      <c r="W3" s="352" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="365" t="s">
+      <c r="X3" s="352" t="s">
         <v>162</v>
       </c>
     </row>
@@ -16429,17 +16429,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="356"/>
-      <c r="G4" s="357"/>
-      <c r="H4" s="357"/>
-      <c r="I4" s="356"/>
-      <c r="J4" s="356"/>
-      <c r="K4" s="356"/>
-      <c r="L4" s="356"/>
-      <c r="M4" s="356"/>
-      <c r="N4" s="360"/>
-      <c r="O4" s="360"/>
-      <c r="P4" s="367"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="372"/>
+      <c r="H4" s="372"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
+      <c r="L4" s="366"/>
+      <c r="M4" s="366"/>
+      <c r="N4" s="355"/>
+      <c r="O4" s="355"/>
+      <c r="P4" s="354"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -16458,8 +16458,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="366"/>
-      <c r="X4" s="366"/>
+      <c r="W4" s="353"/>
+      <c r="X4" s="353"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -17927,7 +17927,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="359" t="s">
+      <c r="A27" s="365" t="s">
         <v>183</v>
       </c>
       <c r="B27" s="295">
@@ -17996,7 +17996,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="359"/>
+      <c r="A28" s="365"/>
       <c r="B28" s="295">
         <v>33</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="359"/>
+      <c r="A29" s="365"/>
       <c r="B29" s="295">
         <v>29</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="359"/>
+      <c r="A30" s="365"/>
       <c r="B30" s="295">
         <v>0</v>
       </c>
@@ -18192,7 +18192,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="359"/>
+      <c r="A31" s="365"/>
       <c r="B31" s="295">
         <v>4</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="358" t="s">
+      <c r="A41" s="364" t="s">
         <v>184</v>
       </c>
       <c r="B41" s="295">
@@ -18936,7 +18936,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="358"/>
+      <c r="A42" s="364"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -19010,7 +19010,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="358"/>
+      <c r="A43" s="364"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -19082,7 +19082,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="358"/>
+      <c r="A44" s="364"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -19154,7 +19154,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="358"/>
+      <c r="A45" s="364"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="AF47" s="255"/>
     </row>
     <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="359" t="s">
+      <c r="A48" s="365" t="s">
         <v>185</v>
       </c>
       <c r="B48" s="295">
@@ -19448,7 +19448,7 @@
       </c>
     </row>
     <row r="49" spans="1:65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="359"/>
+      <c r="A49" s="365"/>
       <c r="B49" s="295">
         <v>33</v>
       </c>
@@ -19513,7 +19513,7 @@
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A50" s="359"/>
+      <c r="A50" s="365"/>
       <c r="B50" s="295">
         <v>29</v>
       </c>
@@ -19576,7 +19576,7 @@
       </c>
     </row>
     <row r="51" spans="1:65" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="359"/>
+      <c r="A51" s="365"/>
       <c r="B51" s="295">
         <v>0</v>
       </c>
@@ -19640,7 +19640,7 @@
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A52" s="359"/>
+      <c r="A52" s="365"/>
       <c r="B52" s="295">
         <v>4</v>
       </c>
@@ -19712,7 +19712,7 @@
       <c r="C53" s="295">
         <v>0</v>
       </c>
-      <c r="D53" s="390">
+      <c r="D53" s="348">
         <v>1</v>
       </c>
       <c r="E53" s="125">
@@ -19766,7 +19766,7 @@
       <c r="C54" s="295">
         <v>0</v>
       </c>
-      <c r="D54" s="390">
+      <c r="D54" s="348">
         <v>1</v>
       </c>
       <c r="E54" s="125">
@@ -19832,31 +19832,31 @@
       </c>
       <c r="F55" s="119"/>
       <c r="G55" s="119">
-        <f>SUM(G47:G52)</f>
+        <f t="shared" ref="G55:M55" si="46">SUM(G47:G52)</f>
         <v>287</v>
       </c>
       <c r="H55" s="119">
-        <f>SUM(H47:H52)</f>
+        <f t="shared" si="46"/>
         <v>318</v>
       </c>
       <c r="I55" s="119">
-        <f>SUM(I47:I52)</f>
+        <f t="shared" si="46"/>
         <v>193</v>
       </c>
       <c r="J55" s="120">
-        <f>SUM(J47:J52)</f>
-        <v>11532.580000000002</v>
+        <f>SUM(J47:J54)</f>
+        <v>11548</v>
       </c>
       <c r="K55" s="119">
-        <f>SUM(K47:K52)</f>
+        <f t="shared" si="46"/>
         <v>7534.4400000000005</v>
       </c>
       <c r="L55" s="118">
-        <f>SUM(L47:L52)</f>
+        <f t="shared" si="46"/>
         <v>1199388.3200000003</v>
       </c>
       <c r="M55" s="151">
-        <f>SUM(M47:M52)</f>
+        <f t="shared" si="46"/>
         <v>20072</v>
       </c>
       <c r="N55" s="123">
@@ -19906,7 +19906,7 @@
         <v>38</v>
       </c>
       <c r="G56" s="125">
-        <f t="shared" ref="G56:G61" si="46">D56+E56*2</f>
+        <f t="shared" ref="G56:G61" si="47">D56+E56*2</f>
         <v>120</v>
       </c>
       <c r="H56" s="125">
@@ -19926,11 +19926,11 @@
         <v>3407.27</v>
       </c>
       <c r="L56" s="125">
-        <f t="shared" ref="L56:L61" si="47">J56*104</f>
+        <f t="shared" ref="L56:L61" si="48">J56*104</f>
         <v>538262.4</v>
       </c>
       <c r="M56" s="125">
-        <f t="shared" ref="M56:M61" si="48">I56*104</f>
+        <f t="shared" ref="M56:M61" si="49">I56*104</f>
         <v>8216</v>
       </c>
       <c r="N56" s="19"/>
@@ -19973,15 +19973,15 @@
         <v>52</v>
       </c>
       <c r="G57" s="125">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>120</v>
       </c>
       <c r="H57" s="125">
-        <f t="shared" ref="H57:H61" si="49">B57+C57*2</f>
+        <f t="shared" ref="H57:H61" si="50">B57+C57*2</f>
         <v>120</v>
       </c>
       <c r="I57" s="125">
-        <f t="shared" ref="I57:I61" si="50">D57+E57</f>
+        <f t="shared" ref="I57:I61" si="51">D57+E57</f>
         <v>78</v>
       </c>
       <c r="J57" s="125">
@@ -19993,11 +19993,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L57" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>538262.4</v>
       </c>
       <c r="M57" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>8112</v>
       </c>
       <c r="N57" s="19"/>
@@ -20040,15 +20040,15 @@
         <v>36</v>
       </c>
       <c r="G58" s="125">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>38</v>
       </c>
       <c r="H58" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>39</v>
       </c>
       <c r="I58" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>36</v>
       </c>
       <c r="J58" s="125">
@@ -20060,11 +20060,11 @@
         <v>1047.96</v>
       </c>
       <c r="L58" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>115042.72</v>
       </c>
       <c r="M58" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3744</v>
       </c>
       <c r="N58" s="19"/>
@@ -20107,15 +20107,15 @@
         <v>53</v>
       </c>
       <c r="G59" s="125">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>34</v>
       </c>
       <c r="H59" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>35</v>
       </c>
       <c r="I59" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>32</v>
       </c>
       <c r="J59" s="125">
@@ -20127,11 +20127,11 @@
         <v>931.52</v>
       </c>
       <c r="L59" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>102932.96</v>
       </c>
       <c r="M59" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>3328</v>
       </c>
       <c r="N59" s="19"/>
@@ -20175,15 +20175,15 @@
         <v>122</v>
       </c>
       <c r="G60" s="125">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="H60" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I60" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J60" s="125">
@@ -20195,11 +20195,11 @@
         <v>0</v>
       </c>
       <c r="L60" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="M60" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N60" s="19"/>
@@ -20240,15 +20240,15 @@
         <v>35</v>
       </c>
       <c r="G61" s="125">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>4</v>
       </c>
       <c r="H61" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>4</v>
       </c>
       <c r="I61" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4</v>
       </c>
       <c r="J61" s="125">
@@ -20260,11 +20260,11 @@
         <v>101.6</v>
       </c>
       <c r="L61" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>10566.4</v>
       </c>
       <c r="M61" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>416</v>
       </c>
       <c r="N61" s="19"/>
@@ -20305,31 +20305,31 @@
       </c>
       <c r="F62" s="119"/>
       <c r="G62" s="119">
-        <f t="shared" ref="G62:M62" si="51">SUM(G56:G61)</f>
+        <f t="shared" ref="G62:M62" si="52">SUM(G56:G61)</f>
         <v>316</v>
       </c>
       <c r="H62" s="119">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>318</v>
       </c>
       <c r="I62" s="119">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>229</v>
       </c>
       <c r="J62" s="120">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K62" s="119">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>8852.49</v>
       </c>
       <c r="L62" s="118">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M62" s="151">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>23816</v>
       </c>
       <c r="N62" s="123">
@@ -20379,7 +20379,7 @@
         <v>38</v>
       </c>
       <c r="G63" s="116">
-        <f t="shared" ref="G63:G68" si="52">D63+E63*2</f>
+        <f t="shared" ref="G63:G68" si="53">D63+E63*2</f>
         <v>75</v>
       </c>
       <c r="H63" s="116">
@@ -20387,7 +20387,7 @@
         <v>75</v>
       </c>
       <c r="I63" s="116">
-        <f t="shared" ref="I63:I68" si="53">D63+E63</f>
+        <f t="shared" ref="I63:I68" si="54">D63+E63</f>
         <v>72</v>
       </c>
       <c r="J63" s="116">
@@ -20399,11 +20399,11 @@
         <v>3105.36</v>
       </c>
       <c r="L63" s="116">
-        <f t="shared" ref="L63:L68" si="54">J63*104</f>
+        <f t="shared" ref="L63:L68" si="55">J63*104</f>
         <v>336414</v>
       </c>
       <c r="M63" s="116">
-        <f t="shared" ref="M63:M68" si="55">I63*104</f>
+        <f t="shared" ref="M63:M68" si="56">I63*104</f>
         <v>7488</v>
       </c>
       <c r="N63" s="19"/>
@@ -20444,15 +20444,15 @@
         <v>52</v>
       </c>
       <c r="G64" s="116">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>75</v>
       </c>
       <c r="H64" s="116">
-        <f t="shared" ref="H64:H68" si="56">B64+C64*2</f>
+        <f t="shared" ref="H64:H68" si="57">B64+C64*2</f>
         <v>75</v>
       </c>
       <c r="I64" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>75</v>
       </c>
       <c r="J64" s="116">
@@ -20464,11 +20464,11 @@
         <v>3234.75</v>
       </c>
       <c r="L64" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>336414</v>
       </c>
       <c r="M64" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>7800</v>
       </c>
       <c r="N64" s="19"/>
@@ -20512,15 +20512,15 @@
         <v>36</v>
       </c>
       <c r="G65" s="116">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H65" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="I65" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J65" s="116">
@@ -20532,11 +20532,11 @@
         <v>0</v>
       </c>
       <c r="L65" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="M65" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N65" s="19"/>
@@ -20578,15 +20578,15 @@
         <v>53</v>
       </c>
       <c r="G66" s="116">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H66" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="I66" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J66" s="116">
@@ -20598,11 +20598,11 @@
         <v>0</v>
       </c>
       <c r="L66" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="M66" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N66" s="165"/>
@@ -20643,15 +20643,15 @@
         <v>122</v>
       </c>
       <c r="G67" s="116">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H67" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="I67" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J67" s="116">
@@ -20663,11 +20663,11 @@
         <v>0</v>
       </c>
       <c r="L67" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="M67" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N67" s="165"/>
@@ -20708,15 +20708,15 @@
         <v>35</v>
       </c>
       <c r="G68" s="116">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H68" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="I68" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J68" s="116">
@@ -20728,11 +20728,11 @@
         <v>0</v>
       </c>
       <c r="L68" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="M68" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N68" s="19"/>
@@ -20773,31 +20773,31 @@
       </c>
       <c r="F69" s="119"/>
       <c r="G69" s="119">
-        <f t="shared" ref="G69:M69" si="57">SUM(G63:G68)</f>
+        <f t="shared" ref="G69:M69" si="58">SUM(G63:G68)</f>
         <v>150</v>
       </c>
       <c r="H69" s="119">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>150</v>
       </c>
       <c r="I69" s="119">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>147</v>
       </c>
       <c r="J69" s="119">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>6469.5</v>
       </c>
       <c r="K69" s="119">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L69" s="119">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>672828</v>
       </c>
       <c r="M69" s="119">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>15288</v>
       </c>
       <c r="N69" s="123">
@@ -20848,7 +20848,7 @@
         <v>38</v>
       </c>
       <c r="G70" s="218">
-        <f t="shared" ref="G70:G77" si="58">D70+E70*2</f>
+        <f t="shared" ref="G70:G77" si="59">D70+E70*2</f>
         <v>57</v>
       </c>
       <c r="H70" s="218">
@@ -20856,7 +20856,7 @@
         <v>57</v>
       </c>
       <c r="I70" s="218">
-        <f t="shared" ref="I70:I75" si="59">D70+E70</f>
+        <f t="shared" ref="I70:I75" si="60">D70+E70</f>
         <v>54</v>
       </c>
       <c r="J70" s="218">
@@ -20868,11 +20868,11 @@
         <v>2329.02</v>
       </c>
       <c r="L70" s="218">
-        <f t="shared" ref="L70:L75" si="60">J70*104</f>
+        <f t="shared" ref="L70:L75" si="61">J70*104</f>
         <v>255674.64000000004</v>
       </c>
       <c r="M70" s="218">
-        <f t="shared" ref="M70:M75" si="61">I70*104</f>
+        <f t="shared" ref="M70:M75" si="62">I70*104</f>
         <v>5616</v>
       </c>
       <c r="N70" s="19"/>
@@ -20913,15 +20913,15 @@
         <v>52</v>
       </c>
       <c r="G71" s="218">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>57</v>
       </c>
       <c r="H71" s="218">
-        <f t="shared" ref="H71:H75" si="62">B71+C71*2</f>
+        <f t="shared" ref="H71:H75" si="63">B71+C71*2</f>
         <v>57</v>
       </c>
       <c r="I71" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>57</v>
       </c>
       <c r="J71" s="218">
@@ -20933,11 +20933,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L71" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M71" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>5928</v>
       </c>
       <c r="N71" s="19"/>
@@ -20978,15 +20978,15 @@
         <v>36</v>
       </c>
       <c r="G72" s="218">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="H72" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I72" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="J72" s="218">
@@ -20998,11 +20998,11 @@
         <v>0</v>
       </c>
       <c r="L72" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M72" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="N72" s="19"/>
@@ -21043,15 +21043,15 @@
         <v>53</v>
       </c>
       <c r="G73" s="218">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="H73" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I73" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="J73" s="218">
@@ -21063,11 +21063,11 @@
         <v>0</v>
       </c>
       <c r="L73" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M73" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="N73" s="19"/>
@@ -21108,15 +21108,15 @@
         <v>122</v>
       </c>
       <c r="G74" s="218">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="H74" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I74" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="J74" s="218">
@@ -21128,11 +21128,11 @@
         <v>0</v>
       </c>
       <c r="L74" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M74" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="N74" s="19"/>
@@ -21173,15 +21173,15 @@
         <v>35</v>
       </c>
       <c r="G75" s="218">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="H75" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I75" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="J75" s="218">
@@ -21193,11 +21193,11 @@
         <v>0</v>
       </c>
       <c r="L75" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M75" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="N75" s="19"/>
@@ -21241,31 +21241,31 @@
       </c>
       <c r="F76" s="119"/>
       <c r="G76" s="119">
-        <f t="shared" ref="G76:M76" si="63">SUM(G70:G75)</f>
+        <f t="shared" ref="G76:M76" si="64">SUM(G70:G75)</f>
         <v>114</v>
       </c>
       <c r="H76" s="119">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>114</v>
       </c>
       <c r="I76" s="119">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>111</v>
       </c>
       <c r="J76" s="119">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>4916.8200000000006</v>
       </c>
       <c r="K76" s="119">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>4787.43</v>
       </c>
       <c r="L76" s="119">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>511349.28000000009</v>
       </c>
       <c r="M76" s="119">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>11544</v>
       </c>
       <c r="N76" s="180">
@@ -21318,7 +21318,7 @@
         <v>38</v>
       </c>
       <c r="G77" s="125">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>121</v>
       </c>
       <c r="H77" s="125">
@@ -21326,7 +21326,7 @@
         <v>120</v>
       </c>
       <c r="I77" s="125">
-        <f t="shared" ref="I77:I82" si="64">D77+E77</f>
+        <f t="shared" ref="I77:I82" si="65">D77+E77</f>
         <v>79</v>
       </c>
       <c r="J77" s="125">
@@ -21338,11 +21338,11 @@
         <v>3407.27</v>
       </c>
       <c r="L77" s="125">
-        <f t="shared" ref="L77:L82" si="65">J77*104</f>
+        <f t="shared" ref="L77:L82" si="66">J77*104</f>
         <v>542747.92000000004</v>
       </c>
       <c r="M77" s="125">
-        <f t="shared" ref="M77:M82" si="66">I77*104</f>
+        <f t="shared" ref="M77:M82" si="67">I77*104</f>
         <v>8216</v>
       </c>
       <c r="N77" s="19"/>
@@ -21388,15 +21388,15 @@
         <v>52</v>
       </c>
       <c r="G78" s="125">
-        <f t="shared" ref="G78:G82" si="67">D78+E78*2</f>
+        <f t="shared" ref="G78:G82" si="68">D78+E78*2</f>
         <v>121</v>
       </c>
       <c r="H78" s="125">
-        <f t="shared" ref="H78:H82" si="68">B78+C78*2</f>
+        <f t="shared" ref="H78:H82" si="69">B78+C78*2</f>
         <v>120</v>
       </c>
       <c r="I78" s="125">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>78</v>
       </c>
       <c r="J78" s="125">
@@ -21408,11 +21408,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L78" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M78" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>8112</v>
       </c>
       <c r="N78" s="19"/>
@@ -21458,15 +21458,15 @@
         <v>36</v>
       </c>
       <c r="G79" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>38</v>
       </c>
       <c r="H79" s="125">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>39</v>
       </c>
       <c r="I79" s="125">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>36</v>
       </c>
       <c r="J79" s="125">
@@ -21478,11 +21478,11 @@
         <v>1047.96</v>
       </c>
       <c r="L79" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>115042.72</v>
       </c>
       <c r="M79" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3744</v>
       </c>
       <c r="N79" s="19"/>
@@ -21530,15 +21530,15 @@
         <v>53</v>
       </c>
       <c r="G80" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>34</v>
       </c>
       <c r="H80" s="125">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>35</v>
       </c>
       <c r="I80" s="125">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>32</v>
       </c>
       <c r="J80" s="125">
@@ -21550,11 +21550,11 @@
         <v>931.52</v>
       </c>
       <c r="L80" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>102932.96</v>
       </c>
       <c r="M80" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>3328</v>
       </c>
       <c r="N80" s="19"/>
@@ -21600,15 +21600,15 @@
         <v>122</v>
       </c>
       <c r="G81" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="H81" s="125">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="I81" s="125">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="J81" s="125">
@@ -21620,11 +21620,11 @@
         <v>0</v>
       </c>
       <c r="L81" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="M81" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="N81" s="19"/>
@@ -21668,15 +21668,15 @@
         <v>35</v>
       </c>
       <c r="G82" s="125">
-        <f t="shared" si="67"/>
-        <v>4</v>
-      </c>
-      <c r="H82" s="125">
         <f t="shared" si="68"/>
         <v>4</v>
       </c>
+      <c r="H82" s="125">
+        <f t="shared" si="69"/>
+        <v>4</v>
+      </c>
       <c r="I82" s="125">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>4</v>
       </c>
       <c r="J82" s="125">
@@ -21688,11 +21688,11 @@
         <v>101.6</v>
       </c>
       <c r="L82" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>10566.4</v>
       </c>
       <c r="M82" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>416</v>
       </c>
       <c r="N82" s="19"/>
@@ -21736,31 +21736,31 @@
       </c>
       <c r="F83" s="119"/>
       <c r="G83" s="119">
-        <f t="shared" ref="G83:M83" si="69">SUM(G77:G82)</f>
+        <f t="shared" ref="G83:M83" si="70">SUM(G77:G82)</f>
         <v>318</v>
       </c>
       <c r="H83" s="119">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>318</v>
       </c>
       <c r="I83" s="119">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>229</v>
       </c>
       <c r="J83" s="120">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>12634.980000000001</v>
       </c>
       <c r="K83" s="119">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8852.49</v>
       </c>
       <c r="L83" s="118">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>1314037.92</v>
       </c>
       <c r="M83" s="151">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>23816</v>
       </c>
       <c r="N83" s="123">
@@ -21814,7 +21814,7 @@
         <v>38</v>
       </c>
       <c r="G84" s="125">
-        <f t="shared" ref="G84:G89" si="70">D84+E84*2</f>
+        <f t="shared" ref="G84:G89" si="71">D84+E84*2</f>
         <v>120</v>
       </c>
       <c r="H84" s="125">
@@ -21822,7 +21822,7 @@
         <v>120</v>
       </c>
       <c r="I84" s="125">
-        <f t="shared" ref="I84:I89" si="71">D84+E84</f>
+        <f t="shared" ref="I84:I89" si="72">D84+E84</f>
         <v>79</v>
       </c>
       <c r="J84" s="125">
@@ -21834,11 +21834,11 @@
         <v>3407.27</v>
       </c>
       <c r="L84" s="125">
-        <f t="shared" ref="L84:L89" si="72">J84*104</f>
+        <f t="shared" ref="L84:L89" si="73">J84*104</f>
         <v>538262.4</v>
       </c>
       <c r="M84" s="125">
-        <f t="shared" ref="M84:M89" si="73">I84*104</f>
+        <f t="shared" ref="M84:M89" si="74">I84*104</f>
         <v>8216</v>
       </c>
       <c r="N84" s="19"/>
@@ -21884,15 +21884,15 @@
         <v>52</v>
       </c>
       <c r="G85" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>120</v>
       </c>
       <c r="H85" s="125">
-        <f t="shared" ref="H85:H89" si="74">B85+C85*2</f>
+        <f t="shared" ref="H85:H89" si="75">B85+C85*2</f>
         <v>120</v>
       </c>
       <c r="I85" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>78</v>
       </c>
       <c r="J85" s="125">
@@ -21904,11 +21904,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L85" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>538262.4</v>
       </c>
       <c r="M85" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8112</v>
       </c>
       <c r="N85" s="19"/>
@@ -21954,15 +21954,15 @@
         <v>36</v>
       </c>
       <c r="G86" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>38</v>
       </c>
       <c r="H86" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>39</v>
       </c>
       <c r="I86" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>36</v>
       </c>
       <c r="J86" s="125">
@@ -21974,11 +21974,11 @@
         <v>1047.96</v>
       </c>
       <c r="L86" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>115042.72</v>
       </c>
       <c r="M86" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>3744</v>
       </c>
       <c r="N86" s="19"/>
@@ -22024,15 +22024,15 @@
         <v>53</v>
       </c>
       <c r="G87" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>34</v>
       </c>
       <c r="H87" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>35</v>
       </c>
       <c r="I87" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>32</v>
       </c>
       <c r="J87" s="125">
@@ -22044,11 +22044,11 @@
         <v>931.52</v>
       </c>
       <c r="L87" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>102932.96</v>
       </c>
       <c r="M87" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>3328</v>
       </c>
       <c r="N87" s="19"/>
@@ -22092,15 +22092,15 @@
         <v>122</v>
       </c>
       <c r="G88" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="H88" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="I88" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="J88" s="125">
@@ -22112,11 +22112,11 @@
         <v>0</v>
       </c>
       <c r="L88" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="M88" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="N88" s="19"/>
@@ -22160,15 +22160,15 @@
         <v>35</v>
       </c>
       <c r="G89" s="125">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>4</v>
       </c>
       <c r="H89" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>4</v>
       </c>
       <c r="I89" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>4</v>
       </c>
       <c r="J89" s="125">
@@ -22180,11 +22180,11 @@
         <v>101.6</v>
       </c>
       <c r="L89" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>10566.4</v>
       </c>
       <c r="M89" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>416</v>
       </c>
       <c r="N89" s="19"/>
@@ -22225,31 +22225,31 @@
       </c>
       <c r="F90" s="119"/>
       <c r="G90" s="119">
-        <f t="shared" ref="G90:M90" si="75">SUM(G84:G89)</f>
+        <f t="shared" ref="G90:M90" si="76">SUM(G84:G89)</f>
         <v>316</v>
       </c>
       <c r="H90" s="119">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>318</v>
       </c>
       <c r="I90" s="119">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>229</v>
       </c>
       <c r="J90" s="120">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K90" s="119">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>8852.49</v>
       </c>
       <c r="L90" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M90" s="151">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>23816</v>
       </c>
       <c r="N90" s="123">
@@ -22300,7 +22300,7 @@
         <v>38</v>
       </c>
       <c r="G91" s="125">
-        <f t="shared" ref="G91:G96" si="76">D91+E91*2</f>
+        <f t="shared" ref="G91:G96" si="77">D91+E91*2</f>
         <v>120</v>
       </c>
       <c r="H91" s="125">
@@ -22308,7 +22308,7 @@
         <v>120</v>
       </c>
       <c r="I91" s="125">
-        <f t="shared" ref="I91:I96" si="77">D91+E91</f>
+        <f t="shared" ref="I91:I96" si="78">D91+E91</f>
         <v>79</v>
       </c>
       <c r="J91" s="125">
@@ -22320,11 +22320,11 @@
         <v>3407.27</v>
       </c>
       <c r="L91" s="125">
-        <f t="shared" ref="L91:L96" si="78">J91*104</f>
+        <f t="shared" ref="L91:L96" si="79">J91*104</f>
         <v>538262.4</v>
       </c>
       <c r="M91" s="125">
-        <f t="shared" ref="M91:M96" si="79">I91*104</f>
+        <f t="shared" ref="M91:M96" si="80">I91*104</f>
         <v>8216</v>
       </c>
       <c r="N91" s="19"/>
@@ -22367,15 +22367,15 @@
         <v>52</v>
       </c>
       <c r="G92" s="125">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>120</v>
       </c>
       <c r="H92" s="125">
-        <f t="shared" ref="H92:H96" si="80">B92+C92*2</f>
+        <f t="shared" ref="H92:H96" si="81">B92+C92*2</f>
         <v>120</v>
       </c>
       <c r="I92" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>78</v>
       </c>
       <c r="J92" s="125">
@@ -22387,11 +22387,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L92" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>538262.4</v>
       </c>
       <c r="M92" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>8112</v>
       </c>
       <c r="N92" s="19"/>
@@ -22434,15 +22434,15 @@
         <v>36</v>
       </c>
       <c r="G93" s="125">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>38</v>
       </c>
       <c r="H93" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>39</v>
       </c>
       <c r="I93" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>36</v>
       </c>
       <c r="J93" s="125">
@@ -22454,11 +22454,11 @@
         <v>1047.96</v>
       </c>
       <c r="L93" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>115042.72</v>
       </c>
       <c r="M93" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3744</v>
       </c>
       <c r="N93" s="19"/>
@@ -22501,15 +22501,15 @@
         <v>53</v>
       </c>
       <c r="G94" s="125">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>34</v>
       </c>
       <c r="H94" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>35</v>
       </c>
       <c r="I94" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>32</v>
       </c>
       <c r="J94" s="125">
@@ -22521,11 +22521,11 @@
         <v>931.52</v>
       </c>
       <c r="L94" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>102932.96</v>
       </c>
       <c r="M94" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>3328</v>
       </c>
       <c r="N94" s="19"/>
@@ -22566,15 +22566,15 @@
         <v>122</v>
       </c>
       <c r="G95" s="125">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="H95" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="I95" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="J95" s="125">
@@ -22586,11 +22586,11 @@
         <v>0</v>
       </c>
       <c r="L95" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="M95" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="N95" s="19"/>
@@ -22631,15 +22631,15 @@
         <v>35</v>
       </c>
       <c r="G96" s="125">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>4</v>
       </c>
       <c r="H96" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>4</v>
       </c>
       <c r="I96" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>4</v>
       </c>
       <c r="J96" s="125">
@@ -22651,11 +22651,11 @@
         <v>101.6</v>
       </c>
       <c r="L96" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>10566.4</v>
       </c>
       <c r="M96" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>416</v>
       </c>
       <c r="N96" s="19"/>
@@ -22696,31 +22696,31 @@
       </c>
       <c r="F97" s="119"/>
       <c r="G97" s="119">
-        <f t="shared" ref="G97:M97" si="81">SUM(G91:G96)</f>
+        <f t="shared" ref="G97:M97" si="82">SUM(G91:G96)</f>
         <v>316</v>
       </c>
       <c r="H97" s="119">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>318</v>
       </c>
       <c r="I97" s="119">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>229</v>
       </c>
       <c r="J97" s="120">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K97" s="119">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>8852.49</v>
       </c>
       <c r="L97" s="118">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M97" s="151">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>23816</v>
       </c>
       <c r="N97" s="123">
@@ -22770,7 +22770,7 @@
         <v>38</v>
       </c>
       <c r="G98" s="125">
-        <f t="shared" ref="G98:G103" si="82">D98+E98*2</f>
+        <f t="shared" ref="G98:G103" si="83">D98+E98*2</f>
         <v>121</v>
       </c>
       <c r="H98" s="125">
@@ -22790,11 +22790,11 @@
         <v>3407.27</v>
       </c>
       <c r="L98" s="125">
-        <f t="shared" ref="L98:L103" si="83">J98*104</f>
+        <f t="shared" ref="L98:L103" si="84">J98*104</f>
         <v>542747.92000000004</v>
       </c>
       <c r="M98" s="125">
-        <f t="shared" ref="M98:M103" si="84">I98*104</f>
+        <f t="shared" ref="M98:M103" si="85">I98*104</f>
         <v>8216</v>
       </c>
       <c r="N98" s="19"/>
@@ -22837,15 +22837,15 @@
         <v>52</v>
       </c>
       <c r="G99" s="125">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>121</v>
       </c>
       <c r="H99" s="125">
-        <f t="shared" ref="H99:H103" si="85">B99+C99*2</f>
+        <f t="shared" ref="H99:H103" si="86">B99+C99*2</f>
         <v>120</v>
       </c>
       <c r="I99" s="125">
-        <f t="shared" ref="I99:I103" si="86">D99+E99</f>
+        <f t="shared" ref="I99:I103" si="87">D99+E99</f>
         <v>78</v>
       </c>
       <c r="J99" s="125">
@@ -22857,11 +22857,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L99" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M99" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>8112</v>
       </c>
       <c r="N99" s="19"/>
@@ -22904,15 +22904,15 @@
         <v>36</v>
       </c>
       <c r="G100" s="125">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>38</v>
       </c>
       <c r="H100" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>39</v>
       </c>
       <c r="I100" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>36</v>
       </c>
       <c r="J100" s="125">
@@ -22924,11 +22924,11 @@
         <v>1047.96</v>
       </c>
       <c r="L100" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>115042.72</v>
       </c>
       <c r="M100" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>3744</v>
       </c>
       <c r="N100" s="19"/>
@@ -22971,15 +22971,15 @@
         <v>53</v>
       </c>
       <c r="G101" s="125">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>34</v>
       </c>
       <c r="H101" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>35</v>
       </c>
       <c r="I101" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>32</v>
       </c>
       <c r="J101" s="125">
@@ -22991,11 +22991,11 @@
         <v>931.52</v>
       </c>
       <c r="L101" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>102932.96</v>
       </c>
       <c r="M101" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>3328</v>
       </c>
       <c r="N101" s="19"/>
@@ -23036,15 +23036,15 @@
         <v>122</v>
       </c>
       <c r="G102" s="125">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="H102" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="I102" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="J102" s="125">
@@ -23056,11 +23056,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M102" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="N102" s="19"/>
@@ -23101,15 +23101,15 @@
         <v>35</v>
       </c>
       <c r="G103" s="125">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>4</v>
       </c>
       <c r="H103" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>4</v>
       </c>
       <c r="I103" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>4</v>
       </c>
       <c r="J103" s="125">
@@ -23121,11 +23121,11 @@
         <v>101.6</v>
       </c>
       <c r="L103" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>10566.4</v>
       </c>
       <c r="M103" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>416</v>
       </c>
       <c r="N103" s="19"/>
@@ -23166,31 +23166,31 @@
       </c>
       <c r="F104" s="119"/>
       <c r="G104" s="119">
-        <f t="shared" ref="G104:M104" si="87">SUM(G98:G103)</f>
+        <f t="shared" ref="G104:M104" si="88">SUM(G98:G103)</f>
         <v>318</v>
       </c>
       <c r="H104" s="119">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>318</v>
       </c>
       <c r="I104" s="119">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>229</v>
       </c>
       <c r="J104" s="120">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>12634.980000000001</v>
       </c>
       <c r="K104" s="119">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>8852.49</v>
       </c>
       <c r="L104" s="118">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1314037.92</v>
       </c>
       <c r="M104" s="151">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>23816</v>
       </c>
       <c r="N104" s="123">
@@ -23242,7 +23242,7 @@
         <v>38</v>
       </c>
       <c r="G105" s="125">
-        <f t="shared" ref="G105:G110" si="88">D105+E105*2</f>
+        <f t="shared" ref="G105:G110" si="89">D105+E105*2</f>
         <v>121</v>
       </c>
       <c r="H105" s="125">
@@ -23250,7 +23250,7 @@
         <v>120</v>
       </c>
       <c r="I105" s="125">
-        <f t="shared" ref="I105:I110" si="89">D105+E105</f>
+        <f t="shared" ref="I105:I110" si="90">D105+E105</f>
         <v>79</v>
       </c>
       <c r="J105" s="125">
@@ -23262,11 +23262,11 @@
         <v>3407.27</v>
       </c>
       <c r="L105" s="125">
-        <f t="shared" ref="L105:L110" si="90">J105*104</f>
+        <f t="shared" ref="L105:L110" si="91">J105*104</f>
         <v>542747.92000000004</v>
       </c>
       <c r="M105" s="125">
-        <f t="shared" ref="M105:M110" si="91">I105*104</f>
+        <f t="shared" ref="M105:M110" si="92">I105*104</f>
         <v>8216</v>
       </c>
       <c r="N105" s="19"/>
@@ -23309,15 +23309,15 @@
         <v>52</v>
       </c>
       <c r="G106" s="125">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>121</v>
       </c>
       <c r="H106" s="125">
-        <f t="shared" ref="H106:H110" si="92">B106+C106*2</f>
+        <f t="shared" ref="H106:H110" si="93">B106+C106*2</f>
         <v>120</v>
       </c>
       <c r="I106" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>78</v>
       </c>
       <c r="J106" s="125">
@@ -23329,11 +23329,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L106" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M106" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>8112</v>
       </c>
       <c r="N106" s="19"/>
@@ -23376,15 +23376,15 @@
         <v>36</v>
       </c>
       <c r="G107" s="125">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>38</v>
       </c>
       <c r="H107" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>39</v>
       </c>
       <c r="I107" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>36</v>
       </c>
       <c r="J107" s="125">
@@ -23396,11 +23396,11 @@
         <v>1047.96</v>
       </c>
       <c r="L107" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>115042.72</v>
       </c>
       <c r="M107" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3744</v>
       </c>
       <c r="N107" s="19"/>
@@ -23443,15 +23443,15 @@
         <v>53</v>
       </c>
       <c r="G108" s="125">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>34</v>
       </c>
       <c r="H108" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>35</v>
       </c>
       <c r="I108" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>32</v>
       </c>
       <c r="J108" s="125">
@@ -23463,11 +23463,11 @@
         <v>931.52</v>
       </c>
       <c r="L108" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>102932.96</v>
       </c>
       <c r="M108" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>3328</v>
       </c>
       <c r="N108" s="19"/>
@@ -23508,15 +23508,15 @@
         <v>122</v>
       </c>
       <c r="G109" s="125">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="H109" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="I109" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="J109" s="125">
@@ -23528,11 +23528,11 @@
         <v>0</v>
       </c>
       <c r="L109" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="M109" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="N109" s="19"/>
@@ -23573,15 +23573,15 @@
         <v>35</v>
       </c>
       <c r="G110" s="125">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>4</v>
       </c>
       <c r="H110" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>4</v>
       </c>
       <c r="I110" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>4</v>
       </c>
       <c r="J110" s="125">
@@ -23593,11 +23593,11 @@
         <v>101.6</v>
       </c>
       <c r="L110" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>10566.4</v>
       </c>
       <c r="M110" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>416</v>
       </c>
       <c r="N110" s="19"/>
@@ -23638,31 +23638,31 @@
       </c>
       <c r="F111" s="119"/>
       <c r="G111" s="119">
-        <f t="shared" ref="G111:M111" si="93">SUM(G105:G110)</f>
+        <f t="shared" ref="G111:M111" si="94">SUM(G105:G110)</f>
         <v>318</v>
       </c>
       <c r="H111" s="119">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>318</v>
       </c>
       <c r="I111" s="119">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>229</v>
       </c>
       <c r="J111" s="120">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>12634.980000000001</v>
       </c>
       <c r="K111" s="119">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>8852.49</v>
       </c>
       <c r="L111" s="118">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1314037.92</v>
       </c>
       <c r="M111" s="151">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>23816</v>
       </c>
       <c r="N111" s="123">
@@ -23712,7 +23712,7 @@
         <v>38</v>
       </c>
       <c r="G112" s="321">
-        <f t="shared" ref="G112:G117" si="94">D112+E112*2</f>
+        <f t="shared" ref="G112:G117" si="95">D112+E112*2</f>
         <v>75</v>
       </c>
       <c r="H112" s="116">
@@ -23720,7 +23720,7 @@
         <v>75</v>
       </c>
       <c r="I112" s="322">
-        <f t="shared" ref="I112:I117" si="95">D112+E112</f>
+        <f t="shared" ref="I112:I117" si="96">D112+E112</f>
         <v>72</v>
       </c>
       <c r="J112" s="322">
@@ -23732,11 +23732,11 @@
         <v>3105.36</v>
       </c>
       <c r="L112" s="116">
-        <f t="shared" ref="L112:L117" si="96">J112*104</f>
+        <f t="shared" ref="L112:L117" si="97">J112*104</f>
         <v>336414</v>
       </c>
       <c r="M112" s="116">
-        <f t="shared" ref="M112:M117" si="97">I112*104</f>
+        <f t="shared" ref="M112:M117" si="98">I112*104</f>
         <v>7488</v>
       </c>
       <c r="N112" s="19"/>
@@ -23777,15 +23777,15 @@
         <v>52</v>
       </c>
       <c r="G113" s="321">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>75</v>
       </c>
       <c r="H113" s="116">
-        <f t="shared" ref="H113:H117" si="98">B113+C113*2</f>
+        <f t="shared" ref="H113:H117" si="99">B113+C113*2</f>
         <v>75</v>
       </c>
       <c r="I113" s="116">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>75</v>
       </c>
       <c r="J113" s="116">
@@ -23797,11 +23797,11 @@
         <v>3234.75</v>
       </c>
       <c r="L113" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>336414</v>
       </c>
       <c r="M113" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>7800</v>
       </c>
       <c r="N113" s="19"/>
@@ -23843,15 +23843,15 @@
         <v>36</v>
       </c>
       <c r="G114" s="321">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="H114" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="I114" s="116">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="J114" s="116">
@@ -23863,11 +23863,11 @@
         <v>0</v>
       </c>
       <c r="L114" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="M114" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="N114" s="19"/>
@@ -23908,15 +23908,15 @@
         <v>53</v>
       </c>
       <c r="G115" s="321">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="H115" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="I115" s="116">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="J115" s="116">
@@ -23928,11 +23928,11 @@
         <v>0</v>
       </c>
       <c r="L115" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="M115" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="N115" s="19"/>
@@ -23973,15 +23973,15 @@
         <v>122</v>
       </c>
       <c r="G116" s="321">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="H116" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="I116" s="116">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="J116" s="323">
@@ -23993,11 +23993,11 @@
         <v>0</v>
       </c>
       <c r="L116" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="M116" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="N116" s="19"/>
@@ -24038,15 +24038,15 @@
         <v>35</v>
       </c>
       <c r="G117" s="321">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="H117" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="I117" s="324">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="J117" s="324">
@@ -24058,11 +24058,11 @@
         <v>0</v>
       </c>
       <c r="L117" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="M117" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="N117" s="19"/>
@@ -24103,31 +24103,31 @@
       </c>
       <c r="F118" s="119"/>
       <c r="G118" s="119">
-        <f t="shared" ref="G118:M118" si="99">SUM(G112:G117)</f>
+        <f t="shared" ref="G118:M118" si="100">SUM(G112:G117)</f>
         <v>150</v>
       </c>
       <c r="H118" s="119">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>150</v>
       </c>
       <c r="I118" s="119">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>147</v>
       </c>
       <c r="J118" s="120">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>6469.5</v>
       </c>
       <c r="K118" s="119">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L118" s="119">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>672828</v>
       </c>
       <c r="M118" s="119">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>15288</v>
       </c>
       <c r="N118" s="123">
@@ -24177,7 +24177,7 @@
         <v>38</v>
       </c>
       <c r="G119" s="333">
-        <f t="shared" ref="G119:G124" si="100">D119+E119*2</f>
+        <f t="shared" ref="G119:G124" si="101">D119+E119*2</f>
         <v>57</v>
       </c>
       <c r="H119" s="218">
@@ -24185,7 +24185,7 @@
         <v>57</v>
       </c>
       <c r="I119" s="334">
-        <f t="shared" ref="I119:I124" si="101">D119+E119</f>
+        <f t="shared" ref="I119:I124" si="102">D119+E119</f>
         <v>54</v>
       </c>
       <c r="J119" s="334">
@@ -24197,11 +24197,11 @@
         <v>2329.02</v>
       </c>
       <c r="L119" s="218">
-        <f t="shared" ref="L119:L124" si="102">J119*104</f>
+        <f t="shared" ref="L119:L124" si="103">J119*104</f>
         <v>255674.64000000004</v>
       </c>
       <c r="M119" s="218">
-        <f t="shared" ref="M119:M124" si="103">I119*104</f>
+        <f t="shared" ref="M119:M124" si="104">I119*104</f>
         <v>5616</v>
       </c>
       <c r="N119" s="19"/>
@@ -24242,15 +24242,15 @@
         <v>52</v>
       </c>
       <c r="G120" s="333">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>57</v>
       </c>
       <c r="H120" s="218">
-        <f t="shared" ref="H120:H124" si="104">B120+C120*2</f>
+        <f t="shared" ref="H120:H124" si="105">B120+C120*2</f>
         <v>57</v>
       </c>
       <c r="I120" s="218">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>57</v>
       </c>
       <c r="J120" s="218">
@@ -24262,11 +24262,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L120" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M120" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>5928</v>
       </c>
       <c r="N120" s="19"/>
@@ -24308,15 +24308,15 @@
         <v>36</v>
       </c>
       <c r="G121" s="333">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="H121" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="I121" s="218">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="J121" s="218">
@@ -24328,11 +24328,11 @@
         <v>0</v>
       </c>
       <c r="L121" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="M121" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="N121" s="19"/>
@@ -24373,15 +24373,15 @@
         <v>53</v>
       </c>
       <c r="G122" s="333">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="H122" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="I122" s="218">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="J122" s="218">
@@ -24393,11 +24393,11 @@
         <v>0</v>
       </c>
       <c r="L122" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="M122" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="N122" s="19"/>
@@ -24439,15 +24439,15 @@
         <v>122</v>
       </c>
       <c r="G123" s="333">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="H123" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="I123" s="218">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="J123" s="335">
@@ -24459,11 +24459,11 @@
         <v>0</v>
       </c>
       <c r="L123" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="M123" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="N123" s="19"/>
@@ -24504,15 +24504,15 @@
         <v>35</v>
       </c>
       <c r="G124" s="333">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="H124" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="I124" s="336">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="J124" s="336">
@@ -24524,11 +24524,11 @@
         <v>0</v>
       </c>
       <c r="L124" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="M124" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="N124" s="19"/>
@@ -24569,15 +24569,15 @@
       </c>
       <c r="F125" s="119"/>
       <c r="G125" s="119">
-        <f t="shared" ref="G125:M125" si="105">SUM(G119:G124)</f>
+        <f t="shared" ref="G125:M125" si="106">SUM(G119:G124)</f>
         <v>114</v>
       </c>
       <c r="H125" s="119">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>114</v>
       </c>
       <c r="I125" s="119">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>111</v>
       </c>
       <c r="J125" s="120">
@@ -24585,15 +24585,15 @@
         <v>4916.8200000000006</v>
       </c>
       <c r="K125" s="119">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>4787.43</v>
       </c>
       <c r="L125" s="119">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>511349.28000000009</v>
       </c>
       <c r="M125" s="119">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>11544</v>
       </c>
       <c r="N125" s="123">
@@ -24643,7 +24643,7 @@
         <v>38</v>
       </c>
       <c r="G126" s="125">
-        <f t="shared" ref="G126:G131" si="106">D126+E126*2</f>
+        <f t="shared" ref="G126:G131" si="107">D126+E126*2</f>
         <v>119</v>
       </c>
       <c r="H126" s="125">
@@ -24651,7 +24651,7 @@
         <v>120</v>
       </c>
       <c r="I126" s="125">
-        <f t="shared" ref="I126:I131" si="107">D126+E126</f>
+        <f t="shared" ref="I126:I131" si="108">D126+E126</f>
         <v>80</v>
       </c>
       <c r="J126" s="125">
@@ -24663,11 +24663,11 @@
         <v>3450.4</v>
       </c>
       <c r="L126" s="125">
-        <f t="shared" ref="L126:L131" si="108">J126*104</f>
+        <f t="shared" ref="L126:L131" si="109">J126*104</f>
         <v>533776.88</v>
       </c>
       <c r="M126" s="125">
-        <f t="shared" ref="M126:M131" si="109">I126*104</f>
+        <f t="shared" ref="M126:M131" si="110">I126*104</f>
         <v>8320</v>
       </c>
       <c r="N126" s="19"/>
@@ -24710,15 +24710,15 @@
         <v>52</v>
       </c>
       <c r="G127" s="125">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>118</v>
       </c>
       <c r="H127" s="125">
-        <f t="shared" ref="H127:H131" si="110">B127+C127*2</f>
+        <f t="shared" ref="H127:H131" si="111">B127+C127*2</f>
         <v>120</v>
       </c>
       <c r="I127" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>78</v>
       </c>
       <c r="J127" s="125">
@@ -24730,11 +24730,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L127" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>529291.36</v>
       </c>
       <c r="M127" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>8112</v>
       </c>
       <c r="N127" s="19"/>
@@ -24777,15 +24777,15 @@
         <v>36</v>
       </c>
       <c r="G128" s="125">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>37</v>
       </c>
       <c r="H128" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>39</v>
       </c>
       <c r="I128" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>35</v>
       </c>
       <c r="J128" s="125">
@@ -24797,11 +24797,11 @@
         <v>1018.85</v>
       </c>
       <c r="L128" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>112015.28</v>
       </c>
       <c r="M128" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>3640</v>
       </c>
       <c r="N128" s="19"/>
@@ -24844,15 +24844,15 @@
         <v>53</v>
       </c>
       <c r="G129" s="125">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>34</v>
       </c>
       <c r="H129" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>35</v>
       </c>
       <c r="I129" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>32</v>
       </c>
       <c r="J129" s="125">
@@ -24864,11 +24864,11 @@
         <v>931.52</v>
       </c>
       <c r="L129" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>102932.96</v>
       </c>
       <c r="M129" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>3328</v>
       </c>
       <c r="N129" s="19"/>
@@ -24909,15 +24909,15 @@
         <v>122</v>
       </c>
       <c r="G130" s="125">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="H130" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="I130" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="J130" s="125">
@@ -24929,11 +24929,11 @@
         <v>0</v>
       </c>
       <c r="L130" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="M130" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="N130" s="19"/>
@@ -24974,15 +24974,15 @@
         <v>35</v>
       </c>
       <c r="G131" s="125">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>4</v>
       </c>
       <c r="H131" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>4</v>
       </c>
       <c r="I131" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>4</v>
       </c>
       <c r="J131" s="125">
@@ -24994,11 +24994,11 @@
         <v>101.6</v>
       </c>
       <c r="L131" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>10566.4</v>
       </c>
       <c r="M131" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>416</v>
       </c>
       <c r="N131" s="19"/>
@@ -25039,31 +25039,31 @@
       </c>
       <c r="F132" s="119"/>
       <c r="G132" s="119">
-        <f t="shared" ref="G132:M132" si="111">SUM(G126:G131)</f>
+        <f t="shared" ref="G132:M132" si="112">SUM(G126:G131)</f>
         <v>312</v>
       </c>
       <c r="H132" s="119">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>318</v>
       </c>
       <c r="I132" s="119">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>229</v>
       </c>
       <c r="J132" s="120">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>12390.220000000001</v>
       </c>
       <c r="K132" s="119">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>8866.510000000002</v>
       </c>
       <c r="L132" s="118">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>1288582.8799999999</v>
       </c>
       <c r="M132" s="151">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>23816</v>
       </c>
       <c r="N132" s="123">
@@ -25113,7 +25113,7 @@
         <v>38</v>
       </c>
       <c r="G133" s="125">
-        <f t="shared" ref="G133:G138" si="112">D133+E133*2</f>
+        <f t="shared" ref="G133:G138" si="113">D133+E133*2</f>
         <v>119</v>
       </c>
       <c r="H133" s="125">
@@ -25121,7 +25121,7 @@
         <v>120</v>
       </c>
       <c r="I133" s="125">
-        <f t="shared" ref="I133:I138" si="113">D133+E133</f>
+        <f t="shared" ref="I133:I138" si="114">D133+E133</f>
         <v>79</v>
       </c>
       <c r="J133" s="125">
@@ -25133,11 +25133,11 @@
         <v>3407.27</v>
       </c>
       <c r="L133" s="125">
-        <f t="shared" ref="L133:L138" si="114">J133*104</f>
+        <f t="shared" ref="L133:L138" si="115">J133*104</f>
         <v>533776.88</v>
       </c>
       <c r="M133" s="125">
-        <f t="shared" ref="M133:M138" si="115">I133*104</f>
+        <f t="shared" ref="M133:M138" si="116">I133*104</f>
         <v>8216</v>
       </c>
       <c r="N133" s="19"/>
@@ -25180,15 +25180,15 @@
         <v>52</v>
       </c>
       <c r="G134" s="125">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>119</v>
       </c>
       <c r="H134" s="125">
-        <f t="shared" ref="H134:H138" si="116">B134+C134*2</f>
+        <f t="shared" ref="H134:H138" si="117">B134+C134*2</f>
         <v>120</v>
       </c>
       <c r="I134" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>78</v>
       </c>
       <c r="J134" s="125">
@@ -25200,11 +25200,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L134" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>533776.88</v>
       </c>
       <c r="M134" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>8112</v>
       </c>
       <c r="N134" s="19"/>
@@ -25247,15 +25247,15 @@
         <v>36</v>
       </c>
       <c r="G135" s="125">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>38</v>
       </c>
       <c r="H135" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>39</v>
       </c>
       <c r="I135" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>36</v>
       </c>
       <c r="J135" s="125">
@@ -25267,11 +25267,11 @@
         <v>1047.96</v>
       </c>
       <c r="L135" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>115042.72</v>
       </c>
       <c r="M135" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3744</v>
       </c>
       <c r="N135" s="19"/>
@@ -25314,15 +25314,15 @@
         <v>53</v>
       </c>
       <c r="G136" s="125">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>34</v>
       </c>
       <c r="H136" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>35</v>
       </c>
       <c r="I136" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>32</v>
       </c>
       <c r="J136" s="125">
@@ -25334,11 +25334,11 @@
         <v>931.52</v>
       </c>
       <c r="L136" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>102932.96</v>
       </c>
       <c r="M136" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>3328</v>
       </c>
       <c r="N136" s="19"/>
@@ -25379,15 +25379,15 @@
         <v>122</v>
       </c>
       <c r="G137" s="125">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0</v>
       </c>
       <c r="H137" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="I137" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="J137" s="125">
@@ -25399,11 +25399,11 @@
         <v>0</v>
       </c>
       <c r="L137" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="M137" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="N137" s="19"/>
@@ -25444,15 +25444,15 @@
         <v>35</v>
       </c>
       <c r="G138" s="125">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>4</v>
       </c>
       <c r="H138" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>4</v>
       </c>
       <c r="I138" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>4</v>
       </c>
       <c r="J138" s="125">
@@ -25464,11 +25464,11 @@
         <v>101.6</v>
       </c>
       <c r="L138" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>10566.4</v>
       </c>
       <c r="M138" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>416</v>
       </c>
       <c r="N138" s="19"/>
@@ -25509,31 +25509,31 @@
       </c>
       <c r="F139" s="119"/>
       <c r="G139" s="119">
-        <f t="shared" ref="G139:M139" si="117">SUM(G133:G138)</f>
+        <f t="shared" ref="G139:M139" si="118">SUM(G133:G138)</f>
         <v>314</v>
       </c>
       <c r="H139" s="119">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>318</v>
       </c>
       <c r="I139" s="119">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>229</v>
       </c>
       <c r="J139" s="120">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>12462.460000000001</v>
       </c>
       <c r="K139" s="119">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>8852.49</v>
       </c>
       <c r="L139" s="118">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>1296095.8399999999</v>
       </c>
       <c r="M139" s="151">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>23816</v>
       </c>
       <c r="N139" s="123">
@@ -25583,7 +25583,7 @@
         <v>38</v>
       </c>
       <c r="G140" s="221">
-        <f t="shared" ref="G140:G145" si="118">D140+E140*2</f>
+        <f t="shared" ref="G140:G145" si="119">D140+E140*2</f>
         <v>118</v>
       </c>
       <c r="H140" s="125">
@@ -25591,7 +25591,7 @@
         <v>120</v>
       </c>
       <c r="I140" s="222">
-        <f t="shared" ref="I140:I145" si="119">D140+E140</f>
+        <f t="shared" ref="I140:I145" si="120">D140+E140</f>
         <v>79</v>
       </c>
       <c r="J140" s="222">
@@ -25603,11 +25603,11 @@
         <v>3407.27</v>
       </c>
       <c r="L140" s="125">
-        <f t="shared" ref="L140:L145" si="120">J140*104</f>
+        <f t="shared" ref="L140:L145" si="121">J140*104</f>
         <v>529291.36</v>
       </c>
       <c r="M140" s="125">
-        <f t="shared" ref="M140:M145" si="121">I140*104</f>
+        <f t="shared" ref="M140:M145" si="122">I140*104</f>
         <v>8216</v>
       </c>
       <c r="N140" s="19"/>
@@ -25650,15 +25650,15 @@
         <v>52</v>
       </c>
       <c r="G141" s="221">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>118</v>
       </c>
       <c r="H141" s="125">
-        <f t="shared" ref="H141:H145" si="122">B141+C141*2</f>
+        <f t="shared" ref="H141:H145" si="123">B141+C141*2</f>
         <v>120</v>
       </c>
       <c r="I141" s="125">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>78</v>
       </c>
       <c r="J141" s="125">
@@ -25670,11 +25670,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L141" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>529291.36</v>
       </c>
       <c r="M141" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>8112</v>
       </c>
       <c r="N141" s="19"/>
@@ -25717,15 +25717,15 @@
         <v>36</v>
       </c>
       <c r="G142" s="221">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>38</v>
       </c>
       <c r="H142" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>39</v>
       </c>
       <c r="I142" s="125">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>36</v>
       </c>
       <c r="J142" s="125">
@@ -25737,11 +25737,11 @@
         <v>1047.96</v>
       </c>
       <c r="L142" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>115042.72</v>
       </c>
       <c r="M142" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>3744</v>
       </c>
       <c r="N142" s="19"/>
@@ -25784,15 +25784,15 @@
         <v>53</v>
       </c>
       <c r="G143" s="221">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>34</v>
       </c>
       <c r="H143" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>35</v>
       </c>
       <c r="I143" s="125">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>32</v>
       </c>
       <c r="J143" s="125">
@@ -25804,11 +25804,11 @@
         <v>931.52</v>
       </c>
       <c r="L143" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>102932.96</v>
       </c>
       <c r="M143" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>3328</v>
       </c>
       <c r="N143" s="19"/>
@@ -25849,15 +25849,15 @@
         <v>122</v>
       </c>
       <c r="G144" s="221">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
       <c r="H144" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="I144" s="125">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="J144" s="223">
@@ -25869,11 +25869,11 @@
         <v>0</v>
       </c>
       <c r="L144" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="M144" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
       <c r="N144" s="19"/>
@@ -25914,15 +25914,15 @@
         <v>35</v>
       </c>
       <c r="G145" s="221">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>4</v>
       </c>
       <c r="H145" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>4</v>
       </c>
       <c r="I145" s="224">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>4</v>
       </c>
       <c r="J145" s="224">
@@ -25934,11 +25934,11 @@
         <v>101.6</v>
       </c>
       <c r="L145" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>10566.4</v>
       </c>
       <c r="M145" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>416</v>
       </c>
       <c r="N145" s="19"/>
@@ -25979,31 +25979,31 @@
       </c>
       <c r="F146" s="119"/>
       <c r="G146" s="119">
-        <f t="shared" ref="G146:M146" si="123">SUM(G140:G145)</f>
+        <f t="shared" ref="G146:M146" si="124">SUM(G140:G145)</f>
         <v>312</v>
       </c>
       <c r="H146" s="119">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>318</v>
       </c>
       <c r="I146" s="119">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>229</v>
       </c>
       <c r="J146" s="120">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>12376.2</v>
       </c>
       <c r="K146" s="119">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>8852.49</v>
       </c>
       <c r="L146" s="119">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>1287124.7999999998</v>
       </c>
       <c r="M146" s="119">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>23816</v>
       </c>
       <c r="N146" s="123">
@@ -26054,7 +26054,7 @@
         <v>38</v>
       </c>
       <c r="G147" s="218">
-        <f t="shared" ref="G147:G152" si="124">D147+E147*2</f>
+        <f t="shared" ref="G147:G152" si="125">D147+E147*2</f>
         <v>71</v>
       </c>
       <c r="H147" s="218">
@@ -26062,7 +26062,7 @@
         <v>71</v>
       </c>
       <c r="I147" s="218">
-        <f t="shared" ref="I147:I152" si="125">D147+E147</f>
+        <f t="shared" ref="I147:I152" si="126">D147+E147</f>
         <v>54</v>
       </c>
       <c r="J147" s="218">
@@ -26074,11 +26074,11 @@
         <v>2329.02</v>
       </c>
       <c r="L147" s="218">
-        <f t="shared" ref="L147:L152" si="126">J147*104</f>
+        <f t="shared" ref="L147:L152" si="127">J147*104</f>
         <v>318471.92</v>
       </c>
       <c r="M147" s="218">
-        <f t="shared" ref="M147:M152" si="127">I147*104</f>
+        <f t="shared" ref="M147:M152" si="128">I147*104</f>
         <v>5616</v>
       </c>
       <c r="N147" s="19"/>
@@ -26100,7 +26100,7 @@
       </c>
     </row>
     <row r="148" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="362" t="s">
+      <c r="A148" s="371" t="s">
         <v>189</v>
       </c>
       <c r="B148" s="218">
@@ -26121,15 +26121,15 @@
         <v>52</v>
       </c>
       <c r="G148" s="218">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>71</v>
       </c>
       <c r="H148" s="218">
-        <f t="shared" ref="H148:H152" si="128">B148+C148*2</f>
+        <f t="shared" ref="H148:H152" si="129">B148+C148*2</f>
         <v>71</v>
       </c>
       <c r="I148" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>57</v>
       </c>
       <c r="J148" s="218">
@@ -26141,11 +26141,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L148" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>318471.92</v>
       </c>
       <c r="M148" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>5928</v>
       </c>
       <c r="N148" s="19"/>
@@ -26169,7 +26169,7 @@
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A149" s="362"/>
+      <c r="A149" s="371"/>
       <c r="B149" s="218">
         <v>0</v>
       </c>
@@ -26188,15 +26188,15 @@
         <v>36</v>
       </c>
       <c r="G149" s="218">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="H149" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="I149" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="J149" s="218">
@@ -26208,11 +26208,11 @@
         <v>0</v>
       </c>
       <c r="L149" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="M149" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="N149" s="19"/>
@@ -26234,7 +26234,7 @@
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A150" s="362"/>
+      <c r="A150" s="371"/>
       <c r="B150" s="218">
         <v>0</v>
       </c>
@@ -26253,15 +26253,15 @@
         <v>53</v>
       </c>
       <c r="G150" s="218">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="H150" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="I150" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="J150" s="218">
@@ -26273,11 +26273,11 @@
         <v>0</v>
       </c>
       <c r="L150" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="M150" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="N150" s="19"/>
@@ -26299,7 +26299,7 @@
       </c>
     </row>
     <row r="151" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="362"/>
+      <c r="A151" s="371"/>
       <c r="B151" s="218">
         <v>0</v>
       </c>
@@ -26318,15 +26318,15 @@
         <v>122</v>
       </c>
       <c r="G151" s="218">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="H151" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="I151" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="J151" s="218">
@@ -26338,11 +26338,11 @@
         <v>0</v>
       </c>
       <c r="L151" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="M151" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="N151" s="19"/>
@@ -26364,7 +26364,7 @@
       </c>
     </row>
     <row r="152" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="362"/>
+      <c r="A152" s="371"/>
       <c r="B152" s="218">
         <v>0</v>
       </c>
@@ -26383,15 +26383,15 @@
         <v>35</v>
       </c>
       <c r="G152" s="218">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>0</v>
       </c>
       <c r="H152" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="I152" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="J152" s="218">
@@ -26403,11 +26403,11 @@
         <v>0</v>
       </c>
       <c r="L152" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="M152" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="N152" s="19"/>
@@ -26448,15 +26448,15 @@
       </c>
       <c r="F153" s="119"/>
       <c r="G153" s="119">
-        <f t="shared" ref="G153:M153" si="129">SUM(G147:G152)</f>
+        <f t="shared" ref="G153:M153" si="130">SUM(G147:G152)</f>
         <v>142</v>
       </c>
       <c r="H153" s="119">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>142</v>
       </c>
       <c r="I153" s="119">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>111</v>
       </c>
       <c r="J153" s="120">
@@ -26464,15 +26464,15 @@
         <v>6124.46</v>
       </c>
       <c r="K153" s="119">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>4787.43</v>
       </c>
       <c r="L153" s="118">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>636943.84</v>
       </c>
       <c r="M153" s="151">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>11544</v>
       </c>
       <c r="N153" s="123">
@@ -26522,7 +26522,7 @@
         <v>38</v>
       </c>
       <c r="G154" s="125">
-        <f t="shared" ref="G154:G159" si="130">D154+E154*2</f>
+        <f t="shared" ref="G154:G159" si="131">D154+E154*2</f>
         <v>120</v>
       </c>
       <c r="H154" s="125">
@@ -26530,7 +26530,7 @@
         <v>120</v>
       </c>
       <c r="I154" s="125">
-        <f t="shared" ref="I154:I159" si="131">D154+E154</f>
+        <f t="shared" ref="I154:I159" si="132">D154+E154</f>
         <v>79</v>
       </c>
       <c r="J154" s="125">
@@ -26542,11 +26542,11 @@
         <v>3407.27</v>
       </c>
       <c r="L154" s="125">
-        <f t="shared" ref="L154:L159" si="132">J154*104</f>
+        <f t="shared" ref="L154:L159" si="133">J154*104</f>
         <v>538262.4</v>
       </c>
       <c r="M154" s="125">
-        <f t="shared" ref="M154:M159" si="133">I154*104</f>
+        <f t="shared" ref="M154:M159" si="134">I154*104</f>
         <v>8216</v>
       </c>
       <c r="N154" s="19"/>
@@ -26589,15 +26589,15 @@
         <v>52</v>
       </c>
       <c r="G155" s="125">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>120</v>
       </c>
       <c r="H155" s="125">
-        <f t="shared" ref="H155:H159" si="134">B155+C155*2</f>
+        <f t="shared" ref="H155:H159" si="135">B155+C155*2</f>
         <v>120</v>
       </c>
       <c r="I155" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>78</v>
       </c>
       <c r="J155" s="125">
@@ -26609,11 +26609,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L155" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>538262.4</v>
       </c>
       <c r="M155" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>8112</v>
       </c>
       <c r="N155" s="19"/>
@@ -26658,15 +26658,15 @@
         <v>36</v>
       </c>
       <c r="G156" s="125">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>38</v>
       </c>
       <c r="H156" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>39</v>
       </c>
       <c r="I156" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>36</v>
       </c>
       <c r="J156" s="125">
@@ -26678,11 +26678,11 @@
         <v>1047.96</v>
       </c>
       <c r="L156" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>115042.72</v>
       </c>
       <c r="M156" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3744</v>
       </c>
       <c r="N156" s="19"/>
@@ -26727,15 +26727,15 @@
         <v>53</v>
       </c>
       <c r="G157" s="125">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>34</v>
       </c>
       <c r="H157" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>35</v>
       </c>
       <c r="I157" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>32</v>
       </c>
       <c r="J157" s="125">
@@ -26747,11 +26747,11 @@
         <v>931.52</v>
       </c>
       <c r="L157" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>102932.96</v>
       </c>
       <c r="M157" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3328</v>
       </c>
       <c r="N157" s="19"/>
@@ -26794,15 +26794,15 @@
         <v>122</v>
       </c>
       <c r="G158" s="125">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0</v>
       </c>
       <c r="H158" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
       <c r="I158" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="J158" s="125">
@@ -26814,11 +26814,11 @@
         <v>0</v>
       </c>
       <c r="L158" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0</v>
       </c>
       <c r="M158" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0</v>
       </c>
       <c r="N158" s="19"/>
@@ -26861,15 +26861,15 @@
         <v>35</v>
       </c>
       <c r="G159" s="125">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>4</v>
       </c>
       <c r="H159" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>4</v>
       </c>
       <c r="I159" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>4</v>
       </c>
       <c r="J159" s="125">
@@ -26881,11 +26881,11 @@
         <v>101.6</v>
       </c>
       <c r="L159" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>10566.4</v>
       </c>
       <c r="M159" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>416</v>
       </c>
       <c r="N159" s="19"/>
@@ -26926,31 +26926,31 @@
       </c>
       <c r="F160" s="119"/>
       <c r="G160" s="119">
-        <f t="shared" ref="G160:M160" si="135">SUM(G154:G159)</f>
+        <f t="shared" ref="G160:M160" si="136">SUM(G154:G159)</f>
         <v>316</v>
       </c>
       <c r="H160" s="119">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>318</v>
       </c>
       <c r="I160" s="119">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>229</v>
       </c>
       <c r="J160" s="120">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K160" s="119">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>8852.49</v>
       </c>
       <c r="L160" s="118">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M160" s="151">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>23816</v>
       </c>
       <c r="N160" s="123">
@@ -27000,7 +27000,7 @@
         <v>38</v>
       </c>
       <c r="G161" s="321">
-        <f t="shared" ref="G161:G166" si="136">D161+E161*2</f>
+        <f t="shared" ref="G161:G166" si="137">D161+E161*2</f>
         <v>75</v>
       </c>
       <c r="H161" s="116">
@@ -27008,7 +27008,7 @@
         <v>75</v>
       </c>
       <c r="I161" s="322">
-        <f t="shared" ref="I161:I166" si="137">D161+E161</f>
+        <f t="shared" ref="I161:I166" si="138">D161+E161</f>
         <v>72</v>
       </c>
       <c r="J161" s="322">
@@ -27020,11 +27020,11 @@
         <v>3105.36</v>
       </c>
       <c r="L161" s="116">
-        <f t="shared" ref="L161:L166" si="138">J161*104</f>
+        <f t="shared" ref="L161:L166" si="139">J161*104</f>
         <v>336414</v>
       </c>
       <c r="M161" s="116">
-        <f t="shared" ref="M161:M166" si="139">I161*104</f>
+        <f t="shared" ref="M161:M166" si="140">I161*104</f>
         <v>7488</v>
       </c>
       <c r="N161" s="19"/>
@@ -27065,15 +27065,15 @@
         <v>52</v>
       </c>
       <c r="G162" s="321">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>75</v>
       </c>
       <c r="H162" s="116">
-        <f t="shared" ref="H162:H166" si="140">B162+C162*2</f>
+        <f t="shared" ref="H162:H166" si="141">B162+C162*2</f>
         <v>75</v>
       </c>
       <c r="I162" s="116">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>75</v>
       </c>
       <c r="J162" s="116">
@@ -27085,11 +27085,11 @@
         <v>3234.75</v>
       </c>
       <c r="L162" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>336414</v>
       </c>
       <c r="M162" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>7800</v>
       </c>
       <c r="N162" s="19"/>
@@ -27131,15 +27131,15 @@
         <v>36</v>
       </c>
       <c r="G163" s="321">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
       <c r="H163" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="I163" s="116">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="J163" s="116">
@@ -27151,11 +27151,11 @@
         <v>0</v>
       </c>
       <c r="L163" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="M163" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="N163" s="19"/>
@@ -27196,15 +27196,15 @@
         <v>53</v>
       </c>
       <c r="G164" s="321">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
       <c r="H164" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="I164" s="116">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="J164" s="116">
@@ -27216,11 +27216,11 @@
         <v>0</v>
       </c>
       <c r="L164" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="M164" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="N164" s="19"/>
@@ -27261,15 +27261,15 @@
         <v>122</v>
       </c>
       <c r="G165" s="321">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
       <c r="H165" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="I165" s="116">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="J165" s="323">
@@ -27281,11 +27281,11 @@
         <v>0</v>
       </c>
       <c r="L165" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="M165" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="N165" s="19"/>
@@ -27326,15 +27326,15 @@
         <v>35</v>
       </c>
       <c r="G166" s="321">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
       <c r="H166" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="I166" s="324">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="J166" s="324">
@@ -27346,11 +27346,11 @@
         <v>0</v>
       </c>
       <c r="L166" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="M166" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="N166" s="19"/>
@@ -27391,31 +27391,31 @@
       </c>
       <c r="F167" s="119"/>
       <c r="G167" s="119">
-        <f t="shared" ref="G167:M167" si="141">SUM(G161:G166)</f>
+        <f t="shared" ref="G167:M167" si="142">SUM(G161:G166)</f>
         <v>150</v>
       </c>
       <c r="H167" s="119">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>150</v>
       </c>
       <c r="I167" s="119">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>147</v>
       </c>
       <c r="J167" s="120">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>6469.5</v>
       </c>
       <c r="K167" s="119">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L167" s="119">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>672828</v>
       </c>
       <c r="M167" s="119">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>15288</v>
       </c>
       <c r="N167" s="123">
@@ -27465,7 +27465,7 @@
         <v>38</v>
       </c>
       <c r="G168" s="333">
-        <f t="shared" ref="G168:G173" si="142">D168+E168*2</f>
+        <f t="shared" ref="G168:G173" si="143">D168+E168*2</f>
         <v>56</v>
       </c>
       <c r="H168" s="218">
@@ -27473,7 +27473,7 @@
         <v>57</v>
       </c>
       <c r="I168" s="334">
-        <f t="shared" ref="I168:I173" si="143">D168+E168</f>
+        <f t="shared" ref="I168:I173" si="144">D168+E168</f>
         <v>54</v>
       </c>
       <c r="J168" s="334">
@@ -27485,11 +27485,11 @@
         <v>2329.02</v>
       </c>
       <c r="L168" s="218">
-        <f t="shared" ref="L168:L173" si="144">J168*104</f>
+        <f t="shared" ref="L168:L173" si="145">J168*104</f>
         <v>251189.12000000002</v>
       </c>
       <c r="M168" s="218">
-        <f t="shared" ref="M168:M173" si="145">I168*104</f>
+        <f t="shared" ref="M168:M173" si="146">I168*104</f>
         <v>5616</v>
       </c>
       <c r="N168" s="19"/>
@@ -27530,15 +27530,15 @@
         <v>52</v>
       </c>
       <c r="G169" s="333">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>57</v>
       </c>
       <c r="H169" s="218">
-        <f t="shared" ref="H169:H173" si="146">B169+C169*2</f>
+        <f t="shared" ref="H169:H173" si="147">B169+C169*2</f>
         <v>57</v>
       </c>
       <c r="I169" s="218">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>57</v>
       </c>
       <c r="J169" s="218">
@@ -27550,11 +27550,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L169" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M169" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>5928</v>
       </c>
       <c r="N169" s="19"/>
@@ -27596,15 +27596,15 @@
         <v>36</v>
       </c>
       <c r="G170" s="333">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0</v>
       </c>
       <c r="H170" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="I170" s="218">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="J170" s="218">
@@ -27616,11 +27616,11 @@
         <v>0</v>
       </c>
       <c r="L170" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M170" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="N170" s="19"/>
@@ -27661,15 +27661,15 @@
         <v>53</v>
       </c>
       <c r="G171" s="333">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0</v>
       </c>
       <c r="H171" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="I171" s="218">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="J171" s="218">
@@ -27681,11 +27681,11 @@
         <v>0</v>
       </c>
       <c r="L171" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M171" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="N171" s="19"/>
@@ -27726,15 +27726,15 @@
         <v>122</v>
       </c>
       <c r="G172" s="333">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0</v>
       </c>
       <c r="H172" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="I172" s="218">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="J172" s="335">
@@ -27746,11 +27746,11 @@
         <v>0</v>
       </c>
       <c r="L172" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M172" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="N172" s="19"/>
@@ -27791,15 +27791,15 @@
         <v>35</v>
       </c>
       <c r="G173" s="333">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>0</v>
       </c>
       <c r="H173" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="I173" s="336">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="J173" s="336">
@@ -27811,11 +27811,11 @@
         <v>0</v>
       </c>
       <c r="L173" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="M173" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="N173" s="19"/>
@@ -27856,31 +27856,31 @@
       </c>
       <c r="F174" s="119"/>
       <c r="G174" s="119">
-        <f t="shared" ref="G174:M174" si="147">SUM(G168:G173)</f>
+        <f t="shared" ref="G174:M174" si="148">SUM(G168:G173)</f>
         <v>113</v>
       </c>
       <c r="H174" s="119">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>114</v>
       </c>
       <c r="I174" s="119">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>111</v>
       </c>
       <c r="J174" s="120">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>4873.6900000000005</v>
       </c>
       <c r="K174" s="119">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>4787.43</v>
       </c>
       <c r="L174" s="119">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>506863.76000000007</v>
       </c>
       <c r="M174" s="119">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>11544</v>
       </c>
       <c r="N174" s="123">
@@ -27930,7 +27930,7 @@
         <v>38</v>
       </c>
       <c r="G175" s="221">
-        <f t="shared" ref="G175:G180" si="148">D175+E175*2</f>
+        <f t="shared" ref="G175:G180" si="149">D175+E175*2</f>
         <v>118</v>
       </c>
       <c r="H175" s="125">
@@ -27938,7 +27938,7 @@
         <v>120</v>
       </c>
       <c r="I175" s="222">
-        <f t="shared" ref="I175:I180" si="149">D175+E175</f>
+        <f t="shared" ref="I175:I180" si="150">D175+E175</f>
         <v>79</v>
       </c>
       <c r="J175" s="222">
@@ -27950,11 +27950,11 @@
         <v>3407.27</v>
       </c>
       <c r="L175" s="125">
-        <f t="shared" ref="L175:L180" si="150">J175*104</f>
+        <f t="shared" ref="L175:L180" si="151">J175*104</f>
         <v>529291.36</v>
       </c>
       <c r="M175" s="125">
-        <f t="shared" ref="M175:M180" si="151">I175*104</f>
+        <f t="shared" ref="M175:M180" si="152">I175*104</f>
         <v>8216</v>
       </c>
       <c r="N175" s="19"/>
@@ -27978,7 +27978,7 @@
       </c>
     </row>
     <row r="176" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="361" t="s">
+      <c r="A176" s="370" t="s">
         <v>188</v>
       </c>
       <c r="B176" s="295">
@@ -27999,15 +27999,15 @@
         <v>52</v>
       </c>
       <c r="G176" s="221">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>118</v>
       </c>
       <c r="H176" s="125">
-        <f t="shared" ref="H176:H180" si="152">B176+C176*2</f>
+        <f t="shared" ref="H176:H180" si="153">B176+C176*2</f>
         <v>120</v>
       </c>
       <c r="I176" s="125">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>78</v>
       </c>
       <c r="J176" s="125">
@@ -28019,11 +28019,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L176" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>529291.36</v>
       </c>
       <c r="M176" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>8112</v>
       </c>
       <c r="N176" s="19"/>
@@ -28048,7 +28048,7 @@
       <c r="Y176" s="172"/>
     </row>
     <row r="177" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A177" s="361"/>
+      <c r="A177" s="370"/>
       <c r="B177" s="295">
         <v>33</v>
       </c>
@@ -28067,15 +28067,15 @@
         <v>36</v>
       </c>
       <c r="G177" s="221">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>39</v>
       </c>
       <c r="H177" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>39</v>
       </c>
       <c r="I177" s="125">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>36</v>
       </c>
       <c r="J177" s="125">
@@ -28087,11 +28087,11 @@
         <v>1047.96</v>
       </c>
       <c r="L177" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>118070.16</v>
       </c>
       <c r="M177" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>3744</v>
       </c>
       <c r="N177" s="19"/>
@@ -28115,7 +28115,7 @@
       </c>
     </row>
     <row r="178" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="361"/>
+      <c r="A178" s="370"/>
       <c r="B178" s="295">
         <v>29</v>
       </c>
@@ -28134,15 +28134,15 @@
         <v>53</v>
       </c>
       <c r="G178" s="221">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>35</v>
       </c>
       <c r="H178" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>35</v>
       </c>
       <c r="I178" s="125">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>32</v>
       </c>
       <c r="J178" s="125">
@@ -28154,11 +28154,11 @@
         <v>931.52</v>
       </c>
       <c r="L178" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M178" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>3328</v>
       </c>
       <c r="N178" s="19"/>
@@ -28180,7 +28180,7 @@
       </c>
     </row>
     <row r="179" spans="1:30" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="361"/>
+      <c r="A179" s="370"/>
       <c r="B179" s="295">
         <v>0</v>
       </c>
@@ -28199,15 +28199,15 @@
         <v>122</v>
       </c>
       <c r="G179" s="221">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>0</v>
       </c>
       <c r="H179" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0</v>
       </c>
       <c r="I179" s="125">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0</v>
       </c>
       <c r="J179" s="223">
@@ -28219,11 +28219,11 @@
         <v>0</v>
       </c>
       <c r="L179" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>0</v>
       </c>
       <c r="M179" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>0</v>
       </c>
       <c r="N179" s="19"/>
@@ -28245,7 +28245,7 @@
       </c>
     </row>
     <row r="180" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="361"/>
+      <c r="A180" s="370"/>
       <c r="B180" s="295">
         <v>4</v>
       </c>
@@ -28264,15 +28264,15 @@
         <v>35</v>
       </c>
       <c r="G180" s="221">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>4</v>
       </c>
       <c r="H180" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>4</v>
       </c>
       <c r="I180" s="224">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>4</v>
       </c>
       <c r="J180" s="224">
@@ -28284,11 +28284,11 @@
         <v>101.6</v>
       </c>
       <c r="L180" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>10566.4</v>
       </c>
       <c r="M180" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>416</v>
       </c>
       <c r="N180" s="19"/>
@@ -28329,31 +28329,31 @@
       </c>
       <c r="F181" s="119"/>
       <c r="G181" s="119">
-        <f t="shared" ref="G181:M181" si="153">SUM(G175:G180)</f>
+        <f t="shared" ref="G181:M181" si="154">SUM(G175:G180)</f>
         <v>314</v>
       </c>
       <c r="H181" s="119">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>318</v>
       </c>
       <c r="I181" s="119">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>229</v>
       </c>
       <c r="J181" s="120">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>12434.420000000002</v>
       </c>
       <c r="K181" s="119">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>8852.49</v>
       </c>
       <c r="L181" s="119">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>1293179.6799999997</v>
       </c>
       <c r="M181" s="119">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>23816</v>
       </c>
       <c r="N181" s="123">
@@ -28404,7 +28404,7 @@
         <v>38</v>
       </c>
       <c r="G182" s="125">
-        <f t="shared" ref="G182:G187" si="154">D182+E182*2</f>
+        <f t="shared" ref="G182:G187" si="155">D182+E182*2</f>
         <v>120</v>
       </c>
       <c r="H182" s="125">
@@ -28412,7 +28412,7 @@
         <v>120</v>
       </c>
       <c r="I182" s="125">
-        <f t="shared" ref="I182:I187" si="155">D182+E182</f>
+        <f t="shared" ref="I182:I187" si="156">D182+E182</f>
         <v>79</v>
       </c>
       <c r="J182" s="125">
@@ -28424,11 +28424,11 @@
         <v>3407.27</v>
       </c>
       <c r="L182" s="125">
-        <f t="shared" ref="L182:L187" si="156">J182*104</f>
+        <f t="shared" ref="L182:L187" si="157">J182*104</f>
         <v>538262.4</v>
       </c>
       <c r="M182" s="125">
-        <f t="shared" ref="M182:M187" si="157">I182*104</f>
+        <f t="shared" ref="M182:M187" si="158">I182*104</f>
         <v>8216</v>
       </c>
       <c r="N182" s="19"/>
@@ -28476,15 +28476,15 @@
         <v>52</v>
       </c>
       <c r="G183" s="125">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>121</v>
       </c>
       <c r="H183" s="125">
-        <f t="shared" ref="H183:H187" si="158">B183+C183*2</f>
+        <f t="shared" ref="H183:H187" si="159">B183+C183*2</f>
         <v>120</v>
       </c>
       <c r="I183" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>79</v>
       </c>
       <c r="J183" s="125">
@@ -28496,11 +28496,11 @@
         <v>3407.27</v>
       </c>
       <c r="L183" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M183" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>8216</v>
       </c>
       <c r="N183" s="19"/>
@@ -28548,15 +28548,15 @@
         <v>36</v>
       </c>
       <c r="G184" s="125">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>39</v>
       </c>
       <c r="H184" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>39</v>
       </c>
       <c r="I184" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>36</v>
       </c>
       <c r="J184" s="125">
@@ -28568,11 +28568,11 @@
         <v>1047.96</v>
       </c>
       <c r="L184" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>118070.16</v>
       </c>
       <c r="M184" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>3744</v>
       </c>
       <c r="N184" s="19"/>
@@ -28617,15 +28617,15 @@
         <v>53</v>
       </c>
       <c r="G185" s="125">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>34</v>
       </c>
       <c r="H185" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>35</v>
       </c>
       <c r="I185" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>31</v>
       </c>
       <c r="J185" s="125">
@@ -28637,11 +28637,11 @@
         <v>902.41</v>
       </c>
       <c r="L185" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>102932.96</v>
       </c>
       <c r="M185" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>3224</v>
       </c>
       <c r="N185" s="19"/>
@@ -28682,15 +28682,15 @@
         <v>122</v>
       </c>
       <c r="G186" s="125">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0</v>
       </c>
       <c r="H186" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="I186" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="J186" s="125">
@@ -28702,11 +28702,11 @@
         <v>0</v>
       </c>
       <c r="L186" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="M186" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="N186" s="19"/>
@@ -28747,15 +28747,15 @@
         <v>35</v>
       </c>
       <c r="G187" s="125">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>4</v>
       </c>
       <c r="H187" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>4</v>
       </c>
       <c r="I187" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>4</v>
       </c>
       <c r="J187" s="125">
@@ -28767,11 +28767,11 @@
         <v>101.6</v>
       </c>
       <c r="L187" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>10566.4</v>
       </c>
       <c r="M187" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>416</v>
       </c>
       <c r="N187" s="19"/>
@@ -28812,31 +28812,31 @@
       </c>
       <c r="F188" s="119"/>
       <c r="G188" s="119">
-        <f t="shared" ref="G188:M188" si="159">SUM(G182:G187)</f>
+        <f t="shared" ref="G188:M188" si="160">SUM(G182:G187)</f>
         <v>318</v>
       </c>
       <c r="H188" s="119">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>318</v>
       </c>
       <c r="I188" s="119">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>229</v>
       </c>
       <c r="J188" s="120">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>12620.960000000003</v>
       </c>
       <c r="K188" s="119">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>8866.51</v>
       </c>
       <c r="L188" s="118">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>1312579.8399999999</v>
       </c>
       <c r="M188" s="151">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>23816</v>
       </c>
       <c r="N188" s="123">
@@ -28886,7 +28886,7 @@
         <v>38</v>
       </c>
       <c r="G189" s="221">
-        <f t="shared" ref="G189:G194" si="160">D189+E189*2</f>
+        <f t="shared" ref="G189:G194" si="161">D189+E189*2</f>
         <v>119</v>
       </c>
       <c r="H189" s="125">
@@ -28894,7 +28894,7 @@
         <v>120</v>
       </c>
       <c r="I189" s="222">
-        <f t="shared" ref="I189:I194" si="161">D189+E189</f>
+        <f t="shared" ref="I189:I194" si="162">D189+E189</f>
         <v>79</v>
       </c>
       <c r="J189" s="222">
@@ -28906,11 +28906,11 @@
         <v>3407.27</v>
       </c>
       <c r="L189" s="125">
-        <f t="shared" ref="L189:L194" si="162">J189*104</f>
+        <f t="shared" ref="L189:L194" si="163">J189*104</f>
         <v>533776.88</v>
       </c>
       <c r="M189" s="125">
-        <f t="shared" ref="M189:M194" si="163">I189*104</f>
+        <f t="shared" ref="M189:M194" si="164">I189*104</f>
         <v>8216</v>
       </c>
       <c r="N189" s="19"/>
@@ -28953,15 +28953,15 @@
         <v>52</v>
       </c>
       <c r="G190" s="221">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>119</v>
       </c>
       <c r="H190" s="125">
-        <f t="shared" ref="H190:H194" si="164">B190+C190*2</f>
+        <f t="shared" ref="H190:H194" si="165">B190+C190*2</f>
         <v>120</v>
       </c>
       <c r="I190" s="125">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>78</v>
       </c>
       <c r="J190" s="125">
@@ -28973,11 +28973,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L190" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>533776.88</v>
       </c>
       <c r="M190" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>8112</v>
       </c>
       <c r="N190" s="19"/>
@@ -29020,15 +29020,15 @@
         <v>36</v>
       </c>
       <c r="G191" s="221">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>39</v>
       </c>
       <c r="H191" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>39</v>
       </c>
       <c r="I191" s="125">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>36</v>
       </c>
       <c r="J191" s="125">
@@ -29040,11 +29040,11 @@
         <v>1047.96</v>
       </c>
       <c r="L191" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>118070.16</v>
       </c>
       <c r="M191" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>3744</v>
       </c>
       <c r="N191" s="19"/>
@@ -29087,15 +29087,15 @@
         <v>53</v>
       </c>
       <c r="G192" s="221">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>35</v>
       </c>
       <c r="H192" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>35</v>
       </c>
       <c r="I192" s="125">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>32</v>
       </c>
       <c r="J192" s="125">
@@ -29107,11 +29107,11 @@
         <v>931.52</v>
       </c>
       <c r="L192" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M192" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>3328</v>
       </c>
       <c r="N192" s="19"/>
@@ -29152,15 +29152,15 @@
         <v>122</v>
       </c>
       <c r="G193" s="221">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0</v>
       </c>
       <c r="H193" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0</v>
       </c>
       <c r="I193" s="125">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0</v>
       </c>
       <c r="J193" s="223">
@@ -29172,11 +29172,11 @@
         <v>0</v>
       </c>
       <c r="L193" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="M193" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="N193" s="19"/>
@@ -29217,15 +29217,15 @@
         <v>35</v>
       </c>
       <c r="G194" s="221">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>4</v>
       </c>
       <c r="H194" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>4</v>
       </c>
       <c r="I194" s="224">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>4</v>
       </c>
       <c r="J194" s="224">
@@ -29237,11 +29237,11 @@
         <v>101.6</v>
       </c>
       <c r="L194" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>10566.4</v>
       </c>
       <c r="M194" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>416</v>
       </c>
       <c r="N194" s="19"/>
@@ -29282,31 +29282,31 @@
       </c>
       <c r="F195" s="119"/>
       <c r="G195" s="119">
-        <f t="shared" ref="G195:M195" si="165">SUM(G189:G194)</f>
+        <f t="shared" ref="G195:M195" si="166">SUM(G189:G194)</f>
         <v>316</v>
       </c>
       <c r="H195" s="119">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>318</v>
       </c>
       <c r="I195" s="119">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>229</v>
       </c>
       <c r="J195" s="119">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>12520.68</v>
       </c>
       <c r="K195" s="119">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>8852.49</v>
       </c>
       <c r="L195" s="119">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>1302150.7199999997</v>
       </c>
       <c r="M195" s="119">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>23816</v>
       </c>
       <c r="N195" s="123">
@@ -29356,7 +29356,7 @@
         <v>38</v>
       </c>
       <c r="G196" s="221">
-        <f t="shared" ref="G196:G201" si="166">D196+E196*2</f>
+        <f t="shared" ref="G196:G201" si="167">D196+E196*2</f>
         <v>119</v>
       </c>
       <c r="H196" s="125">
@@ -29364,7 +29364,7 @@
         <v>120</v>
       </c>
       <c r="I196" s="222">
-        <f t="shared" ref="I196:I201" si="167">D196+E196</f>
+        <f t="shared" ref="I196:I201" si="168">D196+E196</f>
         <v>79</v>
       </c>
       <c r="J196" s="222">
@@ -29376,11 +29376,11 @@
         <v>3407.27</v>
       </c>
       <c r="L196" s="125">
-        <f t="shared" ref="L196:L201" si="168">J196*104</f>
+        <f t="shared" ref="L196:L201" si="169">J196*104</f>
         <v>533776.88</v>
       </c>
       <c r="M196" s="125">
-        <f t="shared" ref="M196:M201" si="169">I196*104</f>
+        <f t="shared" ref="M196:M201" si="170">I196*104</f>
         <v>8216</v>
       </c>
       <c r="N196" s="19"/>
@@ -29423,15 +29423,15 @@
         <v>52</v>
       </c>
       <c r="G197" s="221">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>119</v>
       </c>
       <c r="H197" s="125">
-        <f t="shared" ref="H197:H201" si="170">B197+C197*2</f>
+        <f t="shared" ref="H197:H201" si="171">B197+C197*2</f>
         <v>120</v>
       </c>
       <c r="I197" s="125">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>78</v>
       </c>
       <c r="J197" s="125">
@@ -29443,11 +29443,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L197" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>533776.88</v>
       </c>
       <c r="M197" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>8112</v>
       </c>
       <c r="N197" s="19"/>
@@ -29490,15 +29490,15 @@
         <v>36</v>
       </c>
       <c r="G198" s="221">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>39</v>
       </c>
       <c r="H198" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>39</v>
       </c>
       <c r="I198" s="125">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>36</v>
       </c>
       <c r="J198" s="125">
@@ -29510,11 +29510,11 @@
         <v>1047.96</v>
       </c>
       <c r="L198" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>118070.16</v>
       </c>
       <c r="M198" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>3744</v>
       </c>
       <c r="N198" s="19"/>
@@ -29559,15 +29559,15 @@
         <v>53</v>
       </c>
       <c r="G199" s="221">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>35</v>
       </c>
       <c r="H199" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>35</v>
       </c>
       <c r="I199" s="125">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>32</v>
       </c>
       <c r="J199" s="125">
@@ -29579,11 +29579,11 @@
         <v>931.52</v>
       </c>
       <c r="L199" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M199" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>3328</v>
       </c>
       <c r="N199" s="19"/>
@@ -29626,15 +29626,15 @@
         <v>122</v>
       </c>
       <c r="G200" s="221">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0</v>
       </c>
       <c r="H200" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>0</v>
       </c>
       <c r="I200" s="125">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="J200" s="223">
@@ -29646,11 +29646,11 @@
         <v>0</v>
       </c>
       <c r="L200" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0</v>
       </c>
       <c r="M200" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0</v>
       </c>
       <c r="N200" s="19"/>
@@ -29691,15 +29691,15 @@
         <v>35</v>
       </c>
       <c r="G201" s="221">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>4</v>
       </c>
       <c r="H201" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>4</v>
       </c>
       <c r="I201" s="224">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>4</v>
       </c>
       <c r="J201" s="224">
@@ -29711,11 +29711,11 @@
         <v>101.6</v>
       </c>
       <c r="L201" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>10566.4</v>
       </c>
       <c r="M201" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>416</v>
       </c>
       <c r="N201" s="19"/>
@@ -29756,31 +29756,31 @@
       </c>
       <c r="F202" s="119"/>
       <c r="G202" s="119">
-        <f t="shared" ref="G202:M202" si="171">SUM(G196:G201)</f>
+        <f t="shared" ref="G202:M202" si="172">SUM(G196:G201)</f>
         <v>316</v>
       </c>
       <c r="H202" s="119">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>318</v>
       </c>
       <c r="I202" s="119">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>229</v>
       </c>
       <c r="J202" s="119">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>12520.68</v>
       </c>
       <c r="K202" s="119">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>8852.49</v>
       </c>
       <c r="L202" s="119">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>1302150.7199999997</v>
       </c>
       <c r="M202" s="119">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>23816</v>
       </c>
       <c r="N202" s="123">
@@ -29830,7 +29830,7 @@
         <v>38</v>
       </c>
       <c r="G203" s="125">
-        <f t="shared" ref="G203:G208" si="172">D203+E203*2</f>
+        <f t="shared" ref="G203:G208" si="173">D203+E203*2</f>
         <v>119</v>
       </c>
       <c r="H203" s="125">
@@ -29838,7 +29838,7 @@
         <v>120</v>
       </c>
       <c r="I203" s="125">
-        <f t="shared" ref="I203:I208" si="173">D203+E203</f>
+        <f t="shared" ref="I203:I208" si="174">D203+E203</f>
         <v>79</v>
       </c>
       <c r="J203" s="125">
@@ -29850,11 +29850,11 @@
         <v>3407.27</v>
       </c>
       <c r="L203" s="125">
-        <f t="shared" ref="L203:L208" si="174">J203*104</f>
+        <f t="shared" ref="L203:L208" si="175">J203*104</f>
         <v>533776.88</v>
       </c>
       <c r="M203" s="125">
-        <f t="shared" ref="M203:M208" si="175">I203*104</f>
+        <f t="shared" ref="M203:M208" si="176">I203*104</f>
         <v>8216</v>
       </c>
       <c r="N203" s="19"/>
@@ -29897,15 +29897,15 @@
         <v>52</v>
       </c>
       <c r="G204" s="125">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>119</v>
       </c>
       <c r="H204" s="125">
-        <f t="shared" ref="H204:H208" si="176">B204+C204*2</f>
+        <f t="shared" ref="H204:H208" si="177">B204+C204*2</f>
         <v>120</v>
       </c>
       <c r="I204" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>78</v>
       </c>
       <c r="J204" s="125">
@@ -29917,11 +29917,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L204" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>533776.88</v>
       </c>
       <c r="M204" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>8112</v>
       </c>
       <c r="N204" s="19"/>
@@ -29964,15 +29964,15 @@
         <v>36</v>
       </c>
       <c r="G205" s="125">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>39</v>
       </c>
       <c r="H205" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>39</v>
       </c>
       <c r="I205" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>36</v>
       </c>
       <c r="J205" s="125">
@@ -29984,11 +29984,11 @@
         <v>1047.96</v>
       </c>
       <c r="L205" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>118070.16</v>
       </c>
       <c r="M205" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>3744</v>
       </c>
       <c r="N205" s="19"/>
@@ -30031,15 +30031,15 @@
         <v>53</v>
       </c>
       <c r="G206" s="125">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>35</v>
       </c>
       <c r="H206" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>35</v>
       </c>
       <c r="I206" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>32</v>
       </c>
       <c r="J206" s="125">
@@ -30051,11 +30051,11 @@
         <v>931.52</v>
       </c>
       <c r="L206" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M206" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>3328</v>
       </c>
       <c r="N206" s="165"/>
@@ -30096,15 +30096,15 @@
         <v>122</v>
       </c>
       <c r="G207" s="125">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0</v>
       </c>
       <c r="H207" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="I207" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="J207" s="125">
@@ -30116,11 +30116,11 @@
         <v>0</v>
       </c>
       <c r="L207" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="M207" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="N207" s="19"/>
@@ -30161,15 +30161,15 @@
         <v>35</v>
       </c>
       <c r="G208" s="125">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>4</v>
       </c>
       <c r="H208" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>4</v>
       </c>
       <c r="I208" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>4</v>
       </c>
       <c r="J208" s="125">
@@ -30181,11 +30181,11 @@
         <v>101.6</v>
       </c>
       <c r="L208" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>10566.4</v>
       </c>
       <c r="M208" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>416</v>
       </c>
       <c r="N208" s="19"/>
@@ -30226,27 +30226,27 @@
       </c>
       <c r="F209" s="119"/>
       <c r="G209" s="119">
-        <f t="shared" ref="G209:L209" si="177">SUM(G203:G208)</f>
+        <f t="shared" ref="G209:L209" si="178">SUM(G203:G208)</f>
         <v>316</v>
       </c>
       <c r="H209" s="119">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>318</v>
       </c>
       <c r="I209" s="119">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>229</v>
       </c>
       <c r="J209" s="119">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>12520.68</v>
       </c>
       <c r="K209" s="119">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>8852.49</v>
       </c>
       <c r="L209" s="119">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>1302150.7199999997</v>
       </c>
       <c r="M209" s="123">
@@ -30301,7 +30301,7 @@
         <v>38</v>
       </c>
       <c r="G210" s="321">
-        <f t="shared" ref="G210:G215" si="178">D210+E210*2</f>
+        <f t="shared" ref="G210:G215" si="179">D210+E210*2</f>
         <v>75</v>
       </c>
       <c r="H210" s="116">
@@ -30309,7 +30309,7 @@
         <v>75</v>
       </c>
       <c r="I210" s="322">
-        <f t="shared" ref="I210:I215" si="179">D210+E210</f>
+        <f t="shared" ref="I210:I215" si="180">D210+E210</f>
         <v>72</v>
       </c>
       <c r="J210" s="322">
@@ -30321,11 +30321,11 @@
         <v>3105.36</v>
       </c>
       <c r="L210" s="116">
-        <f t="shared" ref="L210:L215" si="180">J210*104</f>
+        <f t="shared" ref="L210:L215" si="181">J210*104</f>
         <v>336414</v>
       </c>
       <c r="M210" s="116">
-        <f t="shared" ref="M210:M215" si="181">I210*104</f>
+        <f t="shared" ref="M210:M215" si="182">I210*104</f>
         <v>7488</v>
       </c>
       <c r="N210" s="19"/>
@@ -30366,15 +30366,15 @@
         <v>52</v>
       </c>
       <c r="G211" s="321">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>76</v>
       </c>
       <c r="H211" s="116">
-        <f t="shared" ref="H211:H215" si="182">B211+C211*2</f>
+        <f t="shared" ref="H211:H215" si="183">B211+C211*2</f>
         <v>75</v>
       </c>
       <c r="I211" s="116">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>75</v>
       </c>
       <c r="J211" s="116">
@@ -30386,11 +30386,11 @@
         <v>3234.75</v>
       </c>
       <c r="L211" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>340899.52</v>
       </c>
       <c r="M211" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>7800</v>
       </c>
       <c r="N211" s="19"/>
@@ -30431,15 +30431,15 @@
         <v>36</v>
       </c>
       <c r="G212" s="321">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="H212" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="I212" s="116">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="J212" s="116">
@@ -30451,11 +30451,11 @@
         <v>0</v>
       </c>
       <c r="L212" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="M212" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="N212" s="19"/>
@@ -30496,15 +30496,15 @@
         <v>53</v>
       </c>
       <c r="G213" s="321">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="H213" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="I213" s="116">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="J213" s="116">
@@ -30516,11 +30516,11 @@
         <v>0</v>
       </c>
       <c r="L213" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="M213" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="N213" s="19"/>
@@ -30561,15 +30561,15 @@
         <v>122</v>
       </c>
       <c r="G214" s="321">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="H214" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="I214" s="116">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="J214" s="323">
@@ -30581,11 +30581,11 @@
         <v>0</v>
       </c>
       <c r="L214" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="M214" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="N214" s="19"/>
@@ -30626,15 +30626,15 @@
         <v>35</v>
       </c>
       <c r="G215" s="321">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="H215" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="I215" s="324">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="J215" s="324">
@@ -30646,11 +30646,11 @@
         <v>0</v>
       </c>
       <c r="L215" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="M215" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="N215" s="19"/>
@@ -30691,31 +30691,31 @@
       </c>
       <c r="F216" s="119"/>
       <c r="G216" s="119">
-        <f t="shared" ref="G216:M216" si="183">SUM(G210:G215)</f>
+        <f t="shared" ref="G216:M216" si="184">SUM(G210:G215)</f>
         <v>151</v>
       </c>
       <c r="H216" s="119">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>150</v>
       </c>
       <c r="I216" s="119">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>147</v>
       </c>
       <c r="J216" s="119">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6512.63</v>
       </c>
       <c r="K216" s="119">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L216" s="119">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>677313.52</v>
       </c>
       <c r="M216" s="119">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>15288</v>
       </c>
       <c r="N216" s="123">
@@ -30766,7 +30766,7 @@
         <v>38</v>
       </c>
       <c r="G217" s="218">
-        <f t="shared" ref="G217:G222" si="184">D217+E217*2</f>
+        <f t="shared" ref="G217:G222" si="185">D217+E217*2</f>
         <v>57</v>
       </c>
       <c r="H217" s="218">
@@ -30774,7 +30774,7 @@
         <v>57</v>
       </c>
       <c r="I217" s="218">
-        <f t="shared" ref="I217:I222" si="185">D217+E217</f>
+        <f t="shared" ref="I217:I222" si="186">D217+E217</f>
         <v>54</v>
       </c>
       <c r="J217" s="218">
@@ -30786,11 +30786,11 @@
         <v>2329.02</v>
       </c>
       <c r="L217" s="218">
-        <f t="shared" ref="L217:L222" si="186">J217*104</f>
+        <f t="shared" ref="L217:L222" si="187">J217*104</f>
         <v>255674.64000000004</v>
       </c>
       <c r="M217" s="218">
-        <f t="shared" ref="M217:M222" si="187">I217*104</f>
+        <f t="shared" ref="M217:M222" si="188">I217*104</f>
         <v>5616</v>
       </c>
       <c r="N217" s="19"/>
@@ -30832,15 +30832,15 @@
         <v>52</v>
       </c>
       <c r="G218" s="218">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>57</v>
       </c>
       <c r="H218" s="218">
-        <f t="shared" ref="H218:H222" si="188">B218+C218*2</f>
+        <f t="shared" ref="H218:H222" si="189">B218+C218*2</f>
         <v>57</v>
       </c>
       <c r="I218" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>57</v>
       </c>
       <c r="J218" s="218">
@@ -30852,11 +30852,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L218" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M218" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>5928</v>
       </c>
       <c r="N218" s="19"/>
@@ -30898,15 +30898,15 @@
         <v>36</v>
       </c>
       <c r="G219" s="218">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H219" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="I219" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="J219" s="218">
@@ -30918,11 +30918,11 @@
         <v>0</v>
       </c>
       <c r="L219" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="M219" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="N219" s="19"/>
@@ -30964,15 +30964,15 @@
         <v>53</v>
       </c>
       <c r="G220" s="218">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H220" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="I220" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="J220" s="218">
@@ -30984,11 +30984,11 @@
         <v>0</v>
       </c>
       <c r="L220" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="M220" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="N220" s="19"/>
@@ -31030,15 +31030,15 @@
         <v>122</v>
       </c>
       <c r="G221" s="218">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H221" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="I221" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="J221" s="218">
@@ -31050,11 +31050,11 @@
         <v>0</v>
       </c>
       <c r="L221" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="M221" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="N221" s="19"/>
@@ -31096,15 +31096,15 @@
         <v>35</v>
       </c>
       <c r="G222" s="218">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="H222" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="I222" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="J222" s="218">
@@ -31116,11 +31116,11 @@
         <v>0</v>
       </c>
       <c r="L222" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="M222" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="N222" s="19"/>
@@ -31162,27 +31162,27 @@
       </c>
       <c r="F223" s="119"/>
       <c r="G223" s="119">
-        <f t="shared" ref="G223:L223" si="189">SUM(G217:G222)</f>
+        <f t="shared" ref="G223:L223" si="190">SUM(G217:G222)</f>
         <v>114</v>
       </c>
       <c r="H223" s="119">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>114</v>
       </c>
       <c r="I223" s="119">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>111</v>
       </c>
       <c r="J223" s="119">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>4916.8200000000006</v>
       </c>
       <c r="K223" s="119">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>4787.43</v>
       </c>
       <c r="L223" s="119">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>511349.28000000009</v>
       </c>
       <c r="M223" s="123">
@@ -31218,38 +31218,38 @@
     <row r="224" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="225" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225"/>
-      <c r="B225" s="353" t="s">
+      <c r="B225" s="367" t="s">
         <v>56</v>
       </c>
-      <c r="C225" s="354"/>
-      <c r="D225" s="354"/>
-      <c r="E225" s="354"/>
-      <c r="F225" s="354"/>
-      <c r="G225" s="355"/>
+      <c r="C225" s="368"/>
+      <c r="D225" s="368"/>
+      <c r="E225" s="368"/>
+      <c r="F225" s="368"/>
+      <c r="G225" s="369"/>
       <c r="H225" s="290"/>
-      <c r="I225" s="353" t="s">
+      <c r="I225" s="367" t="s">
         <v>57</v>
       </c>
-      <c r="J225" s="354"/>
-      <c r="K225" s="354"/>
-      <c r="L225" s="354"/>
-      <c r="M225" s="354"/>
-      <c r="N225" s="355"/>
-      <c r="P225" s="374" t="s">
+      <c r="J225" s="368"/>
+      <c r="K225" s="368"/>
+      <c r="L225" s="368"/>
+      <c r="M225" s="368"/>
+      <c r="N225" s="369"/>
+      <c r="P225" s="362" t="s">
         <v>139</v>
       </c>
-      <c r="Q225" s="374"/>
-      <c r="R225" s="374"/>
-      <c r="S225" s="375"/>
-      <c r="T225" s="371" t="s">
+      <c r="Q225" s="362"/>
+      <c r="R225" s="362"/>
+      <c r="S225" s="363"/>
+      <c r="T225" s="359" t="s">
         <v>142</v>
       </c>
-      <c r="U225" s="372"/>
-      <c r="V225" s="373"/>
-      <c r="W225" s="363" t="s">
+      <c r="U225" s="360"/>
+      <c r="V225" s="361"/>
+      <c r="W225" s="350" t="s">
         <v>143</v>
       </c>
-      <c r="X225" s="363" t="s">
+      <c r="X225" s="350" t="s">
         <v>162</v>
       </c>
     </row>
@@ -31315,23 +31315,23 @@
       <c r="V226" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W226" s="364"/>
-      <c r="X226" s="364"/>
+      <c r="W226" s="351"/>
+      <c r="X226" s="351"/>
     </row>
     <row r="227" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B227" s="114">
-        <f>B5+B12+B19+B26+B33+B40+B47+B56+B63+B70+B77+B84+B91+B98+B105+B112+B119+B126+B133+B140+B147+B154+B161+B168+B175+B182+B189+B196+B203+B210+B217</f>
+        <f t="shared" ref="B227:C229" si="191">B5+B12+B19+B26+B33+B40+B47+B56+B63+B70+B77+B84+B91+B98+B105+B112+B119+B126+B133+B140+B147+B154+B161+B168+B175+B182+B189+B196+B203+B210+B217</f>
         <v>1410</v>
       </c>
       <c r="C227" s="114">
-        <f>C5+C12+C19+C26+C33+C40+C47+C56+C63+C70+C77+C84+C91+C98+C105+C112+C119+C126+C133+C140+C147+C154+C161+C168+C175+C182+C189+C196+C203+C210+C217</f>
+        <f t="shared" si="191"/>
         <v>829</v>
       </c>
       <c r="D227" s="114">
-        <f t="shared" ref="D227:D232" si="190">B227+C227</f>
+        <f t="shared" ref="D227:D232" si="192">B227+C227</f>
         <v>2239</v>
       </c>
       <c r="E227" s="139">
@@ -31343,20 +31343,20 @@
         <v>132322.84000000003</v>
       </c>
       <c r="G227" s="139">
-        <f t="shared" ref="G227:G232" si="191">F227*104</f>
+        <f t="shared" ref="G227:G232" si="193">F227*104</f>
         <v>13761575.360000003</v>
       </c>
       <c r="H227" s="139"/>
       <c r="I227" s="114">
-        <f>D5+D12+D26+D33+D40+D47+D56+D63+D70+D77+D84+D91+D98+D105+D112+D119+D126+D133+D140+D147+D154+D161+D168+D175+D182+D189+D196+D203+D210+D217+D19</f>
+        <f t="shared" ref="I227:J230" si="194">D5+D12+D26+D33+D40+D47+D56+D63+D70+D77+D84+D91+D98+D105+D112+D119+D126+D133+D140+D147+D154+D161+D168+D175+D182+D189+D196+D203+D210+D217+D19</f>
         <v>1409</v>
       </c>
       <c r="J227" s="114">
-        <f>E5+E12+E26+E33+E40+E47+E56+E63+E70+E77+E84+E91+E98+E105+E112+E119+E126+E133+E140+E147+E154+E161+E168+E175+E182+E189+E196+E203+E210+E217+E19</f>
+        <f t="shared" si="194"/>
         <v>822</v>
       </c>
       <c r="K227" s="114">
-        <f t="shared" ref="K227:K232" si="192">I227+J227</f>
+        <f t="shared" ref="K227:K232" si="195">I227+J227</f>
         <v>2231</v>
       </c>
       <c r="L227" s="139">
@@ -31368,7 +31368,7 @@
         <v>131675.89000000001</v>
       </c>
       <c r="N227" s="139">
-        <f t="shared" ref="N227:N232" si="193">M227*104</f>
+        <f t="shared" ref="N227:N232" si="196">M227*104</f>
         <v>13694292.560000002</v>
       </c>
       <c r="O227" s="124"/>
@@ -31414,15 +31414,15 @@
         <v>52</v>
       </c>
       <c r="B228" s="114">
-        <f>B6+B13+B20+B27+B34+B41+B48+B57+B64+B71+B78+B85+B92+B99+B106+B113+B120+B127+B134+B141+B148+B155+B162+B169+B176+B183+B190+B197+B204+B211+B218</f>
+        <f t="shared" si="191"/>
         <v>1444</v>
       </c>
       <c r="C228" s="114">
-        <f>C6+C13+C20+C27+C34+C41+C48+C57+C64+C71+C78+C85+C92+C99+C106+C113+C120+C127+C134+C141+C148+C155+C162+C169+C176+C183+C190+C197+C204+C211+C218</f>
+        <f t="shared" si="191"/>
         <v>812</v>
       </c>
       <c r="D228" s="114">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>2256</v>
       </c>
       <c r="E228" s="139">
@@ -31434,24 +31434,24 @@
         <v>132322.84000000003</v>
       </c>
       <c r="G228" s="139">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>13761575.360000003</v>
       </c>
       <c r="H228" s="139"/>
       <c r="I228" s="114">
-        <f>D6+D13+D27+D34+D41+D48+D57+D64+D71+D78+D85+D92+D99+D106+D113+D120+D127+D134+D141+D148+D155+D162+D169+D176+D183+D190+D197+D204+D211+D218+D20</f>
+        <f t="shared" si="194"/>
         <v>1437</v>
       </c>
       <c r="J228" s="114">
-        <f>E6+E13+E27+E34+E41+E48+E57+E64+E71+E78+E85+E92+E99+E106+E113+E120+E127+E134+E141+E148+E155+E162+E169+E176+E183+E190+E197+E204+E211+E218+E20</f>
+        <f t="shared" si="194"/>
         <v>810</v>
       </c>
       <c r="K228" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>2247</v>
       </c>
       <c r="L228" s="139">
-        <f t="shared" ref="L228" si="194">K228*43.13</f>
+        <f t="shared" ref="L228" si="197">K228*43.13</f>
         <v>96913.11</v>
       </c>
       <c r="M228" s="139">
@@ -31459,7 +31459,7 @@
         <v>131848.41</v>
       </c>
       <c r="N228" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="196"/>
         <v>13712234.640000001</v>
       </c>
       <c r="O228" s="124"/>
@@ -31471,15 +31471,15 @@
         <v>36</v>
       </c>
       <c r="B229" s="114">
-        <f>B7+B14+B21+B28+B35+B42+B49+B58+B65+B72+B79+B86+B93+B100+B107+B114+B121+B128+B135+B142+B149+B156+B163+B170+B177+B184+B191+B198+B205+B212+B219</f>
+        <f t="shared" si="191"/>
         <v>627</v>
       </c>
       <c r="C229" s="114">
-        <f>C7+C14+C21+C28+C35+C42+C49+C58+C65+C72+C79+C86+C93+C100+C107+C114+C121+C128+C135+C142+C149+C156+C163+C170+C177+C184+C191+C198+C205+C212+C219</f>
+        <f t="shared" si="191"/>
         <v>57</v>
       </c>
       <c r="D229" s="114">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>684</v>
       </c>
       <c r="E229" s="139">
@@ -31491,20 +31491,20 @@
         <v>21570.510000000002</v>
       </c>
       <c r="G229" s="139">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>2243333.04</v>
       </c>
       <c r="H229" s="139"/>
       <c r="I229" s="114">
-        <f>D7+D14+D28+D35+D42+D49+D58+D65+D72+D79+D86+D93+D100+D107+D114+D121+D128+D135+D142+D149+D156+D163+D170+D177+D184+D191+D198+D205+D212+D219+D21</f>
+        <f t="shared" si="194"/>
         <v>626</v>
       </c>
       <c r="J229" s="114">
-        <f>E7+E14+E28+E35+E42+E49+E58+E65+E72+E79+E86+E93+E100+E107+E114+E121+E128+E135+E142+E149+E156+E163+E170+E177+E184+E191+E198+E205+E212+E219+E21</f>
+        <f t="shared" si="194"/>
         <v>44</v>
       </c>
       <c r="K229" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>670</v>
       </c>
       <c r="L229" s="139">
@@ -31516,7 +31516,7 @@
         <v>20784.54</v>
       </c>
       <c r="N229" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="196"/>
         <v>2161592.16</v>
       </c>
       <c r="O229" s="124"/>
@@ -31535,7 +31535,7 @@
         <v>57</v>
       </c>
       <c r="D230" s="114">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>608</v>
       </c>
       <c r="E230" s="139">
@@ -31547,20 +31547,20 @@
         <v>19358.150000000001</v>
       </c>
       <c r="G230" s="139">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>2013247.6</v>
       </c>
       <c r="H230" s="139"/>
       <c r="I230" s="114">
-        <f>D8+D15+D29+D36+D43+D50+D59+D66+D73+D80+D87+D94+D101+D108+D115+D122+D129+D136+D143+D150+D157+D164+D171+D178+D185+D192+D199+D206+D213+D220+D22</f>
+        <f t="shared" si="194"/>
         <v>554</v>
       </c>
       <c r="J230" s="114">
-        <f>E8+E15+E29+E36+E43+E50+E59+E66+E73+E80+E87+E94+E101+E108+E115+E122+E129+E136+E143+E150+E157+E164+E171+E178+E185+E192+E199+E206+E213+E220+E22</f>
+        <f t="shared" si="194"/>
         <v>44</v>
       </c>
       <c r="K230" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>598</v>
       </c>
       <c r="L230" s="139">
@@ -31572,7 +31572,7 @@
         <v>18688.62</v>
       </c>
       <c r="N230" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="196"/>
         <v>1943616.48</v>
       </c>
       <c r="O230" s="124"/>
@@ -31594,7 +31594,7 @@
         <v>0</v>
       </c>
       <c r="D231" s="114">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="E231" s="139">
@@ -31606,7 +31606,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="139">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="H231" s="139"/>
@@ -31619,7 +31619,7 @@
         <v>0</v>
       </c>
       <c r="K231" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>1</v>
       </c>
       <c r="L231" s="139">
@@ -31631,7 +31631,7 @@
         <v>25.4</v>
       </c>
       <c r="N231" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="196"/>
         <v>2641.6</v>
       </c>
       <c r="O231" s="124"/>
@@ -31650,7 +31650,7 @@
         <v>0</v>
       </c>
       <c r="D232" s="114">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>76</v>
       </c>
       <c r="E232" s="139">
@@ -31662,7 +31662,7 @@
         <v>1930.3999999999999</v>
       </c>
       <c r="G232" s="139">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>200761.59999999998</v>
       </c>
       <c r="H232" s="139"/>
@@ -31675,7 +31675,7 @@
         <v>0</v>
       </c>
       <c r="K232" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="195"/>
         <v>76</v>
       </c>
       <c r="L232" s="139">
@@ -31687,7 +31687,7 @@
         <v>1930.3999999999999</v>
       </c>
       <c r="N232" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="196"/>
         <v>200761.59999999998</v>
       </c>
       <c r="O232" s="124"/>
@@ -31826,10 +31826,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="351" t="s">
+      <c r="B237" s="375" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="352"/>
+      <c r="C237" s="376"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -32012,16 +32012,14 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="X225:X226"/>
-    <mergeCell ref="W225:W226"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T225:V225"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="P225:S225"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B225:G225"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="M3:M4"/>
@@ -32035,14 +32033,16 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B225:G225"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="X225:X226"/>
+    <mergeCell ref="W225:W226"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T225:V225"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="P225:S225"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:D31 D47:D54">
     <cfRule type="expression" dxfId="32" priority="28">
@@ -32231,130 +32231,130 @@
   <sheetData>
     <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="376">
+      <c r="D1" s="377">
         <v>46143</v>
       </c>
-      <c r="E1" s="376"/>
-      <c r="F1" s="376">
+      <c r="E1" s="377"/>
+      <c r="F1" s="377">
         <v>46144</v>
       </c>
-      <c r="G1" s="376"/>
-      <c r="H1" s="376">
+      <c r="G1" s="377"/>
+      <c r="H1" s="377">
         <v>46145</v>
       </c>
-      <c r="I1" s="376"/>
-      <c r="J1" s="376">
+      <c r="I1" s="377"/>
+      <c r="J1" s="377">
         <v>46146</v>
       </c>
-      <c r="K1" s="376"/>
-      <c r="L1" s="376">
+      <c r="K1" s="377"/>
+      <c r="L1" s="377">
         <v>46147</v>
       </c>
-      <c r="M1" s="376"/>
-      <c r="N1" s="376">
+      <c r="M1" s="377"/>
+      <c r="N1" s="377">
         <v>46148</v>
       </c>
-      <c r="O1" s="376"/>
-      <c r="P1" s="376">
+      <c r="O1" s="377"/>
+      <c r="P1" s="377">
         <v>46149</v>
       </c>
-      <c r="Q1" s="376"/>
-      <c r="R1" s="376">
+      <c r="Q1" s="377"/>
+      <c r="R1" s="377">
         <v>46150</v>
       </c>
-      <c r="S1" s="376"/>
-      <c r="T1" s="376">
+      <c r="S1" s="377"/>
+      <c r="T1" s="377">
         <v>46151</v>
       </c>
-      <c r="U1" s="376"/>
-      <c r="V1" s="376">
+      <c r="U1" s="377"/>
+      <c r="V1" s="377">
         <v>46152</v>
       </c>
-      <c r="W1" s="376"/>
-      <c r="X1" s="376">
+      <c r="W1" s="377"/>
+      <c r="X1" s="377">
         <v>46153</v>
       </c>
-      <c r="Y1" s="376"/>
-      <c r="Z1" s="376">
+      <c r="Y1" s="377"/>
+      <c r="Z1" s="377">
         <v>46154</v>
       </c>
-      <c r="AA1" s="376"/>
-      <c r="AB1" s="376">
+      <c r="AA1" s="377"/>
+      <c r="AB1" s="377">
         <v>46155</v>
       </c>
-      <c r="AC1" s="376"/>
-      <c r="AD1" s="376">
+      <c r="AC1" s="377"/>
+      <c r="AD1" s="377">
         <v>46156</v>
       </c>
-      <c r="AE1" s="376"/>
-      <c r="AF1" s="376">
+      <c r="AE1" s="377"/>
+      <c r="AF1" s="377">
         <v>46157</v>
       </c>
-      <c r="AG1" s="376"/>
-      <c r="AH1" s="376">
+      <c r="AG1" s="377"/>
+      <c r="AH1" s="377">
         <v>46158</v>
       </c>
-      <c r="AI1" s="376"/>
-      <c r="AJ1" s="376">
+      <c r="AI1" s="377"/>
+      <c r="AJ1" s="377">
         <v>46159</v>
       </c>
-      <c r="AK1" s="376"/>
-      <c r="AL1" s="376">
+      <c r="AK1" s="377"/>
+      <c r="AL1" s="377">
         <v>46160</v>
       </c>
-      <c r="AM1" s="376"/>
-      <c r="AN1" s="376">
+      <c r="AM1" s="377"/>
+      <c r="AN1" s="377">
         <v>46161</v>
       </c>
-      <c r="AO1" s="376"/>
-      <c r="AP1" s="376">
+      <c r="AO1" s="377"/>
+      <c r="AP1" s="377">
         <v>46162</v>
       </c>
-      <c r="AQ1" s="376"/>
-      <c r="AR1" s="376">
+      <c r="AQ1" s="377"/>
+      <c r="AR1" s="377">
         <v>46163</v>
       </c>
-      <c r="AS1" s="376"/>
-      <c r="AT1" s="376">
+      <c r="AS1" s="377"/>
+      <c r="AT1" s="377">
         <v>46164</v>
       </c>
-      <c r="AU1" s="376"/>
-      <c r="AV1" s="376">
+      <c r="AU1" s="377"/>
+      <c r="AV1" s="377">
         <v>46165</v>
       </c>
-      <c r="AW1" s="376"/>
-      <c r="AX1" s="376">
+      <c r="AW1" s="377"/>
+      <c r="AX1" s="377">
         <v>46166</v>
       </c>
-      <c r="AY1" s="376"/>
-      <c r="AZ1" s="376">
+      <c r="AY1" s="377"/>
+      <c r="AZ1" s="377">
         <v>46167</v>
       </c>
-      <c r="BA1" s="376"/>
-      <c r="BB1" s="376">
+      <c r="BA1" s="377"/>
+      <c r="BB1" s="377">
         <v>46168</v>
       </c>
-      <c r="BC1" s="376"/>
-      <c r="BD1" s="376">
+      <c r="BC1" s="377"/>
+      <c r="BD1" s="377">
         <v>46169</v>
       </c>
-      <c r="BE1" s="376"/>
-      <c r="BF1" s="376">
+      <c r="BE1" s="377"/>
+      <c r="BF1" s="377">
         <v>46170</v>
       </c>
-      <c r="BG1" s="376"/>
-      <c r="BH1" s="376">
+      <c r="BG1" s="377"/>
+      <c r="BH1" s="377">
         <v>46171</v>
       </c>
-      <c r="BI1" s="376"/>
-      <c r="BJ1" s="376">
+      <c r="BI1" s="377"/>
+      <c r="BJ1" s="377">
         <v>46172</v>
       </c>
-      <c r="BK1" s="376"/>
-      <c r="BL1" s="376">
+      <c r="BK1" s="377"/>
+      <c r="BL1" s="377">
         <v>46173</v>
       </c>
-      <c r="BM1" s="376"/>
+      <c r="BM1" s="377"/>
     </row>
     <row r="2" spans="1:65" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -38298,10 +38298,10 @@
       </c>
     </row>
     <row r="37" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A37" s="377" t="s">
+      <c r="A37" s="378" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="377"/>
+      <c r="B37" s="378"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="19">SUM(D31:D36)</f>
@@ -41245,6 +41245,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BL1:BM1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
@@ -41261,22 +41277,6 @@
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45080,19 +45080,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="378" t="s">
+      <c r="A2" s="379" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="379"/>
-      <c r="C2" s="379"/>
-      <c r="D2" s="379"/>
-      <c r="E2" s="379"/>
-      <c r="F2" s="379"/>
-      <c r="G2" s="379"/>
-      <c r="H2" s="379"/>
-      <c r="I2" s="379"/>
-      <c r="J2" s="379"/>
-      <c r="K2" s="379"/>
+      <c r="B2" s="380"/>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
+      <c r="F2" s="380"/>
+      <c r="G2" s="380"/>
+      <c r="H2" s="380"/>
+      <c r="I2" s="380"/>
+      <c r="J2" s="380"/>
+      <c r="K2" s="380"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -46719,8 +46719,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="380"/>
-      <c r="H16" s="380"/>
+      <c r="G16" s="390"/>
+      <c r="H16" s="390"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -46735,8 +46735,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="380"/>
-      <c r="H17" s="380"/>
+      <c r="G17" s="390"/>
+      <c r="H17" s="390"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -46751,8 +46751,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="380"/>
-      <c r="H18" s="380"/>
+      <c r="G18" s="390"/>
+      <c r="H18" s="390"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -46766,8 +46766,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="380"/>
-      <c r="H19" s="380"/>
+      <c r="G19" s="390"/>
+      <c r="H19" s="390"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -46781,8 +46781,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="380"/>
-      <c r="H20" s="380"/>
+      <c r="G20" s="390"/>
+      <c r="H20" s="390"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -46796,8 +46796,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="380"/>
-      <c r="H21" s="380"/>
+      <c r="G21" s="390"/>
+      <c r="H21" s="390"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -47087,17 +47087,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -47105,28 +47105,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -47373,28 +47351,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F53AD24-439F-44F1-8272-A2184D6C79E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47412,4 +47391,25 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Mayo 2026.xlsx
+++ b/data/umr/Resumen UMR Mayo 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDA9E0C3-5DE0-41CA-946C-AF271AD42DF0}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C3AA43E-C44D-4BB3-AA5F-DECD82765385}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4841,6 +4841,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4854,9 +4896,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4883,45 +4922,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4934,6 +4934,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4961,9 +4964,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -16261,14 +16261,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="373" t="s">
+      <c r="B2" s="350" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="373"/>
-      <c r="D2" s="374" t="s">
+      <c r="C2" s="350"/>
+      <c r="D2" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="374"/>
+      <c r="E2" s="351"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -16359,59 +16359,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="373" t="s">
+      <c r="B3" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="373"/>
-      <c r="D3" s="374" t="s">
+      <c r="C3" s="350"/>
+      <c r="D3" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="374"/>
-      <c r="F3" s="366" t="s">
+      <c r="E3" s="351"/>
+      <c r="F3" s="357" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="366" t="s">
+      <c r="G3" s="357" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="366" t="s">
+      <c r="H3" s="357" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="366" t="s">
+      <c r="I3" s="357" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="366" t="s">
+      <c r="J3" s="357" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="366" t="s">
+      <c r="K3" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="366" t="s">
+      <c r="L3" s="357" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="366" t="s">
+      <c r="M3" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="355" t="s">
+      <c r="N3" s="361" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="355" t="s">
+      <c r="O3" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="354"/>
-      <c r="Q3" s="356" t="s">
+      <c r="P3" s="368"/>
+      <c r="Q3" s="369" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="357"/>
-      <c r="S3" s="358"/>
-      <c r="T3" s="359" t="s">
+      <c r="R3" s="370"/>
+      <c r="S3" s="371"/>
+      <c r="T3" s="372" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="360"/>
-      <c r="V3" s="361"/>
-      <c r="W3" s="352" t="s">
+      <c r="U3" s="373"/>
+      <c r="V3" s="374"/>
+      <c r="W3" s="366" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="352" t="s">
+      <c r="X3" s="366" t="s">
         <v>162</v>
       </c>
     </row>
@@ -16429,17 +16429,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="366"/>
-      <c r="G4" s="372"/>
-      <c r="H4" s="372"/>
-      <c r="I4" s="366"/>
-      <c r="J4" s="366"/>
-      <c r="K4" s="366"/>
-      <c r="L4" s="366"/>
-      <c r="M4" s="366"/>
-      <c r="N4" s="355"/>
-      <c r="O4" s="355"/>
-      <c r="P4" s="354"/>
+      <c r="F4" s="357"/>
+      <c r="G4" s="358"/>
+      <c r="H4" s="358"/>
+      <c r="I4" s="357"/>
+      <c r="J4" s="357"/>
+      <c r="K4" s="357"/>
+      <c r="L4" s="357"/>
+      <c r="M4" s="357"/>
+      <c r="N4" s="361"/>
+      <c r="O4" s="361"/>
+      <c r="P4" s="368"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -16458,8 +16458,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="353"/>
-      <c r="X4" s="353"/>
+      <c r="W4" s="367"/>
+      <c r="X4" s="367"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -17927,7 +17927,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="365" t="s">
+      <c r="A27" s="360" t="s">
         <v>183</v>
       </c>
       <c r="B27" s="295">
@@ -17996,7 +17996,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="365"/>
+      <c r="A28" s="360"/>
       <c r="B28" s="295">
         <v>33</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="365"/>
+      <c r="A29" s="360"/>
       <c r="B29" s="295">
         <v>29</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="365"/>
+      <c r="A30" s="360"/>
       <c r="B30" s="295">
         <v>0</v>
       </c>
@@ -18192,7 +18192,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="365"/>
+      <c r="A31" s="360"/>
       <c r="B31" s="295">
         <v>4</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="364" t="s">
+      <c r="A41" s="359" t="s">
         <v>184</v>
       </c>
       <c r="B41" s="295">
@@ -18936,7 +18936,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="364"/>
+      <c r="A42" s="359"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -19010,7 +19010,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="364"/>
+      <c r="A43" s="359"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -19082,7 +19082,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="364"/>
+      <c r="A44" s="359"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -19154,7 +19154,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="364"/>
+      <c r="A45" s="359"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="AF47" s="255"/>
     </row>
     <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="365" t="s">
+      <c r="A48" s="360" t="s">
         <v>185</v>
       </c>
       <c r="B48" s="295">
@@ -19448,7 +19448,7 @@
       </c>
     </row>
     <row r="49" spans="1:65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="365"/>
+      <c r="A49" s="360"/>
       <c r="B49" s="295">
         <v>33</v>
       </c>
@@ -19504,8 +19504,8 @@
       <c r="U49" s="189"/>
       <c r="V49" s="189"/>
       <c r="W49" s="182">
-        <f>J49-(Q49*($M$1-$K$1))-24.13-17.73</f>
-        <v>707.58</v>
+        <f>J49-(Q49*($M$1-$K$1))</f>
+        <v>749.44</v>
       </c>
       <c r="X49" s="182">
         <f>H49*$M$1</f>
@@ -19513,7 +19513,7 @@
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A50" s="365"/>
+      <c r="A50" s="360"/>
       <c r="B50" s="295">
         <v>29</v>
       </c>
@@ -19576,7 +19576,7 @@
       </c>
     </row>
     <row r="51" spans="1:65" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="365"/>
+      <c r="A51" s="360"/>
       <c r="B51" s="295">
         <v>0</v>
       </c>
@@ -19640,7 +19640,7 @@
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A52" s="365"/>
+      <c r="A52" s="360"/>
       <c r="B52" s="295">
         <v>4</v>
       </c>
@@ -19832,31 +19832,31 @@
       </c>
       <c r="F55" s="119"/>
       <c r="G55" s="119">
-        <f t="shared" ref="G55:M55" si="46">SUM(G47:G52)</f>
-        <v>287</v>
+        <f>SUM(G47:G54)</f>
+        <v>289</v>
       </c>
       <c r="H55" s="119">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="H55:I55" si="46">SUM(H47:H54)</f>
         <v>318</v>
       </c>
       <c r="I55" s="119">
         <f t="shared" si="46"/>
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J55" s="120">
         <f>SUM(J47:J54)</f>
         <v>11548</v>
       </c>
       <c r="K55" s="119">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="G55:M55" si="47">SUM(K47:K52)</f>
         <v>7534.4400000000005</v>
       </c>
       <c r="L55" s="118">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1199388.3200000003</v>
       </c>
       <c r="M55" s="151">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>20072</v>
       </c>
       <c r="N55" s="123">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="O55" s="21">
         <f>(W55/N55)*100</f>
-        <v>92.9366145278847</v>
+        <v>93.279420194906237</v>
       </c>
       <c r="P55" s="192"/>
       <c r="Q55" s="181"/>
@@ -19876,7 +19876,7 @@
       <c r="V55" s="181"/>
       <c r="W55" s="193">
         <f>SUM(W47:W54)</f>
-        <v>11348.49</v>
+        <v>11390.35</v>
       </c>
       <c r="X55" s="193">
         <f>SUM(X47:X52)</f>
@@ -19906,7 +19906,7 @@
         <v>38</v>
       </c>
       <c r="G56" s="125">
-        <f t="shared" ref="G56:G61" si="47">D56+E56*2</f>
+        <f t="shared" ref="G56:G61" si="48">D56+E56*2</f>
         <v>120</v>
       </c>
       <c r="H56" s="125">
@@ -19926,11 +19926,11 @@
         <v>3407.27</v>
       </c>
       <c r="L56" s="125">
-        <f t="shared" ref="L56:L61" si="48">J56*104</f>
+        <f t="shared" ref="L56:L61" si="49">J56*104</f>
         <v>538262.4</v>
       </c>
       <c r="M56" s="125">
-        <f t="shared" ref="M56:M61" si="49">I56*104</f>
+        <f t="shared" ref="M56:M61" si="50">I56*104</f>
         <v>8216</v>
       </c>
       <c r="N56" s="19"/>
@@ -19973,15 +19973,15 @@
         <v>52</v>
       </c>
       <c r="G57" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>120</v>
       </c>
       <c r="H57" s="125">
-        <f t="shared" ref="H57:H61" si="50">B57+C57*2</f>
+        <f t="shared" ref="H57:H61" si="51">B57+C57*2</f>
         <v>120</v>
       </c>
       <c r="I57" s="125">
-        <f t="shared" ref="I57:I61" si="51">D57+E57</f>
+        <f t="shared" ref="I57:I61" si="52">D57+E57</f>
         <v>78</v>
       </c>
       <c r="J57" s="125">
@@ -19993,11 +19993,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L57" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>538262.4</v>
       </c>
       <c r="M57" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>8112</v>
       </c>
       <c r="N57" s="19"/>
@@ -20040,15 +20040,15 @@
         <v>36</v>
       </c>
       <c r="G58" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>38</v>
       </c>
       <c r="H58" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>39</v>
       </c>
       <c r="I58" s="125">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>36</v>
       </c>
       <c r="J58" s="125">
@@ -20060,11 +20060,11 @@
         <v>1047.96</v>
       </c>
       <c r="L58" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>115042.72</v>
       </c>
       <c r="M58" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>3744</v>
       </c>
       <c r="N58" s="19"/>
@@ -20107,15 +20107,15 @@
         <v>53</v>
       </c>
       <c r="G59" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>34</v>
       </c>
       <c r="H59" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>35</v>
       </c>
       <c r="I59" s="125">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>32</v>
       </c>
       <c r="J59" s="125">
@@ -20127,11 +20127,11 @@
         <v>931.52</v>
       </c>
       <c r="L59" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>102932.96</v>
       </c>
       <c r="M59" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>3328</v>
       </c>
       <c r="N59" s="19"/>
@@ -20175,15 +20175,15 @@
         <v>122</v>
       </c>
       <c r="G60" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="H60" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I60" s="125">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="J60" s="125">
@@ -20195,11 +20195,11 @@
         <v>0</v>
       </c>
       <c r="L60" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M60" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="N60" s="19"/>
@@ -20240,15 +20240,15 @@
         <v>35</v>
       </c>
       <c r="G61" s="125">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>4</v>
       </c>
       <c r="H61" s="125">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>4</v>
       </c>
       <c r="I61" s="125">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4</v>
       </c>
       <c r="J61" s="125">
@@ -20260,11 +20260,11 @@
         <v>101.6</v>
       </c>
       <c r="L61" s="125">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>10566.4</v>
       </c>
       <c r="M61" s="125">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>416</v>
       </c>
       <c r="N61" s="19"/>
@@ -20305,31 +20305,31 @@
       </c>
       <c r="F62" s="119"/>
       <c r="G62" s="119">
-        <f t="shared" ref="G62:M62" si="52">SUM(G56:G61)</f>
+        <f t="shared" ref="G62:M62" si="53">SUM(G56:G61)</f>
         <v>316</v>
       </c>
       <c r="H62" s="119">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>318</v>
       </c>
       <c r="I62" s="119">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>229</v>
       </c>
       <c r="J62" s="120">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K62" s="119">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>8852.49</v>
       </c>
       <c r="L62" s="118">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M62" s="151">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>23816</v>
       </c>
       <c r="N62" s="123">
@@ -20379,7 +20379,7 @@
         <v>38</v>
       </c>
       <c r="G63" s="116">
-        <f t="shared" ref="G63:G68" si="53">D63+E63*2</f>
+        <f t="shared" ref="G63:G68" si="54">D63+E63*2</f>
         <v>75</v>
       </c>
       <c r="H63" s="116">
@@ -20387,7 +20387,7 @@
         <v>75</v>
       </c>
       <c r="I63" s="116">
-        <f t="shared" ref="I63:I68" si="54">D63+E63</f>
+        <f t="shared" ref="I63:I68" si="55">D63+E63</f>
         <v>72</v>
       </c>
       <c r="J63" s="116">
@@ -20399,11 +20399,11 @@
         <v>3105.36</v>
       </c>
       <c r="L63" s="116">
-        <f t="shared" ref="L63:L68" si="55">J63*104</f>
+        <f t="shared" ref="L63:L68" si="56">J63*104</f>
         <v>336414</v>
       </c>
       <c r="M63" s="116">
-        <f t="shared" ref="M63:M68" si="56">I63*104</f>
+        <f t="shared" ref="M63:M68" si="57">I63*104</f>
         <v>7488</v>
       </c>
       <c r="N63" s="19"/>
@@ -20444,15 +20444,15 @@
         <v>52</v>
       </c>
       <c r="G64" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>75</v>
       </c>
       <c r="H64" s="116">
-        <f t="shared" ref="H64:H68" si="57">B64+C64*2</f>
+        <f t="shared" ref="H64:H68" si="58">B64+C64*2</f>
         <v>75</v>
       </c>
       <c r="I64" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>75</v>
       </c>
       <c r="J64" s="116">
@@ -20464,11 +20464,11 @@
         <v>3234.75</v>
       </c>
       <c r="L64" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>336414</v>
       </c>
       <c r="M64" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>7800</v>
       </c>
       <c r="N64" s="19"/>
@@ -20512,15 +20512,15 @@
         <v>36</v>
       </c>
       <c r="G65" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="H65" s="116">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="I65" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="J65" s="116">
@@ -20532,11 +20532,11 @@
         <v>0</v>
       </c>
       <c r="L65" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M65" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="N65" s="19"/>
@@ -20578,15 +20578,15 @@
         <v>53</v>
       </c>
       <c r="G66" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="H66" s="116">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="I66" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="J66" s="116">
@@ -20598,11 +20598,11 @@
         <v>0</v>
       </c>
       <c r="L66" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M66" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="N66" s="165"/>
@@ -20643,15 +20643,15 @@
         <v>122</v>
       </c>
       <c r="G67" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="H67" s="116">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="I67" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="J67" s="116">
@@ -20663,11 +20663,11 @@
         <v>0</v>
       </c>
       <c r="L67" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M67" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="N67" s="165"/>
@@ -20708,15 +20708,15 @@
         <v>35</v>
       </c>
       <c r="G68" s="116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="H68" s="116">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="I68" s="116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="J68" s="116">
@@ -20728,11 +20728,11 @@
         <v>0</v>
       </c>
       <c r="L68" s="116">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M68" s="116">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="N68" s="19"/>
@@ -20773,31 +20773,31 @@
       </c>
       <c r="F69" s="119"/>
       <c r="G69" s="119">
-        <f t="shared" ref="G69:M69" si="58">SUM(G63:G68)</f>
+        <f t="shared" ref="G69:M69" si="59">SUM(G63:G68)</f>
         <v>150</v>
       </c>
       <c r="H69" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>150</v>
       </c>
       <c r="I69" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>147</v>
       </c>
       <c r="J69" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6469.5</v>
       </c>
       <c r="K69" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L69" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>672828</v>
       </c>
       <c r="M69" s="119">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>15288</v>
       </c>
       <c r="N69" s="123">
@@ -20848,7 +20848,7 @@
         <v>38</v>
       </c>
       <c r="G70" s="218">
-        <f t="shared" ref="G70:G77" si="59">D70+E70*2</f>
+        <f t="shared" ref="G70:G77" si="60">D70+E70*2</f>
         <v>57</v>
       </c>
       <c r="H70" s="218">
@@ -20856,7 +20856,7 @@
         <v>57</v>
       </c>
       <c r="I70" s="218">
-        <f t="shared" ref="I70:I75" si="60">D70+E70</f>
+        <f t="shared" ref="I70:I75" si="61">D70+E70</f>
         <v>54</v>
       </c>
       <c r="J70" s="218">
@@ -20868,11 +20868,11 @@
         <v>2329.02</v>
       </c>
       <c r="L70" s="218">
-        <f t="shared" ref="L70:L75" si="61">J70*104</f>
+        <f t="shared" ref="L70:L75" si="62">J70*104</f>
         <v>255674.64000000004</v>
       </c>
       <c r="M70" s="218">
-        <f t="shared" ref="M70:M75" si="62">I70*104</f>
+        <f t="shared" ref="M70:M75" si="63">I70*104</f>
         <v>5616</v>
       </c>
       <c r="N70" s="19"/>
@@ -20913,15 +20913,15 @@
         <v>52</v>
       </c>
       <c r="G71" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>57</v>
       </c>
       <c r="H71" s="218">
-        <f t="shared" ref="H71:H75" si="63">B71+C71*2</f>
+        <f t="shared" ref="H71:H75" si="64">B71+C71*2</f>
         <v>57</v>
       </c>
       <c r="I71" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>57</v>
       </c>
       <c r="J71" s="218">
@@ -20933,11 +20933,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L71" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M71" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5928</v>
       </c>
       <c r="N71" s="19"/>
@@ -20978,15 +20978,15 @@
         <v>36</v>
       </c>
       <c r="G72" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="H72" s="218">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I72" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="J72" s="218">
@@ -20998,11 +20998,11 @@
         <v>0</v>
       </c>
       <c r="L72" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="M72" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="N72" s="19"/>
@@ -21043,15 +21043,15 @@
         <v>53</v>
       </c>
       <c r="G73" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="H73" s="218">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I73" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="J73" s="218">
@@ -21063,11 +21063,11 @@
         <v>0</v>
       </c>
       <c r="L73" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="M73" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="N73" s="19"/>
@@ -21108,15 +21108,15 @@
         <v>122</v>
       </c>
       <c r="G74" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="H74" s="218">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I74" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="J74" s="218">
@@ -21128,11 +21128,11 @@
         <v>0</v>
       </c>
       <c r="L74" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="M74" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="N74" s="19"/>
@@ -21173,15 +21173,15 @@
         <v>35</v>
       </c>
       <c r="G75" s="218">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="H75" s="218">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="I75" s="218">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="J75" s="218">
@@ -21193,11 +21193,11 @@
         <v>0</v>
       </c>
       <c r="L75" s="218">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="M75" s="218">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="N75" s="19"/>
@@ -21241,31 +21241,31 @@
       </c>
       <c r="F76" s="119"/>
       <c r="G76" s="119">
-        <f t="shared" ref="G76:M76" si="64">SUM(G70:G75)</f>
+        <f t="shared" ref="G76:M76" si="65">SUM(G70:G75)</f>
         <v>114</v>
       </c>
       <c r="H76" s="119">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>114</v>
       </c>
       <c r="I76" s="119">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>111</v>
       </c>
       <c r="J76" s="119">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>4916.8200000000006</v>
       </c>
       <c r="K76" s="119">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>4787.43</v>
       </c>
       <c r="L76" s="119">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>511349.28000000009</v>
       </c>
       <c r="M76" s="119">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>11544</v>
       </c>
       <c r="N76" s="180">
@@ -21318,7 +21318,7 @@
         <v>38</v>
       </c>
       <c r="G77" s="125">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>121</v>
       </c>
       <c r="H77" s="125">
@@ -21326,7 +21326,7 @@
         <v>120</v>
       </c>
       <c r="I77" s="125">
-        <f t="shared" ref="I77:I82" si="65">D77+E77</f>
+        <f t="shared" ref="I77:I82" si="66">D77+E77</f>
         <v>79</v>
       </c>
       <c r="J77" s="125">
@@ -21338,11 +21338,11 @@
         <v>3407.27</v>
       </c>
       <c r="L77" s="125">
-        <f t="shared" ref="L77:L82" si="66">J77*104</f>
+        <f t="shared" ref="L77:L82" si="67">J77*104</f>
         <v>542747.92000000004</v>
       </c>
       <c r="M77" s="125">
-        <f t="shared" ref="M77:M82" si="67">I77*104</f>
+        <f t="shared" ref="M77:M82" si="68">I77*104</f>
         <v>8216</v>
       </c>
       <c r="N77" s="19"/>
@@ -21388,15 +21388,15 @@
         <v>52</v>
       </c>
       <c r="G78" s="125">
-        <f t="shared" ref="G78:G82" si="68">D78+E78*2</f>
+        <f t="shared" ref="G78:G82" si="69">D78+E78*2</f>
         <v>121</v>
       </c>
       <c r="H78" s="125">
-        <f t="shared" ref="H78:H82" si="69">B78+C78*2</f>
+        <f t="shared" ref="H78:H82" si="70">B78+C78*2</f>
         <v>120</v>
       </c>
       <c r="I78" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>78</v>
       </c>
       <c r="J78" s="125">
@@ -21408,11 +21408,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L78" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M78" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>8112</v>
       </c>
       <c r="N78" s="19"/>
@@ -21458,15 +21458,15 @@
         <v>36</v>
       </c>
       <c r="G79" s="125">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>38</v>
       </c>
       <c r="H79" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>39</v>
       </c>
       <c r="I79" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>36</v>
       </c>
       <c r="J79" s="125">
@@ -21478,11 +21478,11 @@
         <v>1047.96</v>
       </c>
       <c r="L79" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>115042.72</v>
       </c>
       <c r="M79" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3744</v>
       </c>
       <c r="N79" s="19"/>
@@ -21530,15 +21530,15 @@
         <v>53</v>
       </c>
       <c r="G80" s="125">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>34</v>
       </c>
       <c r="H80" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>35</v>
       </c>
       <c r="I80" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>32</v>
       </c>
       <c r="J80" s="125">
@@ -21550,11 +21550,11 @@
         <v>931.52</v>
       </c>
       <c r="L80" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>102932.96</v>
       </c>
       <c r="M80" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>3328</v>
       </c>
       <c r="N80" s="19"/>
@@ -21600,15 +21600,15 @@
         <v>122</v>
       </c>
       <c r="G81" s="125">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="H81" s="125">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="I81" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="J81" s="125">
@@ -21620,11 +21620,11 @@
         <v>0</v>
       </c>
       <c r="L81" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="M81" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="N81" s="19"/>
@@ -21668,15 +21668,15 @@
         <v>35</v>
       </c>
       <c r="G82" s="125">
-        <f t="shared" si="68"/>
-        <v>4</v>
-      </c>
-      <c r="H82" s="125">
         <f t="shared" si="69"/>
         <v>4</v>
       </c>
+      <c r="H82" s="125">
+        <f t="shared" si="70"/>
+        <v>4</v>
+      </c>
       <c r="I82" s="125">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>4</v>
       </c>
       <c r="J82" s="125">
@@ -21688,11 +21688,11 @@
         <v>101.6</v>
       </c>
       <c r="L82" s="125">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>10566.4</v>
       </c>
       <c r="M82" s="125">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>416</v>
       </c>
       <c r="N82" s="19"/>
@@ -21736,31 +21736,31 @@
       </c>
       <c r="F83" s="119"/>
       <c r="G83" s="119">
-        <f t="shared" ref="G83:M83" si="70">SUM(G77:G82)</f>
+        <f t="shared" ref="G83:M83" si="71">SUM(G77:G82)</f>
         <v>318</v>
       </c>
       <c r="H83" s="119">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>318</v>
       </c>
       <c r="I83" s="119">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>229</v>
       </c>
       <c r="J83" s="120">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>12634.980000000001</v>
       </c>
       <c r="K83" s="119">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>8852.49</v>
       </c>
       <c r="L83" s="118">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>1314037.92</v>
       </c>
       <c r="M83" s="151">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>23816</v>
       </c>
       <c r="N83" s="123">
@@ -21814,7 +21814,7 @@
         <v>38</v>
       </c>
       <c r="G84" s="125">
-        <f t="shared" ref="G84:G89" si="71">D84+E84*2</f>
+        <f t="shared" ref="G84:G89" si="72">D84+E84*2</f>
         <v>120</v>
       </c>
       <c r="H84" s="125">
@@ -21822,7 +21822,7 @@
         <v>120</v>
       </c>
       <c r="I84" s="125">
-        <f t="shared" ref="I84:I89" si="72">D84+E84</f>
+        <f t="shared" ref="I84:I89" si="73">D84+E84</f>
         <v>79</v>
       </c>
       <c r="J84" s="125">
@@ -21834,11 +21834,11 @@
         <v>3407.27</v>
       </c>
       <c r="L84" s="125">
-        <f t="shared" ref="L84:L89" si="73">J84*104</f>
+        <f t="shared" ref="L84:L89" si="74">J84*104</f>
         <v>538262.4</v>
       </c>
       <c r="M84" s="125">
-        <f t="shared" ref="M84:M89" si="74">I84*104</f>
+        <f t="shared" ref="M84:M89" si="75">I84*104</f>
         <v>8216</v>
       </c>
       <c r="N84" s="19"/>
@@ -21884,15 +21884,15 @@
         <v>52</v>
       </c>
       <c r="G85" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>120</v>
       </c>
       <c r="H85" s="125">
-        <f t="shared" ref="H85:H89" si="75">B85+C85*2</f>
+        <f t="shared" ref="H85:H89" si="76">B85+C85*2</f>
         <v>120</v>
       </c>
       <c r="I85" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>78</v>
       </c>
       <c r="J85" s="125">
@@ -21904,11 +21904,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L85" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>538262.4</v>
       </c>
       <c r="M85" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>8112</v>
       </c>
       <c r="N85" s="19"/>
@@ -21954,15 +21954,15 @@
         <v>36</v>
       </c>
       <c r="G86" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>38</v>
       </c>
       <c r="H86" s="125">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>39</v>
       </c>
       <c r="I86" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>36</v>
       </c>
       <c r="J86" s="125">
@@ -21974,11 +21974,11 @@
         <v>1047.96</v>
       </c>
       <c r="L86" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>115042.72</v>
       </c>
       <c r="M86" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3744</v>
       </c>
       <c r="N86" s="19"/>
@@ -22024,15 +22024,15 @@
         <v>53</v>
       </c>
       <c r="G87" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>34</v>
       </c>
       <c r="H87" s="125">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>35</v>
       </c>
       <c r="I87" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>32</v>
       </c>
       <c r="J87" s="125">
@@ -22044,11 +22044,11 @@
         <v>931.52</v>
       </c>
       <c r="L87" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>102932.96</v>
       </c>
       <c r="M87" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>3328</v>
       </c>
       <c r="N87" s="19"/>
@@ -22092,15 +22092,15 @@
         <v>122</v>
       </c>
       <c r="G88" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="H88" s="125">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="I88" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="J88" s="125">
@@ -22112,11 +22112,11 @@
         <v>0</v>
       </c>
       <c r="L88" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="M88" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="N88" s="19"/>
@@ -22160,15 +22160,15 @@
         <v>35</v>
       </c>
       <c r="G89" s="125">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>4</v>
       </c>
       <c r="H89" s="125">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>4</v>
       </c>
       <c r="I89" s="125">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>4</v>
       </c>
       <c r="J89" s="125">
@@ -22180,11 +22180,11 @@
         <v>101.6</v>
       </c>
       <c r="L89" s="125">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>10566.4</v>
       </c>
       <c r="M89" s="125">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>416</v>
       </c>
       <c r="N89" s="19"/>
@@ -22225,31 +22225,31 @@
       </c>
       <c r="F90" s="119"/>
       <c r="G90" s="119">
-        <f t="shared" ref="G90:M90" si="76">SUM(G84:G89)</f>
+        <f t="shared" ref="G90:M90" si="77">SUM(G84:G89)</f>
         <v>316</v>
       </c>
       <c r="H90" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>318</v>
       </c>
       <c r="I90" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>229</v>
       </c>
       <c r="J90" s="120">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K90" s="119">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>8852.49</v>
       </c>
       <c r="L90" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M90" s="151">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>23816</v>
       </c>
       <c r="N90" s="123">
@@ -22300,7 +22300,7 @@
         <v>38</v>
       </c>
       <c r="G91" s="125">
-        <f t="shared" ref="G91:G96" si="77">D91+E91*2</f>
+        <f t="shared" ref="G91:G96" si="78">D91+E91*2</f>
         <v>120</v>
       </c>
       <c r="H91" s="125">
@@ -22308,7 +22308,7 @@
         <v>120</v>
       </c>
       <c r="I91" s="125">
-        <f t="shared" ref="I91:I96" si="78">D91+E91</f>
+        <f t="shared" ref="I91:I96" si="79">D91+E91</f>
         <v>79</v>
       </c>
       <c r="J91" s="125">
@@ -22320,11 +22320,11 @@
         <v>3407.27</v>
       </c>
       <c r="L91" s="125">
-        <f t="shared" ref="L91:L96" si="79">J91*104</f>
+        <f t="shared" ref="L91:L96" si="80">J91*104</f>
         <v>538262.4</v>
       </c>
       <c r="M91" s="125">
-        <f t="shared" ref="M91:M96" si="80">I91*104</f>
+        <f t="shared" ref="M91:M96" si="81">I91*104</f>
         <v>8216</v>
       </c>
       <c r="N91" s="19"/>
@@ -22367,15 +22367,15 @@
         <v>52</v>
       </c>
       <c r="G92" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>120</v>
       </c>
       <c r="H92" s="125">
-        <f t="shared" ref="H92:H96" si="81">B92+C92*2</f>
+        <f t="shared" ref="H92:H96" si="82">B92+C92*2</f>
         <v>120</v>
       </c>
       <c r="I92" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>78</v>
       </c>
       <c r="J92" s="125">
@@ -22387,11 +22387,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L92" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>538262.4</v>
       </c>
       <c r="M92" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>8112</v>
       </c>
       <c r="N92" s="19"/>
@@ -22434,15 +22434,15 @@
         <v>36</v>
       </c>
       <c r="G93" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>38</v>
       </c>
       <c r="H93" s="125">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>39</v>
       </c>
       <c r="I93" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>36</v>
       </c>
       <c r="J93" s="125">
@@ -22454,11 +22454,11 @@
         <v>1047.96</v>
       </c>
       <c r="L93" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>115042.72</v>
       </c>
       <c r="M93" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3744</v>
       </c>
       <c r="N93" s="19"/>
@@ -22501,15 +22501,15 @@
         <v>53</v>
       </c>
       <c r="G94" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>34</v>
       </c>
       <c r="H94" s="125">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>35</v>
       </c>
       <c r="I94" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>32</v>
       </c>
       <c r="J94" s="125">
@@ -22521,11 +22521,11 @@
         <v>931.52</v>
       </c>
       <c r="L94" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>102932.96</v>
       </c>
       <c r="M94" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>3328</v>
       </c>
       <c r="N94" s="19"/>
@@ -22566,15 +22566,15 @@
         <v>122</v>
       </c>
       <c r="G95" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="H95" s="125">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="I95" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="J95" s="125">
@@ -22586,11 +22586,11 @@
         <v>0</v>
       </c>
       <c r="L95" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="M95" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="N95" s="19"/>
@@ -22631,15 +22631,15 @@
         <v>35</v>
       </c>
       <c r="G96" s="125">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>4</v>
       </c>
       <c r="H96" s="125">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>4</v>
       </c>
       <c r="I96" s="125">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>4</v>
       </c>
       <c r="J96" s="125">
@@ -22651,11 +22651,11 @@
         <v>101.6</v>
       </c>
       <c r="L96" s="125">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>10566.4</v>
       </c>
       <c r="M96" s="125">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>416</v>
       </c>
       <c r="N96" s="19"/>
@@ -22696,31 +22696,31 @@
       </c>
       <c r="F97" s="119"/>
       <c r="G97" s="119">
-        <f t="shared" ref="G97:M97" si="82">SUM(G91:G96)</f>
+        <f t="shared" ref="G97:M97" si="83">SUM(G91:G96)</f>
         <v>316</v>
       </c>
       <c r="H97" s="119">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>318</v>
       </c>
       <c r="I97" s="119">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>229</v>
       </c>
       <c r="J97" s="120">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K97" s="119">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>8852.49</v>
       </c>
       <c r="L97" s="118">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M97" s="151">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>23816</v>
       </c>
       <c r="N97" s="123">
@@ -22770,7 +22770,7 @@
         <v>38</v>
       </c>
       <c r="G98" s="125">
-        <f t="shared" ref="G98:G103" si="83">D98+E98*2</f>
+        <f t="shared" ref="G98:G103" si="84">D98+E98*2</f>
         <v>121</v>
       </c>
       <c r="H98" s="125">
@@ -22790,11 +22790,11 @@
         <v>3407.27</v>
       </c>
       <c r="L98" s="125">
-        <f t="shared" ref="L98:L103" si="84">J98*104</f>
+        <f t="shared" ref="L98:L103" si="85">J98*104</f>
         <v>542747.92000000004</v>
       </c>
       <c r="M98" s="125">
-        <f t="shared" ref="M98:M103" si="85">I98*104</f>
+        <f t="shared" ref="M98:M103" si="86">I98*104</f>
         <v>8216</v>
       </c>
       <c r="N98" s="19"/>
@@ -22837,15 +22837,15 @@
         <v>52</v>
       </c>
       <c r="G99" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>121</v>
       </c>
       <c r="H99" s="125">
-        <f t="shared" ref="H99:H103" si="86">B99+C99*2</f>
+        <f t="shared" ref="H99:H103" si="87">B99+C99*2</f>
         <v>120</v>
       </c>
       <c r="I99" s="125">
-        <f t="shared" ref="I99:I103" si="87">D99+E99</f>
+        <f t="shared" ref="I99:I103" si="88">D99+E99</f>
         <v>78</v>
       </c>
       <c r="J99" s="125">
@@ -22857,11 +22857,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L99" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M99" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>8112</v>
       </c>
       <c r="N99" s="19"/>
@@ -22904,15 +22904,15 @@
         <v>36</v>
       </c>
       <c r="G100" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>38</v>
       </c>
       <c r="H100" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>39</v>
       </c>
       <c r="I100" s="125">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>36</v>
       </c>
       <c r="J100" s="125">
@@ -22924,11 +22924,11 @@
         <v>1047.96</v>
       </c>
       <c r="L100" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>115042.72</v>
       </c>
       <c r="M100" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3744</v>
       </c>
       <c r="N100" s="19"/>
@@ -22971,15 +22971,15 @@
         <v>53</v>
       </c>
       <c r="G101" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>34</v>
       </c>
       <c r="H101" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>35</v>
       </c>
       <c r="I101" s="125">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>32</v>
       </c>
       <c r="J101" s="125">
@@ -22991,11 +22991,11 @@
         <v>931.52</v>
       </c>
       <c r="L101" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>102932.96</v>
       </c>
       <c r="M101" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>3328</v>
       </c>
       <c r="N101" s="19"/>
@@ -23036,15 +23036,15 @@
         <v>122</v>
       </c>
       <c r="G102" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="H102" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="I102" s="125">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="J102" s="125">
@@ -23056,11 +23056,11 @@
         <v>0</v>
       </c>
       <c r="L102" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="M102" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="N102" s="19"/>
@@ -23101,15 +23101,15 @@
         <v>35</v>
       </c>
       <c r="G103" s="125">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>4</v>
       </c>
       <c r="H103" s="125">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>4</v>
       </c>
       <c r="I103" s="125">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>4</v>
       </c>
       <c r="J103" s="125">
@@ -23121,11 +23121,11 @@
         <v>101.6</v>
       </c>
       <c r="L103" s="125">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>10566.4</v>
       </c>
       <c r="M103" s="125">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>416</v>
       </c>
       <c r="N103" s="19"/>
@@ -23166,31 +23166,31 @@
       </c>
       <c r="F104" s="119"/>
       <c r="G104" s="119">
-        <f t="shared" ref="G104:M104" si="88">SUM(G98:G103)</f>
+        <f t="shared" ref="G104:M104" si="89">SUM(G98:G103)</f>
         <v>318</v>
       </c>
       <c r="H104" s="119">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>318</v>
       </c>
       <c r="I104" s="119">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>229</v>
       </c>
       <c r="J104" s="120">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>12634.980000000001</v>
       </c>
       <c r="K104" s="119">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>8852.49</v>
       </c>
       <c r="L104" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1314037.92</v>
       </c>
       <c r="M104" s="151">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>23816</v>
       </c>
       <c r="N104" s="123">
@@ -23242,7 +23242,7 @@
         <v>38</v>
       </c>
       <c r="G105" s="125">
-        <f t="shared" ref="G105:G110" si="89">D105+E105*2</f>
+        <f t="shared" ref="G105:G110" si="90">D105+E105*2</f>
         <v>121</v>
       </c>
       <c r="H105" s="125">
@@ -23250,7 +23250,7 @@
         <v>120</v>
       </c>
       <c r="I105" s="125">
-        <f t="shared" ref="I105:I110" si="90">D105+E105</f>
+        <f t="shared" ref="I105:I110" si="91">D105+E105</f>
         <v>79</v>
       </c>
       <c r="J105" s="125">
@@ -23262,11 +23262,11 @@
         <v>3407.27</v>
       </c>
       <c r="L105" s="125">
-        <f t="shared" ref="L105:L110" si="91">J105*104</f>
+        <f t="shared" ref="L105:L110" si="92">J105*104</f>
         <v>542747.92000000004</v>
       </c>
       <c r="M105" s="125">
-        <f t="shared" ref="M105:M110" si="92">I105*104</f>
+        <f t="shared" ref="M105:M110" si="93">I105*104</f>
         <v>8216</v>
       </c>
       <c r="N105" s="19"/>
@@ -23309,15 +23309,15 @@
         <v>52</v>
       </c>
       <c r="G106" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>121</v>
       </c>
       <c r="H106" s="125">
-        <f t="shared" ref="H106:H110" si="93">B106+C106*2</f>
+        <f t="shared" ref="H106:H110" si="94">B106+C106*2</f>
         <v>120</v>
       </c>
       <c r="I106" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>78</v>
       </c>
       <c r="J106" s="125">
@@ -23329,11 +23329,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L106" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M106" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>8112</v>
       </c>
       <c r="N106" s="19"/>
@@ -23376,15 +23376,15 @@
         <v>36</v>
       </c>
       <c r="G107" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>38</v>
       </c>
       <c r="H107" s="125">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>39</v>
       </c>
       <c r="I107" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>36</v>
       </c>
       <c r="J107" s="125">
@@ -23396,11 +23396,11 @@
         <v>1047.96</v>
       </c>
       <c r="L107" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>115042.72</v>
       </c>
       <c r="M107" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3744</v>
       </c>
       <c r="N107" s="19"/>
@@ -23443,15 +23443,15 @@
         <v>53</v>
       </c>
       <c r="G108" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>34</v>
       </c>
       <c r="H108" s="125">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>35</v>
       </c>
       <c r="I108" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>32</v>
       </c>
       <c r="J108" s="125">
@@ -23463,11 +23463,11 @@
         <v>931.52</v>
       </c>
       <c r="L108" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>102932.96</v>
       </c>
       <c r="M108" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3328</v>
       </c>
       <c r="N108" s="19"/>
@@ -23508,15 +23508,15 @@
         <v>122</v>
       </c>
       <c r="G109" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="H109" s="125">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="I109" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="J109" s="125">
@@ -23528,11 +23528,11 @@
         <v>0</v>
       </c>
       <c r="L109" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="M109" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="N109" s="19"/>
@@ -23573,15 +23573,15 @@
         <v>35</v>
       </c>
       <c r="G110" s="125">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>4</v>
       </c>
       <c r="H110" s="125">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>4</v>
       </c>
       <c r="I110" s="125">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>4</v>
       </c>
       <c r="J110" s="125">
@@ -23593,11 +23593,11 @@
         <v>101.6</v>
       </c>
       <c r="L110" s="125">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>10566.4</v>
       </c>
       <c r="M110" s="125">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>416</v>
       </c>
       <c r="N110" s="19"/>
@@ -23638,31 +23638,31 @@
       </c>
       <c r="F111" s="119"/>
       <c r="G111" s="119">
-        <f t="shared" ref="G111:M111" si="94">SUM(G105:G110)</f>
+        <f t="shared" ref="G111:M111" si="95">SUM(G105:G110)</f>
         <v>318</v>
       </c>
       <c r="H111" s="119">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>318</v>
       </c>
       <c r="I111" s="119">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>229</v>
       </c>
       <c r="J111" s="120">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>12634.980000000001</v>
       </c>
       <c r="K111" s="119">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>8852.49</v>
       </c>
       <c r="L111" s="118">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>1314037.92</v>
       </c>
       <c r="M111" s="151">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>23816</v>
       </c>
       <c r="N111" s="123">
@@ -23712,7 +23712,7 @@
         <v>38</v>
       </c>
       <c r="G112" s="321">
-        <f t="shared" ref="G112:G117" si="95">D112+E112*2</f>
+        <f t="shared" ref="G112:G117" si="96">D112+E112*2</f>
         <v>75</v>
       </c>
       <c r="H112" s="116">
@@ -23720,7 +23720,7 @@
         <v>75</v>
       </c>
       <c r="I112" s="322">
-        <f t="shared" ref="I112:I117" si="96">D112+E112</f>
+        <f t="shared" ref="I112:I117" si="97">D112+E112</f>
         <v>72</v>
       </c>
       <c r="J112" s="322">
@@ -23732,11 +23732,11 @@
         <v>3105.36</v>
       </c>
       <c r="L112" s="116">
-        <f t="shared" ref="L112:L117" si="97">J112*104</f>
+        <f t="shared" ref="L112:L117" si="98">J112*104</f>
         <v>336414</v>
       </c>
       <c r="M112" s="116">
-        <f t="shared" ref="M112:M117" si="98">I112*104</f>
+        <f t="shared" ref="M112:M117" si="99">I112*104</f>
         <v>7488</v>
       </c>
       <c r="N112" s="19"/>
@@ -23777,15 +23777,15 @@
         <v>52</v>
       </c>
       <c r="G113" s="321">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>75</v>
       </c>
       <c r="H113" s="116">
-        <f t="shared" ref="H113:H117" si="99">B113+C113*2</f>
+        <f t="shared" ref="H113:H117" si="100">B113+C113*2</f>
         <v>75</v>
       </c>
       <c r="I113" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>75</v>
       </c>
       <c r="J113" s="116">
@@ -23797,11 +23797,11 @@
         <v>3234.75</v>
       </c>
       <c r="L113" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>336414</v>
       </c>
       <c r="M113" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>7800</v>
       </c>
       <c r="N113" s="19"/>
@@ -23843,15 +23843,15 @@
         <v>36</v>
       </c>
       <c r="G114" s="321">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="H114" s="116">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="I114" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="J114" s="116">
@@ -23863,11 +23863,11 @@
         <v>0</v>
       </c>
       <c r="L114" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="M114" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="N114" s="19"/>
@@ -23908,15 +23908,15 @@
         <v>53</v>
       </c>
       <c r="G115" s="321">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="H115" s="116">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="I115" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="J115" s="116">
@@ -23928,11 +23928,11 @@
         <v>0</v>
       </c>
       <c r="L115" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="M115" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="N115" s="19"/>
@@ -23973,15 +23973,15 @@
         <v>122</v>
       </c>
       <c r="G116" s="321">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="H116" s="116">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="I116" s="116">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="J116" s="323">
@@ -23993,11 +23993,11 @@
         <v>0</v>
       </c>
       <c r="L116" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="M116" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="N116" s="19"/>
@@ -24038,15 +24038,15 @@
         <v>35</v>
       </c>
       <c r="G117" s="321">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="H117" s="116">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0</v>
       </c>
       <c r="I117" s="324">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="J117" s="324">
@@ -24058,11 +24058,11 @@
         <v>0</v>
       </c>
       <c r="L117" s="116">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="M117" s="116">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="N117" s="19"/>
@@ -24103,31 +24103,31 @@
       </c>
       <c r="F118" s="119"/>
       <c r="G118" s="119">
-        <f t="shared" ref="G118:M118" si="100">SUM(G112:G117)</f>
+        <f t="shared" ref="G118:M118" si="101">SUM(G112:G117)</f>
         <v>150</v>
       </c>
       <c r="H118" s="119">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>150</v>
       </c>
       <c r="I118" s="119">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>147</v>
       </c>
       <c r="J118" s="120">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>6469.5</v>
       </c>
       <c r="K118" s="119">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L118" s="119">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>672828</v>
       </c>
       <c r="M118" s="119">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>15288</v>
       </c>
       <c r="N118" s="123">
@@ -24177,7 +24177,7 @@
         <v>38</v>
       </c>
       <c r="G119" s="333">
-        <f t="shared" ref="G119:G124" si="101">D119+E119*2</f>
+        <f t="shared" ref="G119:G124" si="102">D119+E119*2</f>
         <v>57</v>
       </c>
       <c r="H119" s="218">
@@ -24185,7 +24185,7 @@
         <v>57</v>
       </c>
       <c r="I119" s="334">
-        <f t="shared" ref="I119:I124" si="102">D119+E119</f>
+        <f t="shared" ref="I119:I124" si="103">D119+E119</f>
         <v>54</v>
       </c>
       <c r="J119" s="334">
@@ -24197,11 +24197,11 @@
         <v>2329.02</v>
       </c>
       <c r="L119" s="218">
-        <f t="shared" ref="L119:L124" si="103">J119*104</f>
+        <f t="shared" ref="L119:L124" si="104">J119*104</f>
         <v>255674.64000000004</v>
       </c>
       <c r="M119" s="218">
-        <f t="shared" ref="M119:M124" si="104">I119*104</f>
+        <f t="shared" ref="M119:M124" si="105">I119*104</f>
         <v>5616</v>
       </c>
       <c r="N119" s="19"/>
@@ -24242,15 +24242,15 @@
         <v>52</v>
       </c>
       <c r="G120" s="333">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>57</v>
       </c>
       <c r="H120" s="218">
-        <f t="shared" ref="H120:H124" si="105">B120+C120*2</f>
+        <f t="shared" ref="H120:H124" si="106">B120+C120*2</f>
         <v>57</v>
       </c>
       <c r="I120" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>57</v>
       </c>
       <c r="J120" s="218">
@@ -24262,11 +24262,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L120" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M120" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>5928</v>
       </c>
       <c r="N120" s="19"/>
@@ -24308,15 +24308,15 @@
         <v>36</v>
       </c>
       <c r="G121" s="333">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="H121" s="218">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="I121" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="J121" s="218">
@@ -24328,11 +24328,11 @@
         <v>0</v>
       </c>
       <c r="L121" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="M121" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="N121" s="19"/>
@@ -24373,15 +24373,15 @@
         <v>53</v>
       </c>
       <c r="G122" s="333">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="H122" s="218">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="I122" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="J122" s="218">
@@ -24393,11 +24393,11 @@
         <v>0</v>
       </c>
       <c r="L122" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="M122" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="N122" s="19"/>
@@ -24439,15 +24439,15 @@
         <v>122</v>
       </c>
       <c r="G123" s="333">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="H123" s="218">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="I123" s="218">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="J123" s="335">
@@ -24459,11 +24459,11 @@
         <v>0</v>
       </c>
       <c r="L123" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="M123" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="N123" s="19"/>
@@ -24504,15 +24504,15 @@
         <v>35</v>
       </c>
       <c r="G124" s="333">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="H124" s="218">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="I124" s="336">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0</v>
       </c>
       <c r="J124" s="336">
@@ -24524,11 +24524,11 @@
         <v>0</v>
       </c>
       <c r="L124" s="218">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0</v>
       </c>
       <c r="M124" s="218">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="N124" s="19"/>
@@ -24569,15 +24569,15 @@
       </c>
       <c r="F125" s="119"/>
       <c r="G125" s="119">
-        <f t="shared" ref="G125:M125" si="106">SUM(G119:G124)</f>
+        <f t="shared" ref="G125:M125" si="107">SUM(G119:G124)</f>
         <v>114</v>
       </c>
       <c r="H125" s="119">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>114</v>
       </c>
       <c r="I125" s="119">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>111</v>
       </c>
       <c r="J125" s="120">
@@ -24585,15 +24585,15 @@
         <v>4916.8200000000006</v>
       </c>
       <c r="K125" s="119">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>4787.43</v>
       </c>
       <c r="L125" s="119">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>511349.28000000009</v>
       </c>
       <c r="M125" s="119">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>11544</v>
       </c>
       <c r="N125" s="123">
@@ -24643,7 +24643,7 @@
         <v>38</v>
       </c>
       <c r="G126" s="125">
-        <f t="shared" ref="G126:G131" si="107">D126+E126*2</f>
+        <f t="shared" ref="G126:G131" si="108">D126+E126*2</f>
         <v>119</v>
       </c>
       <c r="H126" s="125">
@@ -24651,7 +24651,7 @@
         <v>120</v>
       </c>
       <c r="I126" s="125">
-        <f t="shared" ref="I126:I131" si="108">D126+E126</f>
+        <f t="shared" ref="I126:I131" si="109">D126+E126</f>
         <v>80</v>
       </c>
       <c r="J126" s="125">
@@ -24663,11 +24663,11 @@
         <v>3450.4</v>
       </c>
       <c r="L126" s="125">
-        <f t="shared" ref="L126:L131" si="109">J126*104</f>
+        <f t="shared" ref="L126:L131" si="110">J126*104</f>
         <v>533776.88</v>
       </c>
       <c r="M126" s="125">
-        <f t="shared" ref="M126:M131" si="110">I126*104</f>
+        <f t="shared" ref="M126:M131" si="111">I126*104</f>
         <v>8320</v>
       </c>
       <c r="N126" s="19"/>
@@ -24710,15 +24710,15 @@
         <v>52</v>
       </c>
       <c r="G127" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>118</v>
       </c>
       <c r="H127" s="125">
-        <f t="shared" ref="H127:H131" si="111">B127+C127*2</f>
+        <f t="shared" ref="H127:H131" si="112">B127+C127*2</f>
         <v>120</v>
       </c>
       <c r="I127" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>78</v>
       </c>
       <c r="J127" s="125">
@@ -24730,11 +24730,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L127" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>529291.36</v>
       </c>
       <c r="M127" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>8112</v>
       </c>
       <c r="N127" s="19"/>
@@ -24777,15 +24777,15 @@
         <v>36</v>
       </c>
       <c r="G128" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>37</v>
       </c>
       <c r="H128" s="125">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>39</v>
       </c>
       <c r="I128" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>35</v>
       </c>
       <c r="J128" s="125">
@@ -24797,11 +24797,11 @@
         <v>1018.85</v>
       </c>
       <c r="L128" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>112015.28</v>
       </c>
       <c r="M128" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>3640</v>
       </c>
       <c r="N128" s="19"/>
@@ -24844,15 +24844,15 @@
         <v>53</v>
       </c>
       <c r="G129" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>34</v>
       </c>
       <c r="H129" s="125">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>35</v>
       </c>
       <c r="I129" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>32</v>
       </c>
       <c r="J129" s="125">
@@ -24864,11 +24864,11 @@
         <v>931.52</v>
       </c>
       <c r="L129" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>102932.96</v>
       </c>
       <c r="M129" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>3328</v>
       </c>
       <c r="N129" s="19"/>
@@ -24909,15 +24909,15 @@
         <v>122</v>
       </c>
       <c r="G130" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="H130" s="125">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="I130" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="J130" s="125">
@@ -24929,11 +24929,11 @@
         <v>0</v>
       </c>
       <c r="L130" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="M130" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="N130" s="19"/>
@@ -24974,15 +24974,15 @@
         <v>35</v>
       </c>
       <c r="G131" s="125">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>4</v>
       </c>
       <c r="H131" s="125">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>4</v>
       </c>
       <c r="I131" s="125">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>4</v>
       </c>
       <c r="J131" s="125">
@@ -24994,11 +24994,11 @@
         <v>101.6</v>
       </c>
       <c r="L131" s="125">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v>10566.4</v>
       </c>
       <c r="M131" s="125">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>416</v>
       </c>
       <c r="N131" s="19"/>
@@ -25039,31 +25039,31 @@
       </c>
       <c r="F132" s="119"/>
       <c r="G132" s="119">
-        <f t="shared" ref="G132:M132" si="112">SUM(G126:G131)</f>
+        <f t="shared" ref="G132:M132" si="113">SUM(G126:G131)</f>
         <v>312</v>
       </c>
       <c r="H132" s="119">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>318</v>
       </c>
       <c r="I132" s="119">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>229</v>
       </c>
       <c r="J132" s="120">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>12390.220000000001</v>
       </c>
       <c r="K132" s="119">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>8866.510000000002</v>
       </c>
       <c r="L132" s="118">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>1288582.8799999999</v>
       </c>
       <c r="M132" s="151">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>23816</v>
       </c>
       <c r="N132" s="123">
@@ -25113,7 +25113,7 @@
         <v>38</v>
       </c>
       <c r="G133" s="125">
-        <f t="shared" ref="G133:G138" si="113">D133+E133*2</f>
+        <f t="shared" ref="G133:G138" si="114">D133+E133*2</f>
         <v>119</v>
       </c>
       <c r="H133" s="125">
@@ -25121,7 +25121,7 @@
         <v>120</v>
       </c>
       <c r="I133" s="125">
-        <f t="shared" ref="I133:I138" si="114">D133+E133</f>
+        <f t="shared" ref="I133:I138" si="115">D133+E133</f>
         <v>79</v>
       </c>
       <c r="J133" s="125">
@@ -25133,11 +25133,11 @@
         <v>3407.27</v>
       </c>
       <c r="L133" s="125">
-        <f t="shared" ref="L133:L138" si="115">J133*104</f>
+        <f t="shared" ref="L133:L138" si="116">J133*104</f>
         <v>533776.88</v>
       </c>
       <c r="M133" s="125">
-        <f t="shared" ref="M133:M138" si="116">I133*104</f>
+        <f t="shared" ref="M133:M138" si="117">I133*104</f>
         <v>8216</v>
       </c>
       <c r="N133" s="19"/>
@@ -25180,15 +25180,15 @@
         <v>52</v>
       </c>
       <c r="G134" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>119</v>
       </c>
       <c r="H134" s="125">
-        <f t="shared" ref="H134:H138" si="117">B134+C134*2</f>
+        <f t="shared" ref="H134:H138" si="118">B134+C134*2</f>
         <v>120</v>
       </c>
       <c r="I134" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>78</v>
       </c>
       <c r="J134" s="125">
@@ -25200,11 +25200,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L134" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>533776.88</v>
       </c>
       <c r="M134" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>8112</v>
       </c>
       <c r="N134" s="19"/>
@@ -25247,15 +25247,15 @@
         <v>36</v>
       </c>
       <c r="G135" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>38</v>
       </c>
       <c r="H135" s="125">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>39</v>
       </c>
       <c r="I135" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>36</v>
       </c>
       <c r="J135" s="125">
@@ -25267,11 +25267,11 @@
         <v>1047.96</v>
       </c>
       <c r="L135" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>115042.72</v>
       </c>
       <c r="M135" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>3744</v>
       </c>
       <c r="N135" s="19"/>
@@ -25314,15 +25314,15 @@
         <v>53</v>
       </c>
       <c r="G136" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>34</v>
       </c>
       <c r="H136" s="125">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>35</v>
       </c>
       <c r="I136" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>32</v>
       </c>
       <c r="J136" s="125">
@@ -25334,11 +25334,11 @@
         <v>931.52</v>
       </c>
       <c r="L136" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>102932.96</v>
       </c>
       <c r="M136" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>3328</v>
       </c>
       <c r="N136" s="19"/>
@@ -25379,15 +25379,15 @@
         <v>122</v>
       </c>
       <c r="G137" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0</v>
       </c>
       <c r="H137" s="125">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0</v>
       </c>
       <c r="I137" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="J137" s="125">
@@ -25399,11 +25399,11 @@
         <v>0</v>
       </c>
       <c r="L137" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="M137" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0</v>
       </c>
       <c r="N137" s="19"/>
@@ -25444,15 +25444,15 @@
         <v>35</v>
       </c>
       <c r="G138" s="125">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>4</v>
       </c>
       <c r="H138" s="125">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>4</v>
       </c>
       <c r="I138" s="125">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>4</v>
       </c>
       <c r="J138" s="125">
@@ -25464,11 +25464,11 @@
         <v>101.6</v>
       </c>
       <c r="L138" s="125">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>10566.4</v>
       </c>
       <c r="M138" s="125">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>416</v>
       </c>
       <c r="N138" s="19"/>
@@ -25509,31 +25509,31 @@
       </c>
       <c r="F139" s="119"/>
       <c r="G139" s="119">
-        <f t="shared" ref="G139:M139" si="118">SUM(G133:G138)</f>
+        <f t="shared" ref="G139:M139" si="119">SUM(G133:G138)</f>
         <v>314</v>
       </c>
       <c r="H139" s="119">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>318</v>
       </c>
       <c r="I139" s="119">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>229</v>
       </c>
       <c r="J139" s="120">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>12462.460000000001</v>
       </c>
       <c r="K139" s="119">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>8852.49</v>
       </c>
       <c r="L139" s="118">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>1296095.8399999999</v>
       </c>
       <c r="M139" s="151">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>23816</v>
       </c>
       <c r="N139" s="123">
@@ -25583,7 +25583,7 @@
         <v>38</v>
       </c>
       <c r="G140" s="221">
-        <f t="shared" ref="G140:G145" si="119">D140+E140*2</f>
+        <f t="shared" ref="G140:G145" si="120">D140+E140*2</f>
         <v>118</v>
       </c>
       <c r="H140" s="125">
@@ -25591,7 +25591,7 @@
         <v>120</v>
       </c>
       <c r="I140" s="222">
-        <f t="shared" ref="I140:I145" si="120">D140+E140</f>
+        <f t="shared" ref="I140:I145" si="121">D140+E140</f>
         <v>79</v>
       </c>
       <c r="J140" s="222">
@@ -25603,11 +25603,11 @@
         <v>3407.27</v>
       </c>
       <c r="L140" s="125">
-        <f t="shared" ref="L140:L145" si="121">J140*104</f>
+        <f t="shared" ref="L140:L145" si="122">J140*104</f>
         <v>529291.36</v>
       </c>
       <c r="M140" s="125">
-        <f t="shared" ref="M140:M145" si="122">I140*104</f>
+        <f t="shared" ref="M140:M145" si="123">I140*104</f>
         <v>8216</v>
       </c>
       <c r="N140" s="19"/>
@@ -25650,15 +25650,15 @@
         <v>52</v>
       </c>
       <c r="G141" s="221">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>118</v>
       </c>
       <c r="H141" s="125">
-        <f t="shared" ref="H141:H145" si="123">B141+C141*2</f>
+        <f t="shared" ref="H141:H145" si="124">B141+C141*2</f>
         <v>120</v>
       </c>
       <c r="I141" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>78</v>
       </c>
       <c r="J141" s="125">
@@ -25670,11 +25670,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L141" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>529291.36</v>
       </c>
       <c r="M141" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>8112</v>
       </c>
       <c r="N141" s="19"/>
@@ -25717,15 +25717,15 @@
         <v>36</v>
       </c>
       <c r="G142" s="221">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>38</v>
       </c>
       <c r="H142" s="125">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>39</v>
       </c>
       <c r="I142" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>36</v>
       </c>
       <c r="J142" s="125">
@@ -25737,11 +25737,11 @@
         <v>1047.96</v>
       </c>
       <c r="L142" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>115042.72</v>
       </c>
       <c r="M142" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>3744</v>
       </c>
       <c r="N142" s="19"/>
@@ -25784,15 +25784,15 @@
         <v>53</v>
       </c>
       <c r="G143" s="221">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>34</v>
       </c>
       <c r="H143" s="125">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>35</v>
       </c>
       <c r="I143" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>32</v>
       </c>
       <c r="J143" s="125">
@@ -25804,11 +25804,11 @@
         <v>931.52</v>
       </c>
       <c r="L143" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>102932.96</v>
       </c>
       <c r="M143" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>3328</v>
       </c>
       <c r="N143" s="19"/>
@@ -25849,15 +25849,15 @@
         <v>122</v>
       </c>
       <c r="G144" s="221">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="H144" s="125">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="I144" s="125">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="J144" s="223">
@@ -25869,11 +25869,11 @@
         <v>0</v>
       </c>
       <c r="L144" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
       <c r="M144" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="N144" s="19"/>
@@ -25914,15 +25914,15 @@
         <v>35</v>
       </c>
       <c r="G145" s="221">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v>4</v>
       </c>
       <c r="H145" s="125">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>4</v>
       </c>
       <c r="I145" s="224">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>4</v>
       </c>
       <c r="J145" s="224">
@@ -25934,11 +25934,11 @@
         <v>101.6</v>
       </c>
       <c r="L145" s="125">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>10566.4</v>
       </c>
       <c r="M145" s="125">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>416</v>
       </c>
       <c r="N145" s="19"/>
@@ -25979,31 +25979,31 @@
       </c>
       <c r="F146" s="119"/>
       <c r="G146" s="119">
-        <f t="shared" ref="G146:M146" si="124">SUM(G140:G145)</f>
+        <f t="shared" ref="G146:M146" si="125">SUM(G140:G145)</f>
         <v>312</v>
       </c>
       <c r="H146" s="119">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>318</v>
       </c>
       <c r="I146" s="119">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>229</v>
       </c>
       <c r="J146" s="120">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>12376.2</v>
       </c>
       <c r="K146" s="119">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>8852.49</v>
       </c>
       <c r="L146" s="119">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>1287124.7999999998</v>
       </c>
       <c r="M146" s="119">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>23816</v>
       </c>
       <c r="N146" s="123">
@@ -26054,7 +26054,7 @@
         <v>38</v>
       </c>
       <c r="G147" s="218">
-        <f t="shared" ref="G147:G152" si="125">D147+E147*2</f>
+        <f t="shared" ref="G147:G152" si="126">D147+E147*2</f>
         <v>71</v>
       </c>
       <c r="H147" s="218">
@@ -26062,7 +26062,7 @@
         <v>71</v>
       </c>
       <c r="I147" s="218">
-        <f t="shared" ref="I147:I152" si="126">D147+E147</f>
+        <f t="shared" ref="I147:I152" si="127">D147+E147</f>
         <v>54</v>
       </c>
       <c r="J147" s="218">
@@ -26074,11 +26074,11 @@
         <v>2329.02</v>
       </c>
       <c r="L147" s="218">
-        <f t="shared" ref="L147:L152" si="127">J147*104</f>
+        <f t="shared" ref="L147:L152" si="128">J147*104</f>
         <v>318471.92</v>
       </c>
       <c r="M147" s="218">
-        <f t="shared" ref="M147:M152" si="128">I147*104</f>
+        <f t="shared" ref="M147:M152" si="129">I147*104</f>
         <v>5616</v>
       </c>
       <c r="N147" s="19"/>
@@ -26100,7 +26100,7 @@
       </c>
     </row>
     <row r="148" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="371" t="s">
+      <c r="A148" s="363" t="s">
         <v>189</v>
       </c>
       <c r="B148" s="218">
@@ -26121,15 +26121,15 @@
         <v>52</v>
       </c>
       <c r="G148" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>71</v>
       </c>
       <c r="H148" s="218">
-        <f t="shared" ref="H148:H152" si="129">B148+C148*2</f>
+        <f t="shared" ref="H148:H152" si="130">B148+C148*2</f>
         <v>71</v>
       </c>
       <c r="I148" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>57</v>
       </c>
       <c r="J148" s="218">
@@ -26141,11 +26141,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L148" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>318471.92</v>
       </c>
       <c r="M148" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>5928</v>
       </c>
       <c r="N148" s="19"/>
@@ -26169,7 +26169,7 @@
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A149" s="371"/>
+      <c r="A149" s="363"/>
       <c r="B149" s="218">
         <v>0</v>
       </c>
@@ -26188,15 +26188,15 @@
         <v>36</v>
       </c>
       <c r="G149" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="H149" s="218">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="I149" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="J149" s="218">
@@ -26208,11 +26208,11 @@
         <v>0</v>
       </c>
       <c r="L149" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="M149" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="N149" s="19"/>
@@ -26234,7 +26234,7 @@
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A150" s="371"/>
+      <c r="A150" s="363"/>
       <c r="B150" s="218">
         <v>0</v>
       </c>
@@ -26253,15 +26253,15 @@
         <v>53</v>
       </c>
       <c r="G150" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="H150" s="218">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="I150" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="J150" s="218">
@@ -26273,11 +26273,11 @@
         <v>0</v>
       </c>
       <c r="L150" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="M150" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="N150" s="19"/>
@@ -26299,7 +26299,7 @@
       </c>
     </row>
     <row r="151" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="371"/>
+      <c r="A151" s="363"/>
       <c r="B151" s="218">
         <v>0</v>
       </c>
@@ -26318,15 +26318,15 @@
         <v>122</v>
       </c>
       <c r="G151" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="H151" s="218">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="I151" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="J151" s="218">
@@ -26338,11 +26338,11 @@
         <v>0</v>
       </c>
       <c r="L151" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="M151" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="N151" s="19"/>
@@ -26364,7 +26364,7 @@
       </c>
     </row>
     <row r="152" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="371"/>
+      <c r="A152" s="363"/>
       <c r="B152" s="218">
         <v>0</v>
       </c>
@@ -26383,15 +26383,15 @@
         <v>35</v>
       </c>
       <c r="G152" s="218">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="H152" s="218">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0</v>
       </c>
       <c r="I152" s="218">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="J152" s="218">
@@ -26403,11 +26403,11 @@
         <v>0</v>
       </c>
       <c r="L152" s="218">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="M152" s="218">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="N152" s="19"/>
@@ -26448,15 +26448,15 @@
       </c>
       <c r="F153" s="119"/>
       <c r="G153" s="119">
-        <f t="shared" ref="G153:M153" si="130">SUM(G147:G152)</f>
+        <f t="shared" ref="G153:M153" si="131">SUM(G147:G152)</f>
         <v>142</v>
       </c>
       <c r="H153" s="119">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>142</v>
       </c>
       <c r="I153" s="119">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>111</v>
       </c>
       <c r="J153" s="120">
@@ -26464,15 +26464,15 @@
         <v>6124.46</v>
       </c>
       <c r="K153" s="119">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>4787.43</v>
       </c>
       <c r="L153" s="118">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>636943.84</v>
       </c>
       <c r="M153" s="151">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>11544</v>
       </c>
       <c r="N153" s="123">
@@ -26522,7 +26522,7 @@
         <v>38</v>
       </c>
       <c r="G154" s="125">
-        <f t="shared" ref="G154:G159" si="131">D154+E154*2</f>
+        <f t="shared" ref="G154:G159" si="132">D154+E154*2</f>
         <v>120</v>
       </c>
       <c r="H154" s="125">
@@ -26530,7 +26530,7 @@
         <v>120</v>
       </c>
       <c r="I154" s="125">
-        <f t="shared" ref="I154:I159" si="132">D154+E154</f>
+        <f t="shared" ref="I154:I159" si="133">D154+E154</f>
         <v>79</v>
       </c>
       <c r="J154" s="125">
@@ -26542,11 +26542,11 @@
         <v>3407.27</v>
       </c>
       <c r="L154" s="125">
-        <f t="shared" ref="L154:L159" si="133">J154*104</f>
+        <f t="shared" ref="L154:L159" si="134">J154*104</f>
         <v>538262.4</v>
       </c>
       <c r="M154" s="125">
-        <f t="shared" ref="M154:M159" si="134">I154*104</f>
+        <f t="shared" ref="M154:M159" si="135">I154*104</f>
         <v>8216</v>
       </c>
       <c r="N154" s="19"/>
@@ -26589,15 +26589,15 @@
         <v>52</v>
       </c>
       <c r="G155" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>120</v>
       </c>
       <c r="H155" s="125">
-        <f t="shared" ref="H155:H159" si="135">B155+C155*2</f>
+        <f t="shared" ref="H155:H159" si="136">B155+C155*2</f>
         <v>120</v>
       </c>
       <c r="I155" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>78</v>
       </c>
       <c r="J155" s="125">
@@ -26609,11 +26609,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L155" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>538262.4</v>
       </c>
       <c r="M155" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>8112</v>
       </c>
       <c r="N155" s="19"/>
@@ -26658,15 +26658,15 @@
         <v>36</v>
       </c>
       <c r="G156" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>38</v>
       </c>
       <c r="H156" s="125">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>39</v>
       </c>
       <c r="I156" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>36</v>
       </c>
       <c r="J156" s="125">
@@ -26678,11 +26678,11 @@
         <v>1047.96</v>
       </c>
       <c r="L156" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>115042.72</v>
       </c>
       <c r="M156" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>3744</v>
       </c>
       <c r="N156" s="19"/>
@@ -26727,15 +26727,15 @@
         <v>53</v>
       </c>
       <c r="G157" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>34</v>
       </c>
       <c r="H157" s="125">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>35</v>
       </c>
       <c r="I157" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>32</v>
       </c>
       <c r="J157" s="125">
@@ -26747,11 +26747,11 @@
         <v>931.52</v>
       </c>
       <c r="L157" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>102932.96</v>
       </c>
       <c r="M157" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>3328</v>
       </c>
       <c r="N157" s="19"/>
@@ -26794,15 +26794,15 @@
         <v>122</v>
       </c>
       <c r="G158" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0</v>
       </c>
       <c r="H158" s="125">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="I158" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0</v>
       </c>
       <c r="J158" s="125">
@@ -26814,11 +26814,11 @@
         <v>0</v>
       </c>
       <c r="L158" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0</v>
       </c>
       <c r="M158" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
       <c r="N158" s="19"/>
@@ -26861,15 +26861,15 @@
         <v>35</v>
       </c>
       <c r="G159" s="125">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>4</v>
       </c>
       <c r="H159" s="125">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>4</v>
       </c>
       <c r="I159" s="125">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>4</v>
       </c>
       <c r="J159" s="125">
@@ -26881,11 +26881,11 @@
         <v>101.6</v>
       </c>
       <c r="L159" s="125">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>10566.4</v>
       </c>
       <c r="M159" s="125">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>416</v>
       </c>
       <c r="N159" s="19"/>
@@ -26926,31 +26926,31 @@
       </c>
       <c r="F160" s="119"/>
       <c r="G160" s="119">
-        <f t="shared" ref="G160:M160" si="136">SUM(G154:G159)</f>
+        <f t="shared" ref="G160:M160" si="137">SUM(G154:G159)</f>
         <v>316</v>
       </c>
       <c r="H160" s="119">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>318</v>
       </c>
       <c r="I160" s="119">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>229</v>
       </c>
       <c r="J160" s="120">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>12548.720000000001</v>
       </c>
       <c r="K160" s="119">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>8852.49</v>
       </c>
       <c r="L160" s="118">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>1305066.8799999999</v>
       </c>
       <c r="M160" s="151">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>23816</v>
       </c>
       <c r="N160" s="123">
@@ -27000,7 +27000,7 @@
         <v>38</v>
       </c>
       <c r="G161" s="321">
-        <f t="shared" ref="G161:G166" si="137">D161+E161*2</f>
+        <f t="shared" ref="G161:G166" si="138">D161+E161*2</f>
         <v>75</v>
       </c>
       <c r="H161" s="116">
@@ -27008,7 +27008,7 @@
         <v>75</v>
       </c>
       <c r="I161" s="322">
-        <f t="shared" ref="I161:I166" si="138">D161+E161</f>
+        <f t="shared" ref="I161:I166" si="139">D161+E161</f>
         <v>72</v>
       </c>
       <c r="J161" s="322">
@@ -27020,11 +27020,11 @@
         <v>3105.36</v>
       </c>
       <c r="L161" s="116">
-        <f t="shared" ref="L161:L166" si="139">J161*104</f>
+        <f t="shared" ref="L161:L166" si="140">J161*104</f>
         <v>336414</v>
       </c>
       <c r="M161" s="116">
-        <f t="shared" ref="M161:M166" si="140">I161*104</f>
+        <f t="shared" ref="M161:M166" si="141">I161*104</f>
         <v>7488</v>
       </c>
       <c r="N161" s="19"/>
@@ -27065,15 +27065,15 @@
         <v>52</v>
       </c>
       <c r="G162" s="321">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>75</v>
       </c>
       <c r="H162" s="116">
-        <f t="shared" ref="H162:H166" si="141">B162+C162*2</f>
+        <f t="shared" ref="H162:H166" si="142">B162+C162*2</f>
         <v>75</v>
       </c>
       <c r="I162" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>75</v>
       </c>
       <c r="J162" s="116">
@@ -27085,11 +27085,11 @@
         <v>3234.75</v>
       </c>
       <c r="L162" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>336414</v>
       </c>
       <c r="M162" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>7800</v>
       </c>
       <c r="N162" s="19"/>
@@ -27131,15 +27131,15 @@
         <v>36</v>
       </c>
       <c r="G163" s="321">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="H163" s="116">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="I163" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="J163" s="116">
@@ -27151,11 +27151,11 @@
         <v>0</v>
       </c>
       <c r="L163" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="M163" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="N163" s="19"/>
@@ -27196,15 +27196,15 @@
         <v>53</v>
       </c>
       <c r="G164" s="321">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="H164" s="116">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="I164" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="J164" s="116">
@@ -27216,11 +27216,11 @@
         <v>0</v>
       </c>
       <c r="L164" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="M164" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="N164" s="19"/>
@@ -27261,15 +27261,15 @@
         <v>122</v>
       </c>
       <c r="G165" s="321">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="H165" s="116">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="I165" s="116">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="J165" s="323">
@@ -27281,11 +27281,11 @@
         <v>0</v>
       </c>
       <c r="L165" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="M165" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="N165" s="19"/>
@@ -27326,15 +27326,15 @@
         <v>35</v>
       </c>
       <c r="G166" s="321">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="H166" s="116">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>0</v>
       </c>
       <c r="I166" s="324">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="J166" s="324">
@@ -27346,11 +27346,11 @@
         <v>0</v>
       </c>
       <c r="L166" s="116">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0</v>
       </c>
       <c r="M166" s="116">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0</v>
       </c>
       <c r="N166" s="19"/>
@@ -27391,31 +27391,31 @@
       </c>
       <c r="F167" s="119"/>
       <c r="G167" s="119">
-        <f t="shared" ref="G167:M167" si="142">SUM(G161:G166)</f>
+        <f t="shared" ref="G167:M167" si="143">SUM(G161:G166)</f>
         <v>150</v>
       </c>
       <c r="H167" s="119">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>150</v>
       </c>
       <c r="I167" s="119">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>147</v>
       </c>
       <c r="J167" s="120">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>6469.5</v>
       </c>
       <c r="K167" s="119">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L167" s="119">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>672828</v>
       </c>
       <c r="M167" s="119">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>15288</v>
       </c>
       <c r="N167" s="123">
@@ -27465,7 +27465,7 @@
         <v>38</v>
       </c>
       <c r="G168" s="333">
-        <f t="shared" ref="G168:G173" si="143">D168+E168*2</f>
+        <f t="shared" ref="G168:G173" si="144">D168+E168*2</f>
         <v>56</v>
       </c>
       <c r="H168" s="218">
@@ -27473,7 +27473,7 @@
         <v>57</v>
       </c>
       <c r="I168" s="334">
-        <f t="shared" ref="I168:I173" si="144">D168+E168</f>
+        <f t="shared" ref="I168:I173" si="145">D168+E168</f>
         <v>54</v>
       </c>
       <c r="J168" s="334">
@@ -27485,11 +27485,11 @@
         <v>2329.02</v>
       </c>
       <c r="L168" s="218">
-        <f t="shared" ref="L168:L173" si="145">J168*104</f>
+        <f t="shared" ref="L168:L173" si="146">J168*104</f>
         <v>251189.12000000002</v>
       </c>
       <c r="M168" s="218">
-        <f t="shared" ref="M168:M173" si="146">I168*104</f>
+        <f t="shared" ref="M168:M173" si="147">I168*104</f>
         <v>5616</v>
       </c>
       <c r="N168" s="19"/>
@@ -27530,15 +27530,15 @@
         <v>52</v>
       </c>
       <c r="G169" s="333">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>57</v>
       </c>
       <c r="H169" s="218">
-        <f t="shared" ref="H169:H173" si="147">B169+C169*2</f>
+        <f t="shared" ref="H169:H173" si="148">B169+C169*2</f>
         <v>57</v>
       </c>
       <c r="I169" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>57</v>
       </c>
       <c r="J169" s="218">
@@ -27550,11 +27550,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L169" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M169" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>5928</v>
       </c>
       <c r="N169" s="19"/>
@@ -27596,15 +27596,15 @@
         <v>36</v>
       </c>
       <c r="G170" s="333">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="H170" s="218">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="I170" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="J170" s="218">
@@ -27616,11 +27616,11 @@
         <v>0</v>
       </c>
       <c r="L170" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="M170" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="N170" s="19"/>
@@ -27661,15 +27661,15 @@
         <v>53</v>
       </c>
       <c r="G171" s="333">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="H171" s="218">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="I171" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="J171" s="218">
@@ -27681,11 +27681,11 @@
         <v>0</v>
       </c>
       <c r="L171" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="M171" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="N171" s="19"/>
@@ -27726,15 +27726,15 @@
         <v>122</v>
       </c>
       <c r="G172" s="333">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="H172" s="218">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="I172" s="218">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="J172" s="335">
@@ -27746,11 +27746,11 @@
         <v>0</v>
       </c>
       <c r="L172" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="M172" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="N172" s="19"/>
@@ -27791,15 +27791,15 @@
         <v>35</v>
       </c>
       <c r="G173" s="333">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>0</v>
       </c>
       <c r="H173" s="218">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>0</v>
       </c>
       <c r="I173" s="336">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>0</v>
       </c>
       <c r="J173" s="336">
@@ -27811,11 +27811,11 @@
         <v>0</v>
       </c>
       <c r="L173" s="218">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>0</v>
       </c>
       <c r="M173" s="218">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>0</v>
       </c>
       <c r="N173" s="19"/>
@@ -27856,31 +27856,31 @@
       </c>
       <c r="F174" s="119"/>
       <c r="G174" s="119">
-        <f t="shared" ref="G174:M174" si="148">SUM(G168:G173)</f>
+        <f t="shared" ref="G174:M174" si="149">SUM(G168:G173)</f>
         <v>113</v>
       </c>
       <c r="H174" s="119">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>114</v>
       </c>
       <c r="I174" s="119">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>111</v>
       </c>
       <c r="J174" s="120">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>4873.6900000000005</v>
       </c>
       <c r="K174" s="119">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>4787.43</v>
       </c>
       <c r="L174" s="119">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>506863.76000000007</v>
       </c>
       <c r="M174" s="119">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>11544</v>
       </c>
       <c r="N174" s="123">
@@ -27930,7 +27930,7 @@
         <v>38</v>
       </c>
       <c r="G175" s="221">
-        <f t="shared" ref="G175:G180" si="149">D175+E175*2</f>
+        <f t="shared" ref="G175:G180" si="150">D175+E175*2</f>
         <v>118</v>
       </c>
       <c r="H175" s="125">
@@ -27938,7 +27938,7 @@
         <v>120</v>
       </c>
       <c r="I175" s="222">
-        <f t="shared" ref="I175:I180" si="150">D175+E175</f>
+        <f t="shared" ref="I175:I180" si="151">D175+E175</f>
         <v>79</v>
       </c>
       <c r="J175" s="222">
@@ -27950,11 +27950,11 @@
         <v>3407.27</v>
       </c>
       <c r="L175" s="125">
-        <f t="shared" ref="L175:L180" si="151">J175*104</f>
+        <f t="shared" ref="L175:L180" si="152">J175*104</f>
         <v>529291.36</v>
       </c>
       <c r="M175" s="125">
-        <f t="shared" ref="M175:M180" si="152">I175*104</f>
+        <f t="shared" ref="M175:M180" si="153">I175*104</f>
         <v>8216</v>
       </c>
       <c r="N175" s="19"/>
@@ -27978,7 +27978,7 @@
       </c>
     </row>
     <row r="176" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="370" t="s">
+      <c r="A176" s="362" t="s">
         <v>188</v>
       </c>
       <c r="B176" s="295">
@@ -27999,15 +27999,15 @@
         <v>52</v>
       </c>
       <c r="G176" s="221">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>118</v>
       </c>
       <c r="H176" s="125">
-        <f t="shared" ref="H176:H180" si="153">B176+C176*2</f>
+        <f t="shared" ref="H176:H180" si="154">B176+C176*2</f>
         <v>120</v>
       </c>
       <c r="I176" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>78</v>
       </c>
       <c r="J176" s="125">
@@ -28019,11 +28019,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L176" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>529291.36</v>
       </c>
       <c r="M176" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>8112</v>
       </c>
       <c r="N176" s="19"/>
@@ -28048,7 +28048,7 @@
       <c r="Y176" s="172"/>
     </row>
     <row r="177" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A177" s="370"/>
+      <c r="A177" s="362"/>
       <c r="B177" s="295">
         <v>33</v>
       </c>
@@ -28067,15 +28067,15 @@
         <v>36</v>
       </c>
       <c r="G177" s="221">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>39</v>
       </c>
       <c r="H177" s="125">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>39</v>
       </c>
       <c r="I177" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>36</v>
       </c>
       <c r="J177" s="125">
@@ -28087,11 +28087,11 @@
         <v>1047.96</v>
       </c>
       <c r="L177" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>118070.16</v>
       </c>
       <c r="M177" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>3744</v>
       </c>
       <c r="N177" s="19"/>
@@ -28115,7 +28115,7 @@
       </c>
     </row>
     <row r="178" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="370"/>
+      <c r="A178" s="362"/>
       <c r="B178" s="295">
         <v>29</v>
       </c>
@@ -28134,15 +28134,15 @@
         <v>53</v>
       </c>
       <c r="G178" s="221">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>35</v>
       </c>
       <c r="H178" s="125">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>35</v>
       </c>
       <c r="I178" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>32</v>
       </c>
       <c r="J178" s="125">
@@ -28154,11 +28154,11 @@
         <v>931.52</v>
       </c>
       <c r="L178" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M178" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>3328</v>
       </c>
       <c r="N178" s="19"/>
@@ -28180,7 +28180,7 @@
       </c>
     </row>
     <row r="179" spans="1:30" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="370"/>
+      <c r="A179" s="362"/>
       <c r="B179" s="295">
         <v>0</v>
       </c>
@@ -28199,15 +28199,15 @@
         <v>122</v>
       </c>
       <c r="G179" s="221">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0</v>
       </c>
       <c r="H179" s="125">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0</v>
       </c>
       <c r="I179" s="125">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>0</v>
       </c>
       <c r="J179" s="223">
@@ -28219,11 +28219,11 @@
         <v>0</v>
       </c>
       <c r="L179" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>0</v>
       </c>
       <c r="M179" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0</v>
       </c>
       <c r="N179" s="19"/>
@@ -28245,7 +28245,7 @@
       </c>
     </row>
     <row r="180" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="370"/>
+      <c r="A180" s="362"/>
       <c r="B180" s="295">
         <v>4</v>
       </c>
@@ -28264,15 +28264,15 @@
         <v>35</v>
       </c>
       <c r="G180" s="221">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>4</v>
       </c>
       <c r="H180" s="125">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>4</v>
       </c>
       <c r="I180" s="224">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>4</v>
       </c>
       <c r="J180" s="224">
@@ -28284,11 +28284,11 @@
         <v>101.6</v>
       </c>
       <c r="L180" s="125">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>10566.4</v>
       </c>
       <c r="M180" s="125">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>416</v>
       </c>
       <c r="N180" s="19"/>
@@ -28329,31 +28329,31 @@
       </c>
       <c r="F181" s="119"/>
       <c r="G181" s="119">
-        <f t="shared" ref="G181:M181" si="154">SUM(G175:G180)</f>
+        <f t="shared" ref="G181:M181" si="155">SUM(G175:G180)</f>
         <v>314</v>
       </c>
       <c r="H181" s="119">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>318</v>
       </c>
       <c r="I181" s="119">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>229</v>
       </c>
       <c r="J181" s="120">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>12434.420000000002</v>
       </c>
       <c r="K181" s="119">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>8852.49</v>
       </c>
       <c r="L181" s="119">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>1293179.6799999997</v>
       </c>
       <c r="M181" s="119">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>23816</v>
       </c>
       <c r="N181" s="123">
@@ -28404,7 +28404,7 @@
         <v>38</v>
       </c>
       <c r="G182" s="125">
-        <f t="shared" ref="G182:G187" si="155">D182+E182*2</f>
+        <f t="shared" ref="G182:G187" si="156">D182+E182*2</f>
         <v>120</v>
       </c>
       <c r="H182" s="125">
@@ -28412,7 +28412,7 @@
         <v>120</v>
       </c>
       <c r="I182" s="125">
-        <f t="shared" ref="I182:I187" si="156">D182+E182</f>
+        <f t="shared" ref="I182:I187" si="157">D182+E182</f>
         <v>79</v>
       </c>
       <c r="J182" s="125">
@@ -28424,11 +28424,11 @@
         <v>3407.27</v>
       </c>
       <c r="L182" s="125">
-        <f t="shared" ref="L182:L187" si="157">J182*104</f>
+        <f t="shared" ref="L182:L187" si="158">J182*104</f>
         <v>538262.4</v>
       </c>
       <c r="M182" s="125">
-        <f t="shared" ref="M182:M187" si="158">I182*104</f>
+        <f t="shared" ref="M182:M187" si="159">I182*104</f>
         <v>8216</v>
       </c>
       <c r="N182" s="19"/>
@@ -28476,15 +28476,15 @@
         <v>52</v>
       </c>
       <c r="G183" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>121</v>
       </c>
       <c r="H183" s="125">
-        <f t="shared" ref="H183:H187" si="159">B183+C183*2</f>
+        <f t="shared" ref="H183:H187" si="160">B183+C183*2</f>
         <v>120</v>
       </c>
       <c r="I183" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>79</v>
       </c>
       <c r="J183" s="125">
@@ -28496,11 +28496,11 @@
         <v>3407.27</v>
       </c>
       <c r="L183" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>542747.92000000004</v>
       </c>
       <c r="M183" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>8216</v>
       </c>
       <c r="N183" s="19"/>
@@ -28548,15 +28548,15 @@
         <v>36</v>
       </c>
       <c r="G184" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>39</v>
       </c>
       <c r="H184" s="125">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>39</v>
       </c>
       <c r="I184" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>36</v>
       </c>
       <c r="J184" s="125">
@@ -28568,11 +28568,11 @@
         <v>1047.96</v>
       </c>
       <c r="L184" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>118070.16</v>
       </c>
       <c r="M184" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>3744</v>
       </c>
       <c r="N184" s="19"/>
@@ -28617,15 +28617,15 @@
         <v>53</v>
       </c>
       <c r="G185" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>34</v>
       </c>
       <c r="H185" s="125">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>35</v>
       </c>
       <c r="I185" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>31</v>
       </c>
       <c r="J185" s="125">
@@ -28637,11 +28637,11 @@
         <v>902.41</v>
       </c>
       <c r="L185" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>102932.96</v>
       </c>
       <c r="M185" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>3224</v>
       </c>
       <c r="N185" s="19"/>
@@ -28682,15 +28682,15 @@
         <v>122</v>
       </c>
       <c r="G186" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="H186" s="125">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0</v>
       </c>
       <c r="I186" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="J186" s="125">
@@ -28702,11 +28702,11 @@
         <v>0</v>
       </c>
       <c r="L186" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>0</v>
       </c>
       <c r="M186" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="N186" s="19"/>
@@ -28747,15 +28747,15 @@
         <v>35</v>
       </c>
       <c r="G187" s="125">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>4</v>
       </c>
       <c r="H187" s="125">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>4</v>
       </c>
       <c r="I187" s="125">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>4</v>
       </c>
       <c r="J187" s="125">
@@ -28767,11 +28767,11 @@
         <v>101.6</v>
       </c>
       <c r="L187" s="125">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>10566.4</v>
       </c>
       <c r="M187" s="125">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>416</v>
       </c>
       <c r="N187" s="19"/>
@@ -28812,31 +28812,31 @@
       </c>
       <c r="F188" s="119"/>
       <c r="G188" s="119">
-        <f t="shared" ref="G188:M188" si="160">SUM(G182:G187)</f>
+        <f t="shared" ref="G188:M188" si="161">SUM(G182:G187)</f>
         <v>318</v>
       </c>
       <c r="H188" s="119">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>318</v>
       </c>
       <c r="I188" s="119">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>229</v>
       </c>
       <c r="J188" s="120">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>12620.960000000003</v>
       </c>
       <c r="K188" s="119">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>8866.51</v>
       </c>
       <c r="L188" s="118">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>1312579.8399999999</v>
       </c>
       <c r="M188" s="151">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>23816</v>
       </c>
       <c r="N188" s="123">
@@ -28886,7 +28886,7 @@
         <v>38</v>
       </c>
       <c r="G189" s="221">
-        <f t="shared" ref="G189:G194" si="161">D189+E189*2</f>
+        <f t="shared" ref="G189:G194" si="162">D189+E189*2</f>
         <v>119</v>
       </c>
       <c r="H189" s="125">
@@ -28894,7 +28894,7 @@
         <v>120</v>
       </c>
       <c r="I189" s="222">
-        <f t="shared" ref="I189:I194" si="162">D189+E189</f>
+        <f t="shared" ref="I189:I194" si="163">D189+E189</f>
         <v>79</v>
       </c>
       <c r="J189" s="222">
@@ -28906,11 +28906,11 @@
         <v>3407.27</v>
       </c>
       <c r="L189" s="125">
-        <f t="shared" ref="L189:L194" si="163">J189*104</f>
+        <f t="shared" ref="L189:L194" si="164">J189*104</f>
         <v>533776.88</v>
       </c>
       <c r="M189" s="125">
-        <f t="shared" ref="M189:M194" si="164">I189*104</f>
+        <f t="shared" ref="M189:M194" si="165">I189*104</f>
         <v>8216</v>
       </c>
       <c r="N189" s="19"/>
@@ -28953,15 +28953,15 @@
         <v>52</v>
       </c>
       <c r="G190" s="221">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>119</v>
       </c>
       <c r="H190" s="125">
-        <f t="shared" ref="H190:H194" si="165">B190+C190*2</f>
+        <f t="shared" ref="H190:H194" si="166">B190+C190*2</f>
         <v>120</v>
       </c>
       <c r="I190" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>78</v>
       </c>
       <c r="J190" s="125">
@@ -28973,11 +28973,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L190" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>533776.88</v>
       </c>
       <c r="M190" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>8112</v>
       </c>
       <c r="N190" s="19"/>
@@ -29020,15 +29020,15 @@
         <v>36</v>
       </c>
       <c r="G191" s="221">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>39</v>
       </c>
       <c r="H191" s="125">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>39</v>
       </c>
       <c r="I191" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>36</v>
       </c>
       <c r="J191" s="125">
@@ -29040,11 +29040,11 @@
         <v>1047.96</v>
       </c>
       <c r="L191" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>118070.16</v>
       </c>
       <c r="M191" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>3744</v>
       </c>
       <c r="N191" s="19"/>
@@ -29087,15 +29087,15 @@
         <v>53</v>
       </c>
       <c r="G192" s="221">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>35</v>
       </c>
       <c r="H192" s="125">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>35</v>
       </c>
       <c r="I192" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>32</v>
       </c>
       <c r="J192" s="125">
@@ -29107,11 +29107,11 @@
         <v>931.52</v>
       </c>
       <c r="L192" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M192" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>3328</v>
       </c>
       <c r="N192" s="19"/>
@@ -29152,15 +29152,15 @@
         <v>122</v>
       </c>
       <c r="G193" s="221">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0</v>
       </c>
       <c r="H193" s="125">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>0</v>
       </c>
       <c r="I193" s="125">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0</v>
       </c>
       <c r="J193" s="223">
@@ -29172,11 +29172,11 @@
         <v>0</v>
       </c>
       <c r="L193" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>0</v>
       </c>
       <c r="M193" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>0</v>
       </c>
       <c r="N193" s="19"/>
@@ -29217,15 +29217,15 @@
         <v>35</v>
       </c>
       <c r="G194" s="221">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>4</v>
       </c>
       <c r="H194" s="125">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>4</v>
       </c>
       <c r="I194" s="224">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>4</v>
       </c>
       <c r="J194" s="224">
@@ -29237,11 +29237,11 @@
         <v>101.6</v>
       </c>
       <c r="L194" s="125">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>10566.4</v>
       </c>
       <c r="M194" s="125">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>416</v>
       </c>
       <c r="N194" s="19"/>
@@ -29282,31 +29282,31 @@
       </c>
       <c r="F195" s="119"/>
       <c r="G195" s="119">
-        <f t="shared" ref="G195:M195" si="166">SUM(G189:G194)</f>
+        <f t="shared" ref="G195:M195" si="167">SUM(G189:G194)</f>
         <v>316</v>
       </c>
       <c r="H195" s="119">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>318</v>
       </c>
       <c r="I195" s="119">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>229</v>
       </c>
       <c r="J195" s="119">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>12520.68</v>
       </c>
       <c r="K195" s="119">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>8852.49</v>
       </c>
       <c r="L195" s="119">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>1302150.7199999997</v>
       </c>
       <c r="M195" s="119">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>23816</v>
       </c>
       <c r="N195" s="123">
@@ -29356,7 +29356,7 @@
         <v>38</v>
       </c>
       <c r="G196" s="221">
-        <f t="shared" ref="G196:G201" si="167">D196+E196*2</f>
+        <f t="shared" ref="G196:G201" si="168">D196+E196*2</f>
         <v>119</v>
       </c>
       <c r="H196" s="125">
@@ -29364,7 +29364,7 @@
         <v>120</v>
       </c>
       <c r="I196" s="222">
-        <f t="shared" ref="I196:I201" si="168">D196+E196</f>
+        <f t="shared" ref="I196:I201" si="169">D196+E196</f>
         <v>79</v>
       </c>
       <c r="J196" s="222">
@@ -29376,11 +29376,11 @@
         <v>3407.27</v>
       </c>
       <c r="L196" s="125">
-        <f t="shared" ref="L196:L201" si="169">J196*104</f>
+        <f t="shared" ref="L196:L201" si="170">J196*104</f>
         <v>533776.88</v>
       </c>
       <c r="M196" s="125">
-        <f t="shared" ref="M196:M201" si="170">I196*104</f>
+        <f t="shared" ref="M196:M201" si="171">I196*104</f>
         <v>8216</v>
       </c>
       <c r="N196" s="19"/>
@@ -29423,15 +29423,15 @@
         <v>52</v>
       </c>
       <c r="G197" s="221">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>119</v>
       </c>
       <c r="H197" s="125">
-        <f t="shared" ref="H197:H201" si="171">B197+C197*2</f>
+        <f t="shared" ref="H197:H201" si="172">B197+C197*2</f>
         <v>120</v>
       </c>
       <c r="I197" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>78</v>
       </c>
       <c r="J197" s="125">
@@ -29443,11 +29443,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L197" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>533776.88</v>
       </c>
       <c r="M197" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>8112</v>
       </c>
       <c r="N197" s="19"/>
@@ -29490,15 +29490,15 @@
         <v>36</v>
       </c>
       <c r="G198" s="221">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>39</v>
       </c>
       <c r="H198" s="125">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>39</v>
       </c>
       <c r="I198" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>36</v>
       </c>
       <c r="J198" s="125">
@@ -29510,11 +29510,11 @@
         <v>1047.96</v>
       </c>
       <c r="L198" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>118070.16</v>
       </c>
       <c r="M198" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>3744</v>
       </c>
       <c r="N198" s="19"/>
@@ -29559,15 +29559,15 @@
         <v>53</v>
       </c>
       <c r="G199" s="221">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>35</v>
       </c>
       <c r="H199" s="125">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>35</v>
       </c>
       <c r="I199" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>32</v>
       </c>
       <c r="J199" s="125">
@@ -29579,11 +29579,11 @@
         <v>931.52</v>
       </c>
       <c r="L199" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M199" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>3328</v>
       </c>
       <c r="N199" s="19"/>
@@ -29626,15 +29626,15 @@
         <v>122</v>
       </c>
       <c r="G200" s="221">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>0</v>
       </c>
       <c r="H200" s="125">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0</v>
       </c>
       <c r="I200" s="125">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>0</v>
       </c>
       <c r="J200" s="223">
@@ -29646,11 +29646,11 @@
         <v>0</v>
       </c>
       <c r="L200" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>0</v>
       </c>
       <c r="M200" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>0</v>
       </c>
       <c r="N200" s="19"/>
@@ -29691,15 +29691,15 @@
         <v>35</v>
       </c>
       <c r="G201" s="221">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>4</v>
       </c>
       <c r="H201" s="125">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>4</v>
       </c>
       <c r="I201" s="224">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v>4</v>
       </c>
       <c r="J201" s="224">
@@ -29711,11 +29711,11 @@
         <v>101.6</v>
       </c>
       <c r="L201" s="125">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v>10566.4</v>
       </c>
       <c r="M201" s="125">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>416</v>
       </c>
       <c r="N201" s="19"/>
@@ -29756,31 +29756,31 @@
       </c>
       <c r="F202" s="119"/>
       <c r="G202" s="119">
-        <f t="shared" ref="G202:M202" si="172">SUM(G196:G201)</f>
+        <f t="shared" ref="G202:M202" si="173">SUM(G196:G201)</f>
         <v>316</v>
       </c>
       <c r="H202" s="119">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>318</v>
       </c>
       <c r="I202" s="119">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>229</v>
       </c>
       <c r="J202" s="119">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>12520.68</v>
       </c>
       <c r="K202" s="119">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>8852.49</v>
       </c>
       <c r="L202" s="119">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>1302150.7199999997</v>
       </c>
       <c r="M202" s="119">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>23816</v>
       </c>
       <c r="N202" s="123">
@@ -29830,7 +29830,7 @@
         <v>38</v>
       </c>
       <c r="G203" s="125">
-        <f t="shared" ref="G203:G208" si="173">D203+E203*2</f>
+        <f t="shared" ref="G203:G208" si="174">D203+E203*2</f>
         <v>119</v>
       </c>
       <c r="H203" s="125">
@@ -29838,7 +29838,7 @@
         <v>120</v>
       </c>
       <c r="I203" s="125">
-        <f t="shared" ref="I203:I208" si="174">D203+E203</f>
+        <f t="shared" ref="I203:I208" si="175">D203+E203</f>
         <v>79</v>
       </c>
       <c r="J203" s="125">
@@ -29850,11 +29850,11 @@
         <v>3407.27</v>
       </c>
       <c r="L203" s="125">
-        <f t="shared" ref="L203:L208" si="175">J203*104</f>
+        <f t="shared" ref="L203:L208" si="176">J203*104</f>
         <v>533776.88</v>
       </c>
       <c r="M203" s="125">
-        <f t="shared" ref="M203:M208" si="176">I203*104</f>
+        <f t="shared" ref="M203:M208" si="177">I203*104</f>
         <v>8216</v>
       </c>
       <c r="N203" s="19"/>
@@ -29897,15 +29897,15 @@
         <v>52</v>
       </c>
       <c r="G204" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>119</v>
       </c>
       <c r="H204" s="125">
-        <f t="shared" ref="H204:H208" si="177">B204+C204*2</f>
+        <f t="shared" ref="H204:H208" si="178">B204+C204*2</f>
         <v>120</v>
       </c>
       <c r="I204" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>78</v>
       </c>
       <c r="J204" s="125">
@@ -29917,11 +29917,11 @@
         <v>3364.1400000000003</v>
       </c>
       <c r="L204" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>533776.88</v>
       </c>
       <c r="M204" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>8112</v>
       </c>
       <c r="N204" s="19"/>
@@ -29964,15 +29964,15 @@
         <v>36</v>
       </c>
       <c r="G205" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>39</v>
       </c>
       <c r="H205" s="125">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>39</v>
       </c>
       <c r="I205" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>36</v>
       </c>
       <c r="J205" s="125">
@@ -29984,11 +29984,11 @@
         <v>1047.96</v>
       </c>
       <c r="L205" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>118070.16</v>
       </c>
       <c r="M205" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>3744</v>
       </c>
       <c r="N205" s="19"/>
@@ -30031,15 +30031,15 @@
         <v>53</v>
       </c>
       <c r="G206" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>35</v>
       </c>
       <c r="H206" s="125">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>35</v>
       </c>
       <c r="I206" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>32</v>
       </c>
       <c r="J206" s="125">
@@ -30051,11 +30051,11 @@
         <v>931.52</v>
       </c>
       <c r="L206" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>105960.40000000001</v>
       </c>
       <c r="M206" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>3328</v>
       </c>
       <c r="N206" s="165"/>
@@ -30096,15 +30096,15 @@
         <v>122</v>
       </c>
       <c r="G207" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0</v>
       </c>
       <c r="H207" s="125">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="I207" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0</v>
       </c>
       <c r="J207" s="125">
@@ -30116,11 +30116,11 @@
         <v>0</v>
       </c>
       <c r="L207" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0</v>
       </c>
       <c r="M207" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0</v>
       </c>
       <c r="N207" s="19"/>
@@ -30161,15 +30161,15 @@
         <v>35</v>
       </c>
       <c r="G208" s="125">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>4</v>
       </c>
       <c r="H208" s="125">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>4</v>
       </c>
       <c r="I208" s="125">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>4</v>
       </c>
       <c r="J208" s="125">
@@ -30181,11 +30181,11 @@
         <v>101.6</v>
       </c>
       <c r="L208" s="125">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>10566.4</v>
       </c>
       <c r="M208" s="125">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>416</v>
       </c>
       <c r="N208" s="19"/>
@@ -30226,27 +30226,27 @@
       </c>
       <c r="F209" s="119"/>
       <c r="G209" s="119">
-        <f t="shared" ref="G209:L209" si="178">SUM(G203:G208)</f>
+        <f t="shared" ref="G209:L209" si="179">SUM(G203:G208)</f>
         <v>316</v>
       </c>
       <c r="H209" s="119">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>318</v>
       </c>
       <c r="I209" s="119">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>229</v>
       </c>
       <c r="J209" s="119">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>12520.68</v>
       </c>
       <c r="K209" s="119">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>8852.49</v>
       </c>
       <c r="L209" s="119">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>1302150.7199999997</v>
       </c>
       <c r="M209" s="123">
@@ -30301,7 +30301,7 @@
         <v>38</v>
       </c>
       <c r="G210" s="321">
-        <f t="shared" ref="G210:G215" si="179">D210+E210*2</f>
+        <f t="shared" ref="G210:G215" si="180">D210+E210*2</f>
         <v>75</v>
       </c>
       <c r="H210" s="116">
@@ -30309,7 +30309,7 @@
         <v>75</v>
       </c>
       <c r="I210" s="322">
-        <f t="shared" ref="I210:I215" si="180">D210+E210</f>
+        <f t="shared" ref="I210:I215" si="181">D210+E210</f>
         <v>72</v>
       </c>
       <c r="J210" s="322">
@@ -30321,11 +30321,11 @@
         <v>3105.36</v>
       </c>
       <c r="L210" s="116">
-        <f t="shared" ref="L210:L215" si="181">J210*104</f>
+        <f t="shared" ref="L210:L215" si="182">J210*104</f>
         <v>336414</v>
       </c>
       <c r="M210" s="116">
-        <f t="shared" ref="M210:M215" si="182">I210*104</f>
+        <f t="shared" ref="M210:M215" si="183">I210*104</f>
         <v>7488</v>
       </c>
       <c r="N210" s="19"/>
@@ -30366,15 +30366,15 @@
         <v>52</v>
       </c>
       <c r="G211" s="321">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>76</v>
       </c>
       <c r="H211" s="116">
-        <f t="shared" ref="H211:H215" si="183">B211+C211*2</f>
+        <f t="shared" ref="H211:H215" si="184">B211+C211*2</f>
         <v>75</v>
       </c>
       <c r="I211" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>75</v>
       </c>
       <c r="J211" s="116">
@@ -30386,11 +30386,11 @@
         <v>3234.75</v>
       </c>
       <c r="L211" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>340899.52</v>
       </c>
       <c r="M211" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>7800</v>
       </c>
       <c r="N211" s="19"/>
@@ -30431,15 +30431,15 @@
         <v>36</v>
       </c>
       <c r="G212" s="321">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="H212" s="116">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="I212" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="J212" s="116">
@@ -30451,11 +30451,11 @@
         <v>0</v>
       </c>
       <c r="L212" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="M212" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="N212" s="19"/>
@@ -30496,15 +30496,15 @@
         <v>53</v>
       </c>
       <c r="G213" s="321">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="H213" s="116">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="I213" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="J213" s="116">
@@ -30516,11 +30516,11 @@
         <v>0</v>
       </c>
       <c r="L213" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="M213" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="N213" s="19"/>
@@ -30561,15 +30561,15 @@
         <v>122</v>
       </c>
       <c r="G214" s="321">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="H214" s="116">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="I214" s="116">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="J214" s="323">
@@ -30581,11 +30581,11 @@
         <v>0</v>
       </c>
       <c r="L214" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="M214" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="N214" s="19"/>
@@ -30626,15 +30626,15 @@
         <v>35</v>
       </c>
       <c r="G215" s="321">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v>0</v>
       </c>
       <c r="H215" s="116">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>0</v>
       </c>
       <c r="I215" s="324">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v>0</v>
       </c>
       <c r="J215" s="324">
@@ -30646,11 +30646,11 @@
         <v>0</v>
       </c>
       <c r="L215" s="116">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0</v>
       </c>
       <c r="M215" s="116">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>0</v>
       </c>
       <c r="N215" s="19"/>
@@ -30691,31 +30691,31 @@
       </c>
       <c r="F216" s="119"/>
       <c r="G216" s="119">
-        <f t="shared" ref="G216:M216" si="184">SUM(G210:G215)</f>
+        <f t="shared" ref="G216:M216" si="185">SUM(G210:G215)</f>
         <v>151</v>
       </c>
       <c r="H216" s="119">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>150</v>
       </c>
       <c r="I216" s="119">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>147</v>
       </c>
       <c r="J216" s="119">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>6512.63</v>
       </c>
       <c r="K216" s="119">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>6340.1100000000006</v>
       </c>
       <c r="L216" s="119">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>677313.52</v>
       </c>
       <c r="M216" s="119">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>15288</v>
       </c>
       <c r="N216" s="123">
@@ -30766,7 +30766,7 @@
         <v>38</v>
       </c>
       <c r="G217" s="218">
-        <f t="shared" ref="G217:G222" si="185">D217+E217*2</f>
+        <f t="shared" ref="G217:G222" si="186">D217+E217*2</f>
         <v>57</v>
       </c>
       <c r="H217" s="218">
@@ -30774,7 +30774,7 @@
         <v>57</v>
       </c>
       <c r="I217" s="218">
-        <f t="shared" ref="I217:I222" si="186">D217+E217</f>
+        <f t="shared" ref="I217:I222" si="187">D217+E217</f>
         <v>54</v>
       </c>
       <c r="J217" s="218">
@@ -30786,11 +30786,11 @@
         <v>2329.02</v>
       </c>
       <c r="L217" s="218">
-        <f t="shared" ref="L217:L222" si="187">J217*104</f>
+        <f t="shared" ref="L217:L222" si="188">J217*104</f>
         <v>255674.64000000004</v>
       </c>
       <c r="M217" s="218">
-        <f t="shared" ref="M217:M222" si="188">I217*104</f>
+        <f t="shared" ref="M217:M222" si="189">I217*104</f>
         <v>5616</v>
       </c>
       <c r="N217" s="19"/>
@@ -30832,15 +30832,15 @@
         <v>52</v>
       </c>
       <c r="G218" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>57</v>
       </c>
       <c r="H218" s="218">
-        <f t="shared" ref="H218:H222" si="189">B218+C218*2</f>
+        <f t="shared" ref="H218:H222" si="190">B218+C218*2</f>
         <v>57</v>
       </c>
       <c r="I218" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>57</v>
       </c>
       <c r="J218" s="218">
@@ -30852,11 +30852,11 @@
         <v>2458.4100000000003</v>
       </c>
       <c r="L218" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>255674.64000000004</v>
       </c>
       <c r="M218" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>5928</v>
       </c>
       <c r="N218" s="19"/>
@@ -30898,15 +30898,15 @@
         <v>36</v>
       </c>
       <c r="G219" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="H219" s="218">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="I219" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J219" s="218">
@@ -30918,11 +30918,11 @@
         <v>0</v>
       </c>
       <c r="L219" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="M219" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="N219" s="19"/>
@@ -30964,15 +30964,15 @@
         <v>53</v>
       </c>
       <c r="G220" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="H220" s="218">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="I220" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J220" s="218">
@@ -30984,11 +30984,11 @@
         <v>0</v>
       </c>
       <c r="L220" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="M220" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="N220" s="19"/>
@@ -31030,15 +31030,15 @@
         <v>122</v>
       </c>
       <c r="G221" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="H221" s="218">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="I221" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J221" s="218">
@@ -31050,11 +31050,11 @@
         <v>0</v>
       </c>
       <c r="L221" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="M221" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="N221" s="19"/>
@@ -31096,15 +31096,15 @@
         <v>35</v>
       </c>
       <c r="G222" s="218">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0</v>
       </c>
       <c r="H222" s="218">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0</v>
       </c>
       <c r="I222" s="218">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0</v>
       </c>
       <c r="J222" s="218">
@@ -31116,11 +31116,11 @@
         <v>0</v>
       </c>
       <c r="L222" s="218">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
       <c r="M222" s="218">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0</v>
       </c>
       <c r="N222" s="19"/>
@@ -31162,27 +31162,27 @@
       </c>
       <c r="F223" s="119"/>
       <c r="G223" s="119">
-        <f t="shared" ref="G223:L223" si="190">SUM(G217:G222)</f>
+        <f t="shared" ref="G223:L223" si="191">SUM(G217:G222)</f>
         <v>114</v>
       </c>
       <c r="H223" s="119">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>114</v>
       </c>
       <c r="I223" s="119">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>111</v>
       </c>
       <c r="J223" s="119">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>4916.8200000000006</v>
       </c>
       <c r="K223" s="119">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>4787.43</v>
       </c>
       <c r="L223" s="119">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>511349.28000000009</v>
       </c>
       <c r="M223" s="123">
@@ -31218,38 +31218,38 @@
     <row r="224" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="225" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225"/>
-      <c r="B225" s="367" t="s">
+      <c r="B225" s="354" t="s">
         <v>56</v>
       </c>
-      <c r="C225" s="368"/>
-      <c r="D225" s="368"/>
-      <c r="E225" s="368"/>
-      <c r="F225" s="368"/>
-      <c r="G225" s="369"/>
+      <c r="C225" s="355"/>
+      <c r="D225" s="355"/>
+      <c r="E225" s="355"/>
+      <c r="F225" s="355"/>
+      <c r="G225" s="356"/>
       <c r="H225" s="290"/>
-      <c r="I225" s="367" t="s">
+      <c r="I225" s="354" t="s">
         <v>57</v>
       </c>
-      <c r="J225" s="368"/>
-      <c r="K225" s="368"/>
-      <c r="L225" s="368"/>
-      <c r="M225" s="368"/>
-      <c r="N225" s="369"/>
-      <c r="P225" s="362" t="s">
+      <c r="J225" s="355"/>
+      <c r="K225" s="355"/>
+      <c r="L225" s="355"/>
+      <c r="M225" s="355"/>
+      <c r="N225" s="356"/>
+      <c r="P225" s="375" t="s">
         <v>139</v>
       </c>
-      <c r="Q225" s="362"/>
-      <c r="R225" s="362"/>
-      <c r="S225" s="363"/>
-      <c r="T225" s="359" t="s">
+      <c r="Q225" s="375"/>
+      <c r="R225" s="375"/>
+      <c r="S225" s="376"/>
+      <c r="T225" s="372" t="s">
         <v>142</v>
       </c>
-      <c r="U225" s="360"/>
-      <c r="V225" s="361"/>
-      <c r="W225" s="350" t="s">
+      <c r="U225" s="373"/>
+      <c r="V225" s="374"/>
+      <c r="W225" s="364" t="s">
         <v>143</v>
       </c>
-      <c r="X225" s="350" t="s">
+      <c r="X225" s="364" t="s">
         <v>162</v>
       </c>
     </row>
@@ -31315,23 +31315,23 @@
       <c r="V226" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W226" s="351"/>
-      <c r="X226" s="351"/>
+      <c r="W226" s="365"/>
+      <c r="X226" s="365"/>
     </row>
     <row r="227" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B227" s="114">
-        <f t="shared" ref="B227:C229" si="191">B5+B12+B19+B26+B33+B40+B47+B56+B63+B70+B77+B84+B91+B98+B105+B112+B119+B126+B133+B140+B147+B154+B161+B168+B175+B182+B189+B196+B203+B210+B217</f>
+        <f t="shared" ref="B227:C229" si="192">B5+B12+B19+B26+B33+B40+B47+B56+B63+B70+B77+B84+B91+B98+B105+B112+B119+B126+B133+B140+B147+B154+B161+B168+B175+B182+B189+B196+B203+B210+B217</f>
         <v>1410</v>
       </c>
       <c r="C227" s="114">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>829</v>
       </c>
       <c r="D227" s="114">
-        <f t="shared" ref="D227:D232" si="192">B227+C227</f>
+        <f t="shared" ref="D227:D232" si="193">B227+C227</f>
         <v>2239</v>
       </c>
       <c r="E227" s="139">
@@ -31343,20 +31343,20 @@
         <v>132322.84000000003</v>
       </c>
       <c r="G227" s="139">
-        <f t="shared" ref="G227:G232" si="193">F227*104</f>
+        <f t="shared" ref="G227:G232" si="194">F227*104</f>
         <v>13761575.360000003</v>
       </c>
       <c r="H227" s="139"/>
       <c r="I227" s="114">
-        <f t="shared" ref="I227:J230" si="194">D5+D12+D26+D33+D40+D47+D56+D63+D70+D77+D84+D91+D98+D105+D112+D119+D126+D133+D140+D147+D154+D161+D168+D175+D182+D189+D196+D203+D210+D217+D19</f>
+        <f t="shared" ref="I227:J230" si="195">D5+D12+D26+D33+D40+D47+D56+D63+D70+D77+D84+D91+D98+D105+D112+D119+D126+D133+D140+D147+D154+D161+D168+D175+D182+D189+D196+D203+D210+D217+D19</f>
         <v>1409</v>
       </c>
       <c r="J227" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>822</v>
       </c>
       <c r="K227" s="114">
-        <f t="shared" ref="K227:K232" si="195">I227+J227</f>
+        <f t="shared" ref="K227:K232" si="196">I227+J227</f>
         <v>2231</v>
       </c>
       <c r="L227" s="139">
@@ -31368,7 +31368,7 @@
         <v>131675.89000000001</v>
       </c>
       <c r="N227" s="139">
-        <f t="shared" ref="N227:N232" si="196">M227*104</f>
+        <f t="shared" ref="N227:N232" si="197">M227*104</f>
         <v>13694292.560000002</v>
       </c>
       <c r="O227" s="124"/>
@@ -31402,7 +31402,7 @@
       </c>
       <c r="W227" s="231">
         <f>W11+W18+W25+W32+W39+W46+W55+W62+W69+W76+W83+W90+W97+W104+W111+W118+W125+W132+W139+W146+W153+W160+W167+W174+W181+W188+W195+W202+W209+W216+W223</f>
-        <v>302570.24000000005</v>
+        <v>302612.10000000009</v>
       </c>
       <c r="X227" s="231">
         <f>X11+X18+X25+X32+X39+X46+X55+X62+X69+X76+X83+X90+X97+X104+X111+X118+X125+X132+X139+X146+X153+X160+X167+X174+X181+X188+X195+X202+X209+X216+X223</f>
@@ -31414,15 +31414,15 @@
         <v>52</v>
       </c>
       <c r="B228" s="114">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>1444</v>
       </c>
       <c r="C228" s="114">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>812</v>
       </c>
       <c r="D228" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>2256</v>
       </c>
       <c r="E228" s="139">
@@ -31434,24 +31434,24 @@
         <v>132322.84000000003</v>
       </c>
       <c r="G228" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>13761575.360000003</v>
       </c>
       <c r="H228" s="139"/>
       <c r="I228" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>1437</v>
       </c>
       <c r="J228" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>810</v>
       </c>
       <c r="K228" s="114">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>2247</v>
       </c>
       <c r="L228" s="139">
-        <f t="shared" ref="L228" si="197">K228*43.13</f>
+        <f t="shared" ref="L228" si="198">K228*43.13</f>
         <v>96913.11</v>
       </c>
       <c r="M228" s="139">
@@ -31459,7 +31459,7 @@
         <v>131848.41</v>
       </c>
       <c r="N228" s="139">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>13712234.640000001</v>
       </c>
       <c r="O228" s="124"/>
@@ -31471,15 +31471,15 @@
         <v>36</v>
       </c>
       <c r="B229" s="114">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>627</v>
       </c>
       <c r="C229" s="114">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>57</v>
       </c>
       <c r="D229" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>684</v>
       </c>
       <c r="E229" s="139">
@@ -31491,20 +31491,20 @@
         <v>21570.510000000002</v>
       </c>
       <c r="G229" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>2243333.04</v>
       </c>
       <c r="H229" s="139"/>
       <c r="I229" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>626</v>
       </c>
       <c r="J229" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>44</v>
       </c>
       <c r="K229" s="114">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>670</v>
       </c>
       <c r="L229" s="139">
@@ -31516,7 +31516,7 @@
         <v>20784.54</v>
       </c>
       <c r="N229" s="139">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>2161592.16</v>
       </c>
       <c r="O229" s="124"/>
@@ -31535,7 +31535,7 @@
         <v>57</v>
       </c>
       <c r="D230" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>608</v>
       </c>
       <c r="E230" s="139">
@@ -31547,20 +31547,20 @@
         <v>19358.150000000001</v>
       </c>
       <c r="G230" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>2013247.6</v>
       </c>
       <c r="H230" s="139"/>
       <c r="I230" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>554</v>
       </c>
       <c r="J230" s="114">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v>44</v>
       </c>
       <c r="K230" s="114">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>598</v>
       </c>
       <c r="L230" s="139">
@@ -31572,7 +31572,7 @@
         <v>18688.62</v>
       </c>
       <c r="N230" s="139">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>1943616.48</v>
       </c>
       <c r="O230" s="124"/>
@@ -31594,7 +31594,7 @@
         <v>0</v>
       </c>
       <c r="D231" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0</v>
       </c>
       <c r="E231" s="139">
@@ -31606,7 +31606,7 @@
         <v>0</v>
       </c>
       <c r="G231" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0</v>
       </c>
       <c r="H231" s="139"/>
@@ -31619,7 +31619,7 @@
         <v>0</v>
       </c>
       <c r="K231" s="114">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>1</v>
       </c>
       <c r="L231" s="139">
@@ -31631,7 +31631,7 @@
         <v>25.4</v>
       </c>
       <c r="N231" s="139">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>2641.6</v>
       </c>
       <c r="O231" s="124"/>
@@ -31650,7 +31650,7 @@
         <v>0</v>
       </c>
       <c r="D232" s="114">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>76</v>
       </c>
       <c r="E232" s="139">
@@ -31662,7 +31662,7 @@
         <v>1930.3999999999999</v>
       </c>
       <c r="G232" s="139">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>200761.59999999998</v>
       </c>
       <c r="H232" s="139"/>
@@ -31675,7 +31675,7 @@
         <v>0</v>
       </c>
       <c r="K232" s="114">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>76</v>
       </c>
       <c r="L232" s="139">
@@ -31687,7 +31687,7 @@
         <v>1930.3999999999999</v>
       </c>
       <c r="N232" s="139">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>200761.59999999998</v>
       </c>
       <c r="O232" s="124"/>
@@ -31826,10 +31826,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="375" t="s">
+      <c r="B237" s="352" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="376"/>
+      <c r="C237" s="353"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -32012,14 +32012,16 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B225:G225"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="X225:X226"/>
+    <mergeCell ref="W225:W226"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T225:V225"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="P225:S225"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="M3:M4"/>
@@ -32033,16 +32035,14 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="X225:X226"/>
-    <mergeCell ref="W225:W226"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T225:V225"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="P225:S225"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B225:G225"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:D31 D47:D54">
     <cfRule type="expression" dxfId="32" priority="28">
@@ -41245,6 +41245,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="AV1:AW1"/>
@@ -41261,22 +41277,6 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="BL1:BM1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AZ1:BA1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45395,15 +45395,15 @@
       </c>
       <c r="D10" s="312">
         <f>'KM-Servicio'!W55</f>
-        <v>11348.49</v>
+        <v>11390.35</v>
       </c>
       <c r="E10" s="312">
         <f t="shared" si="1"/>
-        <v>64865.1</v>
+        <v>64906.96</v>
       </c>
       <c r="F10" s="313">
         <f>'KM-Servicio'!O55</f>
-        <v>92.9366145278847</v>
+        <v>93.279420194906237</v>
       </c>
       <c r="G10" s="314">
         <f>SUM('KM-Servicio'!B55:C55)</f>
@@ -45441,7 +45441,7 @@
       </c>
       <c r="E11" s="312">
         <f t="shared" si="1"/>
-        <v>77286</v>
+        <v>77327.86</v>
       </c>
       <c r="F11" s="313">
         <f>'KM-Servicio'!O62</f>
@@ -45483,7 +45483,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>83755.5</v>
+        <v>83797.36</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O69</f>
@@ -45525,7 +45525,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>88672.320000000007</v>
+        <v>88714.180000000008</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O76</f>
@@ -45567,7 +45567,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>101140.31000000001</v>
+        <v>101182.17000000001</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O83</f>
@@ -45609,7 +45609,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>113508.02000000002</v>
+        <v>113549.88000000002</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O90</f>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="E16" s="312">
         <f t="shared" si="1"/>
-        <v>125946.65000000002</v>
+        <v>125988.51000000002</v>
       </c>
       <c r="F16" s="313">
         <f>'KM-Servicio'!O97</f>
@@ -45693,7 +45693,7 @@
       </c>
       <c r="E17" s="312">
         <f t="shared" si="1"/>
-        <v>138467.83000000002</v>
+        <v>138509.69000000003</v>
       </c>
       <c r="F17" s="313">
         <f>'KM-Servicio'!O104</f>
@@ -45735,7 +45735,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>151042.20000000001</v>
+        <v>151084.06000000003</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O111</f>
@@ -45777,7 +45777,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>157511.70000000001</v>
+        <v>157553.56000000003</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O118</f>
@@ -45818,7 +45818,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>162428.52000000002</v>
+        <v>162470.38000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O125</f>
@@ -45860,7 +45860,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>174669.48</v>
+        <v>174711.34000000003</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O132</f>
@@ -45902,7 +45902,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>187000.41</v>
+        <v>187042.27000000002</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O139</f>
@@ -45944,7 +45944,7 @@
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>199298.27000000002</v>
+        <v>199340.13000000003</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O146</f>
@@ -45986,7 +45986,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>205405.00000000003</v>
+        <v>205446.86000000004</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O153</f>
@@ -46028,7 +46028,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>217804.46000000002</v>
+        <v>217846.32000000004</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O160</f>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>224273.96000000002</v>
+        <v>224315.82000000004</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O167</f>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>229128.65000000002</v>
+        <v>229170.51000000004</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O174</f>
@@ -46154,7 +46154,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>241427.83000000002</v>
+        <v>241469.69000000003</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O181</f>
@@ -46196,7 +46196,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>253913.55000000002</v>
+        <v>253955.41000000003</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O188</f>
@@ -46238,7 +46238,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>266298.99</v>
+        <v>266340.85000000003</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O195</f>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>278719.89</v>
+        <v>278761.75000000006</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O202</f>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>291140.79000000004</v>
+        <v>291182.65000000008</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O209</f>
@@ -46364,7 +46364,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>297653.42000000004</v>
+        <v>297695.28000000009</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -46408,7 +46408,7 @@
       </c>
       <c r="E34" s="12">
         <f t="shared" ref="E34" si="3">D34+E33</f>
-        <v>302570.24000000005</v>
+        <v>302612.10000000009</v>
       </c>
       <c r="F34" s="171">
         <f>'KM-Servicio'!O223</f>
@@ -46464,15 +46464,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>302570.24000000005</v>
+        <v>302612.10000000009</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4789836.2700000005</v>
+        <v>4790882.7700000014</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>96.850355369701234</v>
+        <v>96.86141361702451</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -46516,12 +46516,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="381" t="s">
+      <c r="A3" s="382" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="382"/>
-      <c r="C3" s="382"/>
-      <c r="D3" s="383"/>
+      <c r="B3" s="383"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="384"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -46667,12 +46667,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="384" t="s">
+      <c r="A13" s="385" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="385"/>
-      <c r="C13" s="385"/>
-      <c r="D13" s="386"/>
+      <c r="B13" s="386"/>
+      <c r="C13" s="386"/>
+      <c r="D13" s="387"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -46719,8 +46719,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="390"/>
-      <c r="H16" s="390"/>
+      <c r="G16" s="381"/>
+      <c r="H16" s="381"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -46735,8 +46735,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="390"/>
-      <c r="H17" s="390"/>
+      <c r="G17" s="381"/>
+      <c r="H17" s="381"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -46751,8 +46751,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="390"/>
-      <c r="H18" s="390"/>
+      <c r="G18" s="381"/>
+      <c r="H18" s="381"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -46766,8 +46766,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="390"/>
-      <c r="H19" s="390"/>
+      <c r="G19" s="381"/>
+      <c r="H19" s="381"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -46781,8 +46781,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="390"/>
-      <c r="H20" s="390"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -46796,8 +46796,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="390"/>
-      <c r="H21" s="390"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -46822,9 +46822,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="387"/>
-      <c r="C23" s="388"/>
-      <c r="D23" s="389"/>
+      <c r="B23" s="388"/>
+      <c r="C23" s="389"/>
+      <c r="D23" s="390"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -46836,10 +46836,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="384"/>
-      <c r="B24" s="385"/>
-      <c r="C24" s="385"/>
-      <c r="D24" s="386"/>
+      <c r="A24" s="385"/>
+      <c r="B24" s="386"/>
+      <c r="C24" s="386"/>
+      <c r="D24" s="387"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -46952,9 +46952,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="387"/>
-      <c r="C34" s="388"/>
-      <c r="D34" s="389"/>
+      <c r="B34" s="388"/>
+      <c r="C34" s="389"/>
+      <c r="D34" s="390"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -47087,17 +47087,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -47352,15 +47352,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
@@ -47371,6 +47362,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47394,14 +47394,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -47412,4 +47404,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Mayo 2026.xlsx
+++ b/data/umr/Resumen UMR Mayo 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C3AA43E-C44D-4BB3-AA5F-DECD82765385}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D08D33EC-A92C-434E-AD80-C1C433ACA2DC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4841,48 +4841,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4896,6 +4854,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4922,6 +4883,45 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4934,9 +4934,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4964,6 +4961,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -16261,14 +16261,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="373" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="351" t="s">
+      <c r="C2" s="373"/>
+      <c r="D2" s="374" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="351"/>
+      <c r="E2" s="374"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -16359,59 +16359,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="350" t="s">
+      <c r="B3" s="373" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="351" t="s">
+      <c r="C3" s="373"/>
+      <c r="D3" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="351"/>
-      <c r="F3" s="357" t="s">
+      <c r="E3" s="374"/>
+      <c r="F3" s="366" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="357" t="s">
+      <c r="G3" s="366" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="357" t="s">
+      <c r="H3" s="366" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="357" t="s">
+      <c r="I3" s="366" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="357" t="s">
+      <c r="J3" s="366" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="357" t="s">
+      <c r="K3" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="357" t="s">
+      <c r="L3" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="357" t="s">
+      <c r="M3" s="366" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="361" t="s">
+      <c r="N3" s="355" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="361" t="s">
+      <c r="O3" s="355" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="368"/>
-      <c r="Q3" s="369" t="s">
+      <c r="P3" s="354"/>
+      <c r="Q3" s="356" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="370"/>
-      <c r="S3" s="371"/>
-      <c r="T3" s="372" t="s">
+      <c r="R3" s="357"/>
+      <c r="S3" s="358"/>
+      <c r="T3" s="359" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="373"/>
-      <c r="V3" s="374"/>
-      <c r="W3" s="366" t="s">
+      <c r="U3" s="360"/>
+      <c r="V3" s="361"/>
+      <c r="W3" s="352" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="366" t="s">
+      <c r="X3" s="352" t="s">
         <v>162</v>
       </c>
     </row>
@@ -16429,17 +16429,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="357"/>
-      <c r="G4" s="358"/>
-      <c r="H4" s="358"/>
-      <c r="I4" s="357"/>
-      <c r="J4" s="357"/>
-      <c r="K4" s="357"/>
-      <c r="L4" s="357"/>
-      <c r="M4" s="357"/>
-      <c r="N4" s="361"/>
-      <c r="O4" s="361"/>
-      <c r="P4" s="368"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="372"/>
+      <c r="H4" s="372"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
+      <c r="L4" s="366"/>
+      <c r="M4" s="366"/>
+      <c r="N4" s="355"/>
+      <c r="O4" s="355"/>
+      <c r="P4" s="354"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -16458,8 +16458,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="367"/>
-      <c r="X4" s="367"/>
+      <c r="W4" s="353"/>
+      <c r="X4" s="353"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -17927,7 +17927,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="360" t="s">
+      <c r="A27" s="365" t="s">
         <v>183</v>
       </c>
       <c r="B27" s="295">
@@ -17996,7 +17996,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="360"/>
+      <c r="A28" s="365"/>
       <c r="B28" s="295">
         <v>33</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="360"/>
+      <c r="A29" s="365"/>
       <c r="B29" s="295">
         <v>29</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="360"/>
+      <c r="A30" s="365"/>
       <c r="B30" s="295">
         <v>0</v>
       </c>
@@ -18192,7 +18192,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="360"/>
+      <c r="A31" s="365"/>
       <c r="B31" s="295">
         <v>4</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="359" t="s">
+      <c r="A41" s="364" t="s">
         <v>184</v>
       </c>
       <c r="B41" s="295">
@@ -18936,7 +18936,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="359"/>
+      <c r="A42" s="364"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -19010,7 +19010,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="359"/>
+      <c r="A43" s="364"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -19082,7 +19082,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="359"/>
+      <c r="A44" s="364"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -19154,7 +19154,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="359"/>
+      <c r="A45" s="364"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="AF47" s="255"/>
     </row>
     <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="360" t="s">
+      <c r="A48" s="365" t="s">
         <v>185</v>
       </c>
       <c r="B48" s="295">
@@ -19448,7 +19448,7 @@
       </c>
     </row>
     <row r="49" spans="1:65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="360"/>
+      <c r="A49" s="365"/>
       <c r="B49" s="295">
         <v>33</v>
       </c>
@@ -19513,7 +19513,7 @@
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A50" s="360"/>
+      <c r="A50" s="365"/>
       <c r="B50" s="295">
         <v>29</v>
       </c>
@@ -19567,8 +19567,8 @@
       <c r="U50" s="189"/>
       <c r="V50" s="189"/>
       <c r="W50" s="182">
-        <f>J50-0.72-25.4</f>
-        <v>788.95999999999992</v>
+        <f>J50</f>
+        <v>815.07999999999993</v>
       </c>
       <c r="X50" s="182">
         <f>H50*$M$1</f>
@@ -19576,7 +19576,7 @@
       </c>
     </row>
     <row r="51" spans="1:65" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="360"/>
+      <c r="A51" s="365"/>
       <c r="B51" s="295">
         <v>0</v>
       </c>
@@ -19640,7 +19640,7 @@
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A52" s="360"/>
+      <c r="A52" s="365"/>
       <c r="B52" s="295">
         <v>4</v>
       </c>
@@ -19848,7 +19848,7 @@
         <v>11548</v>
       </c>
       <c r="K55" s="119">
-        <f t="shared" ref="G55:M55" si="47">SUM(K47:K52)</f>
+        <f t="shared" ref="K55:M55" si="47">SUM(K47:K52)</f>
         <v>7534.4400000000005</v>
       </c>
       <c r="L55" s="118">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="O55" s="21">
         <f>(W55/N55)*100</f>
-        <v>93.279420194906237</v>
+        <v>93.493325689951689</v>
       </c>
       <c r="P55" s="192"/>
       <c r="Q55" s="181"/>
@@ -19876,7 +19876,7 @@
       <c r="V55" s="181"/>
       <c r="W55" s="193">
         <f>SUM(W47:W54)</f>
-        <v>11390.35</v>
+        <v>11416.470000000001</v>
       </c>
       <c r="X55" s="193">
         <f>SUM(X47:X52)</f>
@@ -26100,7 +26100,7 @@
       </c>
     </row>
     <row r="148" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="363" t="s">
+      <c r="A148" s="371" t="s">
         <v>189</v>
       </c>
       <c r="B148" s="218">
@@ -26169,7 +26169,7 @@
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A149" s="363"/>
+      <c r="A149" s="371"/>
       <c r="B149" s="218">
         <v>0</v>
       </c>
@@ -26234,7 +26234,7 @@
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A150" s="363"/>
+      <c r="A150" s="371"/>
       <c r="B150" s="218">
         <v>0</v>
       </c>
@@ -26299,7 +26299,7 @@
       </c>
     </row>
     <row r="151" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="363"/>
+      <c r="A151" s="371"/>
       <c r="B151" s="218">
         <v>0</v>
       </c>
@@ -26364,7 +26364,7 @@
       </c>
     </row>
     <row r="152" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="363"/>
+      <c r="A152" s="371"/>
       <c r="B152" s="218">
         <v>0</v>
       </c>
@@ -27978,7 +27978,7 @@
       </c>
     </row>
     <row r="176" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="362" t="s">
+      <c r="A176" s="370" t="s">
         <v>188</v>
       </c>
       <c r="B176" s="295">
@@ -28048,7 +28048,7 @@
       <c r="Y176" s="172"/>
     </row>
     <row r="177" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A177" s="362"/>
+      <c r="A177" s="370"/>
       <c r="B177" s="295">
         <v>33</v>
       </c>
@@ -28115,7 +28115,7 @@
       </c>
     </row>
     <row r="178" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="362"/>
+      <c r="A178" s="370"/>
       <c r="B178" s="295">
         <v>29</v>
       </c>
@@ -28180,7 +28180,7 @@
       </c>
     </row>
     <row r="179" spans="1:30" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="362"/>
+      <c r="A179" s="370"/>
       <c r="B179" s="295">
         <v>0</v>
       </c>
@@ -28245,7 +28245,7 @@
       </c>
     </row>
     <row r="180" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="362"/>
+      <c r="A180" s="370"/>
       <c r="B180" s="295">
         <v>4</v>
       </c>
@@ -31218,38 +31218,38 @@
     <row r="224" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="225" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225"/>
-      <c r="B225" s="354" t="s">
+      <c r="B225" s="367" t="s">
         <v>56</v>
       </c>
-      <c r="C225" s="355"/>
-      <c r="D225" s="355"/>
-      <c r="E225" s="355"/>
-      <c r="F225" s="355"/>
-      <c r="G225" s="356"/>
+      <c r="C225" s="368"/>
+      <c r="D225" s="368"/>
+      <c r="E225" s="368"/>
+      <c r="F225" s="368"/>
+      <c r="G225" s="369"/>
       <c r="H225" s="290"/>
-      <c r="I225" s="354" t="s">
+      <c r="I225" s="367" t="s">
         <v>57</v>
       </c>
-      <c r="J225" s="355"/>
-      <c r="K225" s="355"/>
-      <c r="L225" s="355"/>
-      <c r="M225" s="355"/>
-      <c r="N225" s="356"/>
-      <c r="P225" s="375" t="s">
+      <c r="J225" s="368"/>
+      <c r="K225" s="368"/>
+      <c r="L225" s="368"/>
+      <c r="M225" s="368"/>
+      <c r="N225" s="369"/>
+      <c r="P225" s="362" t="s">
         <v>139</v>
       </c>
-      <c r="Q225" s="375"/>
-      <c r="R225" s="375"/>
-      <c r="S225" s="376"/>
-      <c r="T225" s="372" t="s">
+      <c r="Q225" s="362"/>
+      <c r="R225" s="362"/>
+      <c r="S225" s="363"/>
+      <c r="T225" s="359" t="s">
         <v>142</v>
       </c>
-      <c r="U225" s="373"/>
-      <c r="V225" s="374"/>
-      <c r="W225" s="364" t="s">
+      <c r="U225" s="360"/>
+      <c r="V225" s="361"/>
+      <c r="W225" s="350" t="s">
         <v>143</v>
       </c>
-      <c r="X225" s="364" t="s">
+      <c r="X225" s="350" t="s">
         <v>162</v>
       </c>
     </row>
@@ -31315,8 +31315,8 @@
       <c r="V226" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W226" s="365"/>
-      <c r="X226" s="365"/>
+      <c r="W226" s="351"/>
+      <c r="X226" s="351"/>
     </row>
     <row r="227" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
@@ -31402,7 +31402,7 @@
       </c>
       <c r="W227" s="231">
         <f>W11+W18+W25+W32+W39+W46+W55+W62+W69+W76+W83+W90+W97+W104+W111+W118+W125+W132+W139+W146+W153+W160+W167+W174+W181+W188+W195+W202+W209+W216+W223</f>
-        <v>302612.10000000009</v>
+        <v>302638.22000000009</v>
       </c>
       <c r="X227" s="231">
         <f>X11+X18+X25+X32+X39+X46+X55+X62+X69+X76+X83+X90+X97+X104+X111+X118+X125+X132+X139+X146+X153+X160+X167+X174+X181+X188+X195+X202+X209+X216+X223</f>
@@ -31826,10 +31826,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="352" t="s">
+      <c r="B237" s="375" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="353"/>
+      <c r="C237" s="376"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -32012,16 +32012,14 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="X225:X226"/>
-    <mergeCell ref="W225:W226"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T225:V225"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="P225:S225"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B225:G225"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="M3:M4"/>
@@ -32035,14 +32033,16 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B225:G225"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="X225:X226"/>
+    <mergeCell ref="W225:W226"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T225:V225"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="P225:S225"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:D31 D47:D54">
     <cfRule type="expression" dxfId="32" priority="28">
@@ -41245,6 +41245,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BL1:BM1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
@@ -41261,22 +41277,6 @@
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45395,15 +45395,15 @@
       </c>
       <c r="D10" s="312">
         <f>'KM-Servicio'!W55</f>
-        <v>11390.35</v>
+        <v>11416.470000000001</v>
       </c>
       <c r="E10" s="312">
         <f t="shared" si="1"/>
-        <v>64906.96</v>
+        <v>64933.08</v>
       </c>
       <c r="F10" s="313">
         <f>'KM-Servicio'!O55</f>
-        <v>93.279420194906237</v>
+        <v>93.493325689951689</v>
       </c>
       <c r="G10" s="314">
         <f>SUM('KM-Servicio'!B55:C55)</f>
@@ -45441,7 +45441,7 @@
       </c>
       <c r="E11" s="312">
         <f t="shared" si="1"/>
-        <v>77327.86</v>
+        <v>77353.98</v>
       </c>
       <c r="F11" s="313">
         <f>'KM-Servicio'!O62</f>
@@ -45483,7 +45483,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>83797.36</v>
+        <v>83823.48</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O69</f>
@@ -45525,7 +45525,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>88714.180000000008</v>
+        <v>88740.3</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O76</f>
@@ -45567,7 +45567,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>101182.17000000001</v>
+        <v>101208.29000000001</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O83</f>
@@ -45609,7 +45609,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>113549.88000000002</v>
+        <v>113576.00000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O90</f>
@@ -45651,7 +45651,7 @@
       </c>
       <c r="E16" s="312">
         <f t="shared" si="1"/>
-        <v>125988.51000000002</v>
+        <v>126014.63000000002</v>
       </c>
       <c r="F16" s="313">
         <f>'KM-Servicio'!O97</f>
@@ -45693,7 +45693,7 @@
       </c>
       <c r="E17" s="312">
         <f t="shared" si="1"/>
-        <v>138509.69000000003</v>
+        <v>138535.81000000003</v>
       </c>
       <c r="F17" s="313">
         <f>'KM-Servicio'!O104</f>
@@ -45735,7 +45735,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>151084.06000000003</v>
+        <v>151110.18000000002</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O111</f>
@@ -45777,7 +45777,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>157553.56000000003</v>
+        <v>157579.68000000002</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O118</f>
@@ -45818,7 +45818,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>162470.38000000003</v>
+        <v>162496.50000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O125</f>
@@ -45860,7 +45860,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>174711.34000000003</v>
+        <v>174737.46000000002</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O132</f>
@@ -45902,7 +45902,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>187042.27000000002</v>
+        <v>187068.39</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O139</f>
@@ -45944,7 +45944,7 @@
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>199340.13000000003</v>
+        <v>199366.25000000003</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O146</f>
@@ -45986,7 +45986,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>205446.86000000004</v>
+        <v>205472.98000000004</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O153</f>
@@ -46028,7 +46028,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>217846.32000000004</v>
+        <v>217872.44000000003</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O160</f>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>224315.82000000004</v>
+        <v>224341.94000000003</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O167</f>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>229170.51000000004</v>
+        <v>229196.63000000003</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O174</f>
@@ -46154,7 +46154,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>241469.69000000003</v>
+        <v>241495.81000000003</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O181</f>
@@ -46196,7 +46196,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>253955.41000000003</v>
+        <v>253981.53000000003</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O188</f>
@@ -46238,7 +46238,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>266340.85000000003</v>
+        <v>266366.97000000003</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O195</f>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>278761.75000000006</v>
+        <v>278787.87000000005</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O202</f>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>291182.65000000008</v>
+        <v>291208.77000000008</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O209</f>
@@ -46364,7 +46364,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>297695.28000000009</v>
+        <v>297721.40000000008</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -46408,7 +46408,7 @@
       </c>
       <c r="E34" s="12">
         <f t="shared" ref="E34" si="3">D34+E33</f>
-        <v>302612.10000000009</v>
+        <v>302638.22000000009</v>
       </c>
       <c r="F34" s="171">
         <f>'KM-Servicio'!O223</f>
@@ -46464,15 +46464,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>302612.10000000009</v>
+        <v>302638.22000000009</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4790882.7700000014</v>
+        <v>4791535.7700000005</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>96.86141361702451</v>
+        <v>96.86831379428402</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -46516,12 +46516,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="382" t="s">
+      <c r="A3" s="381" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="383"/>
-      <c r="C3" s="383"/>
-      <c r="D3" s="384"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="383"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -46667,12 +46667,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="385" t="s">
+      <c r="A13" s="384" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="386"/>
-      <c r="C13" s="386"/>
-      <c r="D13" s="387"/>
+      <c r="B13" s="385"/>
+      <c r="C13" s="385"/>
+      <c r="D13" s="386"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -46719,8 +46719,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="381"/>
-      <c r="H16" s="381"/>
+      <c r="G16" s="390"/>
+      <c r="H16" s="390"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -46735,8 +46735,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="381"/>
-      <c r="H17" s="381"/>
+      <c r="G17" s="390"/>
+      <c r="H17" s="390"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -46751,8 +46751,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="381"/>
-      <c r="H18" s="381"/>
+      <c r="G18" s="390"/>
+      <c r="H18" s="390"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -46766,8 +46766,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="381"/>
-      <c r="H19" s="381"/>
+      <c r="G19" s="390"/>
+      <c r="H19" s="390"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -46781,8 +46781,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="381"/>
-      <c r="H20" s="381"/>
+      <c r="G20" s="390"/>
+      <c r="H20" s="390"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -46796,8 +46796,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="381"/>
-      <c r="H21" s="381"/>
+      <c r="G21" s="390"/>
+      <c r="H21" s="390"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -46822,9 +46822,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="388"/>
-      <c r="C23" s="389"/>
-      <c r="D23" s="390"/>
+      <c r="B23" s="387"/>
+      <c r="C23" s="388"/>
+      <c r="D23" s="389"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -46836,10 +46836,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="385"/>
-      <c r="B24" s="386"/>
-      <c r="C24" s="386"/>
-      <c r="D24" s="387"/>
+      <c r="A24" s="384"/>
+      <c r="B24" s="385"/>
+      <c r="C24" s="385"/>
+      <c r="D24" s="386"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -46952,9 +46952,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="388"/>
-      <c r="C34" s="389"/>
-      <c r="D34" s="390"/>
+      <c r="B34" s="387"/>
+      <c r="C34" s="388"/>
+      <c r="D34" s="389"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -47087,17 +47087,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -47352,6 +47352,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
@@ -47362,15 +47371,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47394,6 +47394,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -47404,12 +47412,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Mayo 2026.xlsx
+++ b/data/umr/Resumen UMR Mayo 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D08D33EC-A92C-434E-AD80-C1C433ACA2DC}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A85CF6-A2E7-4BA3-9E9F-107C5E49F0DE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -4841,6 +4841,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4854,9 +4896,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4883,45 +4922,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4934,6 +4934,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4961,9 +4964,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -16261,14 +16261,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="373" t="s">
+      <c r="B2" s="350" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="373"/>
-      <c r="D2" s="374" t="s">
+      <c r="C2" s="350"/>
+      <c r="D2" s="351" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="374"/>
+      <c r="E2" s="351"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -16359,59 +16359,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="373" t="s">
+      <c r="B3" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="373"/>
-      <c r="D3" s="374" t="s">
+      <c r="C3" s="350"/>
+      <c r="D3" s="351" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="374"/>
-      <c r="F3" s="366" t="s">
+      <c r="E3" s="351"/>
+      <c r="F3" s="357" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="366" t="s">
+      <c r="G3" s="357" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="366" t="s">
+      <c r="H3" s="357" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="366" t="s">
+      <c r="I3" s="357" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="366" t="s">
+      <c r="J3" s="357" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="366" t="s">
+      <c r="K3" s="357" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="366" t="s">
+      <c r="L3" s="357" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="366" t="s">
+      <c r="M3" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="355" t="s">
+      <c r="N3" s="361" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="355" t="s">
+      <c r="O3" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="354"/>
-      <c r="Q3" s="356" t="s">
+      <c r="P3" s="368"/>
+      <c r="Q3" s="369" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="357"/>
-      <c r="S3" s="358"/>
-      <c r="T3" s="359" t="s">
+      <c r="R3" s="370"/>
+      <c r="S3" s="371"/>
+      <c r="T3" s="372" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="360"/>
-      <c r="V3" s="361"/>
-      <c r="W3" s="352" t="s">
+      <c r="U3" s="373"/>
+      <c r="V3" s="374"/>
+      <c r="W3" s="366" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="352" t="s">
+      <c r="X3" s="366" t="s">
         <v>162</v>
       </c>
     </row>
@@ -16429,17 +16429,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="366"/>
-      <c r="G4" s="372"/>
-      <c r="H4" s="372"/>
-      <c r="I4" s="366"/>
-      <c r="J4" s="366"/>
-      <c r="K4" s="366"/>
-      <c r="L4" s="366"/>
-      <c r="M4" s="366"/>
-      <c r="N4" s="355"/>
-      <c r="O4" s="355"/>
-      <c r="P4" s="354"/>
+      <c r="F4" s="357"/>
+      <c r="G4" s="358"/>
+      <c r="H4" s="358"/>
+      <c r="I4" s="357"/>
+      <c r="J4" s="357"/>
+      <c r="K4" s="357"/>
+      <c r="L4" s="357"/>
+      <c r="M4" s="357"/>
+      <c r="N4" s="361"/>
+      <c r="O4" s="361"/>
+      <c r="P4" s="368"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -16458,8 +16458,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="353"/>
-      <c r="X4" s="353"/>
+      <c r="W4" s="367"/>
+      <c r="X4" s="367"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -17927,7 +17927,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="365" t="s">
+      <c r="A27" s="360" t="s">
         <v>183</v>
       </c>
       <c r="B27" s="295">
@@ -17996,7 +17996,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="365"/>
+      <c r="A28" s="360"/>
       <c r="B28" s="295">
         <v>33</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="365"/>
+      <c r="A29" s="360"/>
       <c r="B29" s="295">
         <v>29</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="365"/>
+      <c r="A30" s="360"/>
       <c r="B30" s="295">
         <v>0</v>
       </c>
@@ -18192,7 +18192,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="365"/>
+      <c r="A31" s="360"/>
       <c r="B31" s="295">
         <v>4</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="364" t="s">
+      <c r="A41" s="359" t="s">
         <v>184</v>
       </c>
       <c r="B41" s="295">
@@ -18936,7 +18936,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="364"/>
+      <c r="A42" s="359"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -19010,7 +19010,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="364"/>
+      <c r="A43" s="359"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -19082,7 +19082,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="364"/>
+      <c r="A44" s="359"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -19154,7 +19154,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="364"/>
+      <c r="A45" s="359"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="AF47" s="255"/>
     </row>
     <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="365" t="s">
+      <c r="A48" s="360" t="s">
         <v>185</v>
       </c>
       <c r="B48" s="295">
@@ -19448,7 +19448,7 @@
       </c>
     </row>
     <row r="49" spans="1:65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="365"/>
+      <c r="A49" s="360"/>
       <c r="B49" s="295">
         <v>33</v>
       </c>
@@ -19513,7 +19513,7 @@
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A50" s="365"/>
+      <c r="A50" s="360"/>
       <c r="B50" s="295">
         <v>29</v>
       </c>
@@ -19576,7 +19576,7 @@
       </c>
     </row>
     <row r="51" spans="1:65" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="365"/>
+      <c r="A51" s="360"/>
       <c r="B51" s="295">
         <v>0</v>
       </c>
@@ -19640,7 +19640,7 @@
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A52" s="365"/>
+      <c r="A52" s="360"/>
       <c r="B52" s="295">
         <v>4</v>
       </c>
@@ -25614,7 +25614,7 @@
       <c r="O140" s="19"/>
       <c r="P140" s="146"/>
       <c r="Q140" s="183">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R140" s="183"/>
       <c r="S140" s="206"/>
@@ -25623,7 +25623,7 @@
       <c r="V140" s="228"/>
       <c r="W140" s="182">
         <f>J140-(Q140*($M$2-$K$1))-(R140*($M$2-$M$1))- (S140*($M$2-$I$2))+ (T140*($G$2))</f>
-        <v>5071.6100000000006</v>
+        <v>5053.88</v>
       </c>
       <c r="X140" s="182">
         <f>H140*$M$2</f>
@@ -26012,7 +26012,7 @@
       </c>
       <c r="O146" s="21">
         <f>(W146/N146)*100</f>
-        <v>95.80757245247743</v>
+        <v>95.669445310065441</v>
       </c>
       <c r="P146" s="192"/>
       <c r="Q146" s="181"/>
@@ -26023,7 +26023,7 @@
       <c r="V146" s="181"/>
       <c r="W146" s="193">
         <f>SUM(W140:W145)</f>
-        <v>12297.860000000002</v>
+        <v>12280.130000000001</v>
       </c>
       <c r="X146" s="193">
         <f>SUM(X140:X145)</f>
@@ -26100,7 +26100,7 @@
       </c>
     </row>
     <row r="148" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="371" t="s">
+      <c r="A148" s="363" t="s">
         <v>189</v>
       </c>
       <c r="B148" s="218">
@@ -26169,7 +26169,7 @@
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A149" s="371"/>
+      <c r="A149" s="363"/>
       <c r="B149" s="218">
         <v>0</v>
       </c>
@@ -26234,7 +26234,7 @@
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A150" s="371"/>
+      <c r="A150" s="363"/>
       <c r="B150" s="218">
         <v>0</v>
       </c>
@@ -26299,7 +26299,7 @@
       </c>
     </row>
     <row r="151" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="371"/>
+      <c r="A151" s="363"/>
       <c r="B151" s="218">
         <v>0</v>
       </c>
@@ -26364,7 +26364,7 @@
       </c>
     </row>
     <row r="152" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="371"/>
+      <c r="A152" s="363"/>
       <c r="B152" s="218">
         <v>0</v>
       </c>
@@ -27978,7 +27978,7 @@
       </c>
     </row>
     <row r="176" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="370" t="s">
+      <c r="A176" s="362" t="s">
         <v>188</v>
       </c>
       <c r="B176" s="295">
@@ -28048,7 +28048,7 @@
       <c r="Y176" s="172"/>
     </row>
     <row r="177" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A177" s="370"/>
+      <c r="A177" s="362"/>
       <c r="B177" s="295">
         <v>33</v>
       </c>
@@ -28115,7 +28115,7 @@
       </c>
     </row>
     <row r="178" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="370"/>
+      <c r="A178" s="362"/>
       <c r="B178" s="295">
         <v>29</v>
       </c>
@@ -28180,7 +28180,7 @@
       </c>
     </row>
     <row r="179" spans="1:30" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="370"/>
+      <c r="A179" s="362"/>
       <c r="B179" s="295">
         <v>0</v>
       </c>
@@ -28245,7 +28245,7 @@
       </c>
     </row>
     <row r="180" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="370"/>
+      <c r="A180" s="362"/>
       <c r="B180" s="295">
         <v>4</v>
       </c>
@@ -31218,38 +31218,38 @@
     <row r="224" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="225" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225"/>
-      <c r="B225" s="367" t="s">
+      <c r="B225" s="354" t="s">
         <v>56</v>
       </c>
-      <c r="C225" s="368"/>
-      <c r="D225" s="368"/>
-      <c r="E225" s="368"/>
-      <c r="F225" s="368"/>
-      <c r="G225" s="369"/>
+      <c r="C225" s="355"/>
+      <c r="D225" s="355"/>
+      <c r="E225" s="355"/>
+      <c r="F225" s="355"/>
+      <c r="G225" s="356"/>
       <c r="H225" s="290"/>
-      <c r="I225" s="367" t="s">
+      <c r="I225" s="354" t="s">
         <v>57</v>
       </c>
-      <c r="J225" s="368"/>
-      <c r="K225" s="368"/>
-      <c r="L225" s="368"/>
-      <c r="M225" s="368"/>
-      <c r="N225" s="369"/>
-      <c r="P225" s="362" t="s">
+      <c r="J225" s="355"/>
+      <c r="K225" s="355"/>
+      <c r="L225" s="355"/>
+      <c r="M225" s="355"/>
+      <c r="N225" s="356"/>
+      <c r="P225" s="375" t="s">
         <v>139</v>
       </c>
-      <c r="Q225" s="362"/>
-      <c r="R225" s="362"/>
-      <c r="S225" s="363"/>
-      <c r="T225" s="359" t="s">
+      <c r="Q225" s="375"/>
+      <c r="R225" s="375"/>
+      <c r="S225" s="376"/>
+      <c r="T225" s="372" t="s">
         <v>142</v>
       </c>
-      <c r="U225" s="360"/>
-      <c r="V225" s="361"/>
-      <c r="W225" s="350" t="s">
+      <c r="U225" s="373"/>
+      <c r="V225" s="374"/>
+      <c r="W225" s="364" t="s">
         <v>143</v>
       </c>
-      <c r="X225" s="350" t="s">
+      <c r="X225" s="364" t="s">
         <v>162</v>
       </c>
     </row>
@@ -31315,8 +31315,8 @@
       <c r="V226" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W226" s="351"/>
-      <c r="X226" s="351"/>
+      <c r="W226" s="365"/>
+      <c r="X226" s="365"/>
     </row>
     <row r="227" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
@@ -31374,7 +31374,7 @@
       <c r="O227" s="124"/>
       <c r="P227" s="209">
         <f>SUM(Q196,Q189,Q182,Q175,Q168,Q161,Q154,Q147,Q140,Q133,Q126,Q119,Q112,Q105,Q98,Q91,Q84,Q77,Q70,Q63,Q56,Q47,Q40,Q33,Q26,Q19,Q12,Q5,Q203,Q210,Q217)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q227" s="209">
         <f>SUM(R196,R189,R182,R175,R168,R161,R154,R147,R140,R133,R126,R119,R112,R105,R98,R91,R84,R77,R70,R63,R56,R47,R40,R33,R26,R19,R12,R5,R203,R210,R217)</f>
@@ -31402,7 +31402,7 @@
       </c>
       <c r="W227" s="231">
         <f>W11+W18+W25+W32+W39+W46+W55+W62+W69+W76+W83+W90+W97+W104+W111+W118+W125+W132+W139+W146+W153+W160+W167+W174+W181+W188+W195+W202+W209+W216+W223</f>
-        <v>302638.22000000009</v>
+        <v>302620.49000000005</v>
       </c>
       <c r="X227" s="231">
         <f>X11+X18+X25+X32+X39+X46+X55+X62+X69+X76+X83+X90+X97+X104+X111+X118+X125+X132+X139+X146+X153+X160+X167+X174+X181+X188+X195+X202+X209+X216+X223</f>
@@ -31826,10 +31826,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="375" t="s">
+      <c r="B237" s="352" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="376"/>
+      <c r="C237" s="353"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -32012,14 +32012,16 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B225:G225"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="X225:X226"/>
+    <mergeCell ref="W225:W226"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T225:V225"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="P225:S225"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="M3:M4"/>
@@ -32033,16 +32035,14 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="X225:X226"/>
-    <mergeCell ref="W225:W226"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T225:V225"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="P225:S225"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B225:G225"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:D31 D47:D54">
     <cfRule type="expression" dxfId="32" priority="28">
@@ -41245,6 +41245,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="AX1:AY1"/>
     <mergeCell ref="AV1:AW1"/>
@@ -41261,22 +41277,6 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="BL1:BM1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AZ1:BA1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43134,7 +43134,7 @@
       </c>
       <c r="V19" s="83">
         <f>'KM-Servicio'!Q140</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="83">
         <f>'KM-Servicio'!Q147</f>
@@ -43975,7 +43975,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>302573.62000000005</v>
+        <v>302555.89000000007</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -44055,7 +44055,7 @@
       </c>
       <c r="V29" s="91">
         <f>(V12*$B$12+V13*$B$13+V14*$B$14+V15*$B$15+V17*$B$17+V20*$B$20+V16*$B$16+V19*$B$19+V21*$B$21+V22*$B$22)</f>
-        <v>12297.86</v>
+        <v>12280.130000000001</v>
       </c>
       <c r="W29" s="91">
         <f t="shared" ref="W29:AD29" si="7">(W12*$B$12+W13*$B$13+W14*$B$14+W15*$B$15+W17*$B$17+W20*$B$20+W16*$B$16+W19*$B$19+W21*$B$21+W22*$B$22)</f>
@@ -44241,7 +44241,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>31467656.480000012</v>
+        <v>31465812.56000001</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="13">C29*104</f>
@@ -44321,7 +44321,7 @@
       </c>
       <c r="V31" s="91">
         <f t="shared" si="13"/>
-        <v>1278977.44</v>
+        <v>1277133.52</v>
       </c>
       <c r="W31" s="91">
         <f t="shared" si="13"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>605147.24000000011</v>
+        <v>605111.78000000014</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -44454,7 +44454,7 @@
       </c>
       <c r="V32" s="91">
         <f t="shared" si="16"/>
-        <v>24595.72</v>
+        <v>24560.260000000002</v>
       </c>
       <c r="W32" s="91">
         <f t="shared" si="16"/>
@@ -44640,7 +44640,7 @@
       </c>
       <c r="B34" s="226">
         <f>SUM(C34:AG34)</f>
-        <v>23994088.066000007</v>
+        <v>23992682.077000007</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -44720,7 +44720,7 @@
       </c>
       <c r="V34" s="91">
         <f t="shared" si="22"/>
-        <v>975220.29800000007</v>
+        <v>973814.30900000001</v>
       </c>
       <c r="W34" s="91">
         <f t="shared" si="22"/>
@@ -45940,15 +45940,15 @@
       </c>
       <c r="D23" s="312">
         <f>'KM-Servicio'!$W$146</f>
-        <v>12297.860000000002</v>
+        <v>12280.130000000001</v>
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>199366.25000000003</v>
+        <v>199348.52000000002</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O146</f>
-        <v>95.80757245247743</v>
+        <v>95.669445310065441</v>
       </c>
       <c r="G23" s="314">
         <f>SUM('KM-Servicio'!B146:C146)</f>
@@ -45960,7 +45960,7 @@
       </c>
       <c r="I23" s="312">
         <f>'Oferta Diaria'!V34</f>
-        <v>975220.29800000007</v>
+        <v>973814.30900000001</v>
       </c>
       <c r="J23" s="161" t="s">
         <v>137</v>
@@ -45986,7 +45986,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>205472.98000000004</v>
+        <v>205455.25000000003</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O153</f>
@@ -46028,7 +46028,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>217872.44000000003</v>
+        <v>217854.71000000002</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O160</f>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>224341.94000000003</v>
+        <v>224324.21000000002</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O167</f>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>229196.63000000003</v>
+        <v>229178.90000000002</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O174</f>
@@ -46154,7 +46154,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>241495.81000000003</v>
+        <v>241478.08000000002</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O181</f>
@@ -46196,7 +46196,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>253981.53000000003</v>
+        <v>253963.80000000002</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O188</f>
@@ -46238,7 +46238,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>266366.97000000003</v>
+        <v>266349.24</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O195</f>
@@ -46280,7 +46280,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>278787.87000000005</v>
+        <v>278770.14</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O202</f>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>291208.77000000008</v>
+        <v>291191.04000000004</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O209</f>
@@ -46364,7 +46364,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>297721.40000000008</v>
+        <v>297703.67000000004</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -46408,7 +46408,7 @@
       </c>
       <c r="E34" s="12">
         <f t="shared" ref="E34" si="3">D34+E33</f>
-        <v>302638.22000000009</v>
+        <v>302620.49000000005</v>
       </c>
       <c r="F34" s="171">
         <f>'KM-Servicio'!O223</f>
@@ -46464,15 +46464,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>302638.22000000009</v>
+        <v>302620.49000000005</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4791535.7700000005</v>
+        <v>4791323.0100000007</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>96.86831379428402</v>
+        <v>96.863858080012676</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -46484,7 +46484,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>23994088.066000007</v>
+        <v>23992682.077000007</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -46516,12 +46516,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="381" t="s">
+      <c r="A3" s="382" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="382"/>
-      <c r="C3" s="382"/>
-      <c r="D3" s="383"/>
+      <c r="B3" s="383"/>
+      <c r="C3" s="383"/>
+      <c r="D3" s="384"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -46667,12 +46667,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="384" t="s">
+      <c r="A13" s="385" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="385"/>
-      <c r="C13" s="385"/>
-      <c r="D13" s="386"/>
+      <c r="B13" s="386"/>
+      <c r="C13" s="386"/>
+      <c r="D13" s="387"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -46719,8 +46719,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="390"/>
-      <c r="H16" s="390"/>
+      <c r="G16" s="381"/>
+      <c r="H16" s="381"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -46735,8 +46735,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="390"/>
-      <c r="H17" s="390"/>
+      <c r="G17" s="381"/>
+      <c r="H17" s="381"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -46751,8 +46751,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="390"/>
-      <c r="H18" s="390"/>
+      <c r="G18" s="381"/>
+      <c r="H18" s="381"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -46766,8 +46766,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="390"/>
-      <c r="H19" s="390"/>
+      <c r="G19" s="381"/>
+      <c r="H19" s="381"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -46781,8 +46781,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="390"/>
-      <c r="H20" s="390"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -46796,8 +46796,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="390"/>
-      <c r="H21" s="390"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -46822,9 +46822,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="387"/>
-      <c r="C23" s="388"/>
-      <c r="D23" s="389"/>
+      <c r="B23" s="388"/>
+      <c r="C23" s="389"/>
+      <c r="D23" s="390"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -46836,10 +46836,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="384"/>
-      <c r="B24" s="385"/>
-      <c r="C24" s="385"/>
-      <c r="D24" s="386"/>
+      <c r="A24" s="385"/>
+      <c r="B24" s="386"/>
+      <c r="C24" s="386"/>
+      <c r="D24" s="387"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -46952,9 +46952,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="387"/>
-      <c r="C34" s="388"/>
-      <c r="D34" s="389"/>
+      <c r="B34" s="388"/>
+      <c r="C34" s="389"/>
+      <c r="D34" s="390"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -47087,17 +47087,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -47105,6 +47105,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -47351,29 +47373,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F53AD24-439F-44F1-8272-A2184D6C79E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47391,25 +47412,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Mayo 2026.xlsx
+++ b/data/umr/Resumen UMR Mayo 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A85CF6-A2E7-4BA3-9E9F-107C5E49F0DE}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{A7F80FDC-1AA0-40AB-99CF-64F4E498BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{022B4984-3DD1-4702-82A6-E80C0AAB182B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -4841,48 +4841,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4896,6 +4854,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4922,6 +4883,45 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="57" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4934,9 +4934,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4964,6 +4961,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -16261,14 +16261,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="350" t="s">
+      <c r="B2" s="373" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="350"/>
-      <c r="D2" s="351" t="s">
+      <c r="C2" s="373"/>
+      <c r="D2" s="374" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="351"/>
+      <c r="E2" s="374"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -16359,59 +16359,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="350" t="s">
+      <c r="B3" s="373" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="350"/>
-      <c r="D3" s="351" t="s">
+      <c r="C3" s="373"/>
+      <c r="D3" s="374" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="351"/>
-      <c r="F3" s="357" t="s">
+      <c r="E3" s="374"/>
+      <c r="F3" s="366" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="357" t="s">
+      <c r="G3" s="366" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="357" t="s">
+      <c r="H3" s="366" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="357" t="s">
+      <c r="I3" s="366" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="357" t="s">
+      <c r="J3" s="366" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="357" t="s">
+      <c r="K3" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="357" t="s">
+      <c r="L3" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="357" t="s">
+      <c r="M3" s="366" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="361" t="s">
+      <c r="N3" s="355" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="361" t="s">
+      <c r="O3" s="355" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="368"/>
-      <c r="Q3" s="369" t="s">
+      <c r="P3" s="354"/>
+      <c r="Q3" s="356" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="370"/>
-      <c r="S3" s="371"/>
-      <c r="T3" s="372" t="s">
+      <c r="R3" s="357"/>
+      <c r="S3" s="358"/>
+      <c r="T3" s="359" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="373"/>
-      <c r="V3" s="374"/>
-      <c r="W3" s="366" t="s">
+      <c r="U3" s="360"/>
+      <c r="V3" s="361"/>
+      <c r="W3" s="352" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="366" t="s">
+      <c r="X3" s="352" t="s">
         <v>162</v>
       </c>
     </row>
@@ -16429,17 +16429,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="357"/>
-      <c r="G4" s="358"/>
-      <c r="H4" s="358"/>
-      <c r="I4" s="357"/>
-      <c r="J4" s="357"/>
-      <c r="K4" s="357"/>
-      <c r="L4" s="357"/>
-      <c r="M4" s="357"/>
-      <c r="N4" s="361"/>
-      <c r="O4" s="361"/>
-      <c r="P4" s="368"/>
+      <c r="F4" s="366"/>
+      <c r="G4" s="372"/>
+      <c r="H4" s="372"/>
+      <c r="I4" s="366"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="366"/>
+      <c r="L4" s="366"/>
+      <c r="M4" s="366"/>
+      <c r="N4" s="355"/>
+      <c r="O4" s="355"/>
+      <c r="P4" s="354"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -16458,8 +16458,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="367"/>
-      <c r="X4" s="367"/>
+      <c r="W4" s="353"/>
+      <c r="X4" s="353"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -17927,7 +17927,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="360" t="s">
+      <c r="A27" s="365" t="s">
         <v>183</v>
       </c>
       <c r="B27" s="295">
@@ -17996,7 +17996,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="360"/>
+      <c r="A28" s="365"/>
       <c r="B28" s="295">
         <v>33</v>
       </c>
@@ -18063,7 +18063,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="360"/>
+      <c r="A29" s="365"/>
       <c r="B29" s="295">
         <v>29</v>
       </c>
@@ -18128,7 +18128,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="360"/>
+      <c r="A30" s="365"/>
       <c r="B30" s="295">
         <v>0</v>
       </c>
@@ -18192,7 +18192,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="360"/>
+      <c r="A31" s="365"/>
       <c r="B31" s="295">
         <v>4</v>
       </c>
@@ -18867,7 +18867,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="359" t="s">
+      <c r="A41" s="364" t="s">
         <v>184</v>
       </c>
       <c r="B41" s="295">
@@ -18936,7 +18936,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="359"/>
+      <c r="A42" s="364"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -19010,7 +19010,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="359"/>
+      <c r="A43" s="364"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -19082,7 +19082,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="359"/>
+      <c r="A44" s="364"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -19154,7 +19154,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="359"/>
+      <c r="A45" s="364"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -19379,7 +19379,7 @@
       <c r="AF47" s="255"/>
     </row>
     <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="360" t="s">
+      <c r="A48" s="365" t="s">
         <v>185</v>
       </c>
       <c r="B48" s="295">
@@ -19448,7 +19448,7 @@
       </c>
     </row>
     <row r="49" spans="1:65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="360"/>
+      <c r="A49" s="365"/>
       <c r="B49" s="295">
         <v>33</v>
       </c>
@@ -19513,7 +19513,7 @@
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A50" s="360"/>
+      <c r="A50" s="365"/>
       <c r="B50" s="295">
         <v>29</v>
       </c>
@@ -19576,7 +19576,7 @@
       </c>
     </row>
     <row r="51" spans="1:65" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="360"/>
+      <c r="A51" s="365"/>
       <c r="B51" s="295">
         <v>0</v>
       </c>
@@ -19640,7 +19640,7 @@
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A52" s="360"/>
+      <c r="A52" s="365"/>
       <c r="B52" s="295">
         <v>4</v>
       </c>
@@ -26100,7 +26100,7 @@
       </c>
     </row>
     <row r="148" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="363" t="s">
+      <c r="A148" s="371" t="s">
         <v>189</v>
       </c>
       <c r="B148" s="218">
@@ -26169,7 +26169,7 @@
       </c>
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A149" s="363"/>
+      <c r="A149" s="371"/>
       <c r="B149" s="218">
         <v>0</v>
       </c>
@@ -26234,7 +26234,7 @@
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A150" s="363"/>
+      <c r="A150" s="371"/>
       <c r="B150" s="218">
         <v>0</v>
       </c>
@@ -26299,7 +26299,7 @@
       </c>
     </row>
     <row r="151" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="363"/>
+      <c r="A151" s="371"/>
       <c r="B151" s="218">
         <v>0</v>
       </c>
@@ -26364,7 +26364,7 @@
       </c>
     </row>
     <row r="152" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="363"/>
+      <c r="A152" s="371"/>
       <c r="B152" s="218">
         <v>0</v>
       </c>
@@ -26578,8 +26578,7 @@
         <v>42</v>
       </c>
       <c r="D155" s="126">
-        <f>'Data Ocupacion'!AT32</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E155" s="126">
         <f>'Data Ocupacion'!AU32</f>
@@ -26590,7 +26589,7 @@
       </c>
       <c r="G155" s="125">
         <f t="shared" si="132"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H155" s="125">
         <f t="shared" ref="H155:H159" si="136">B155+C155*2</f>
@@ -26598,23 +26597,23 @@
       </c>
       <c r="I155" s="125">
         <f t="shared" si="133"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J155" s="125">
         <f>G155*M$2</f>
-        <v>5175.6000000000004</v>
+        <v>5218.7300000000005</v>
       </c>
       <c r="K155" s="153">
         <f>I155*M$2</f>
-        <v>3364.1400000000003</v>
+        <v>3407.27</v>
       </c>
       <c r="L155" s="125">
         <f t="shared" si="134"/>
-        <v>538262.4</v>
+        <v>542747.92000000004</v>
       </c>
       <c r="M155" s="125">
         <f t="shared" si="135"/>
-        <v>8112</v>
+        <v>8216</v>
       </c>
       <c r="N155" s="19"/>
       <c r="O155" s="19"/>
@@ -26629,7 +26628,7 @@
       <c r="V155" s="229"/>
       <c r="W155" s="185">
         <f>J155-(T155*($M$2-$K$1)+(U155*($M$2-$M$1)))</f>
-        <v>5086.9500000000007</v>
+        <v>5130.0800000000008</v>
       </c>
       <c r="X155" s="182">
         <f>H155*$M$2</f>
@@ -26716,8 +26715,7 @@
         <v>3</v>
       </c>
       <c r="D157" s="126">
-        <f>'Data Ocupacion'!AT34</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E157" s="126">
         <f>'Data Ocupacion'!AU34</f>
@@ -26728,7 +26726,7 @@
       </c>
       <c r="G157" s="125">
         <f t="shared" si="132"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H157" s="125">
         <f t="shared" si="136"/>
@@ -26736,23 +26734,23 @@
       </c>
       <c r="I157" s="125">
         <f t="shared" si="133"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J157" s="125">
         <f>G157*M$1</f>
-        <v>989.74</v>
+        <v>960.63</v>
       </c>
       <c r="K157" s="153">
         <f>I157*M$1</f>
-        <v>931.52</v>
+        <v>902.41</v>
       </c>
       <c r="L157" s="125">
         <f t="shared" si="134"/>
-        <v>102932.96</v>
+        <v>99905.52</v>
       </c>
       <c r="M157" s="125">
         <f t="shared" si="135"/>
-        <v>3328</v>
+        <v>3224</v>
       </c>
       <c r="N157" s="19"/>
       <c r="O157" s="19"/>
@@ -26765,7 +26763,7 @@
       <c r="V157" s="189"/>
       <c r="W157" s="182">
         <f>J157</f>
-        <v>989.74</v>
+        <v>960.63</v>
       </c>
       <c r="X157" s="182">
         <f>H157*$M$1</f>
@@ -26939,15 +26937,15 @@
       </c>
       <c r="J160" s="120">
         <f t="shared" si="137"/>
-        <v>12548.720000000001</v>
+        <v>12562.740000000002</v>
       </c>
       <c r="K160" s="119">
         <f t="shared" si="137"/>
-        <v>8852.49</v>
+        <v>8866.51</v>
       </c>
       <c r="L160" s="118">
         <f t="shared" si="137"/>
-        <v>1305066.8799999999</v>
+        <v>1306524.96</v>
       </c>
       <c r="M160" s="151">
         <f t="shared" si="137"/>
@@ -26959,7 +26957,7 @@
       </c>
       <c r="O160" s="21">
         <f>(W160/N160)*100</f>
-        <v>95.56423892100193</v>
+        <v>95.672292870905594</v>
       </c>
       <c r="P160" s="192"/>
       <c r="Q160" s="181"/>
@@ -26970,7 +26968,7 @@
       <c r="V160" s="181"/>
       <c r="W160" s="193">
         <f>SUM(W154:W159)</f>
-        <v>12399.460000000001</v>
+        <v>12413.480000000001</v>
       </c>
       <c r="X160" s="193">
         <f>SUM(X154:X159)</f>
@@ -27978,7 +27976,7 @@
       </c>
     </row>
     <row r="176" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="362" t="s">
+      <c r="A176" s="370" t="s">
         <v>188</v>
       </c>
       <c r="B176" s="295">
@@ -28048,7 +28046,7 @@
       <c r="Y176" s="172"/>
     </row>
     <row r="177" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A177" s="362"/>
+      <c r="A177" s="370"/>
       <c r="B177" s="295">
         <v>33</v>
       </c>
@@ -28115,7 +28113,7 @@
       </c>
     </row>
     <row r="178" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="362"/>
+      <c r="A178" s="370"/>
       <c r="B178" s="295">
         <v>29</v>
       </c>
@@ -28180,7 +28178,7 @@
       </c>
     </row>
     <row r="179" spans="1:30" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="362"/>
+      <c r="A179" s="370"/>
       <c r="B179" s="295">
         <v>0</v>
       </c>
@@ -28245,7 +28243,7 @@
       </c>
     </row>
     <row r="180" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="362"/>
+      <c r="A180" s="370"/>
       <c r="B180" s="295">
         <v>4</v>
       </c>
@@ -31218,38 +31216,38 @@
     <row r="224" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="225" spans="1:29" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225"/>
-      <c r="B225" s="354" t="s">
+      <c r="B225" s="367" t="s">
         <v>56</v>
       </c>
-      <c r="C225" s="355"/>
-      <c r="D225" s="355"/>
-      <c r="E225" s="355"/>
-      <c r="F225" s="355"/>
-      <c r="G225" s="356"/>
+      <c r="C225" s="368"/>
+      <c r="D225" s="368"/>
+      <c r="E225" s="368"/>
+      <c r="F225" s="368"/>
+      <c r="G225" s="369"/>
       <c r="H225" s="290"/>
-      <c r="I225" s="354" t="s">
+      <c r="I225" s="367" t="s">
         <v>57</v>
       </c>
-      <c r="J225" s="355"/>
-      <c r="K225" s="355"/>
-      <c r="L225" s="355"/>
-      <c r="M225" s="355"/>
-      <c r="N225" s="356"/>
-      <c r="P225" s="375" t="s">
+      <c r="J225" s="368"/>
+      <c r="K225" s="368"/>
+      <c r="L225" s="368"/>
+      <c r="M225" s="368"/>
+      <c r="N225" s="369"/>
+      <c r="P225" s="362" t="s">
         <v>139</v>
       </c>
-      <c r="Q225" s="375"/>
-      <c r="R225" s="375"/>
-      <c r="S225" s="376"/>
-      <c r="T225" s="372" t="s">
+      <c r="Q225" s="362"/>
+      <c r="R225" s="362"/>
+      <c r="S225" s="363"/>
+      <c r="T225" s="359" t="s">
         <v>142</v>
       </c>
-      <c r="U225" s="373"/>
-      <c r="V225" s="374"/>
-      <c r="W225" s="364" t="s">
+      <c r="U225" s="360"/>
+      <c r="V225" s="361"/>
+      <c r="W225" s="350" t="s">
         <v>143</v>
       </c>
-      <c r="X225" s="364" t="s">
+      <c r="X225" s="350" t="s">
         <v>162</v>
       </c>
     </row>
@@ -31315,8 +31313,8 @@
       <c r="V226" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W226" s="365"/>
-      <c r="X226" s="365"/>
+      <c r="W226" s="351"/>
+      <c r="X226" s="351"/>
     </row>
     <row r="227" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="23" t="s">
@@ -31402,7 +31400,7 @@
       </c>
       <c r="W227" s="231">
         <f>W11+W18+W25+W32+W39+W46+W55+W62+W69+W76+W83+W90+W97+W104+W111+W118+W125+W132+W139+W146+W153+W160+W167+W174+W181+W188+W195+W202+W209+W216+W223</f>
-        <v>302620.49000000005</v>
+        <v>302634.51000000007</v>
       </c>
       <c r="X227" s="231">
         <f>X11+X18+X25+X32+X39+X46+X55+X62+X69+X76+X83+X90+X97+X104+X111+X118+X125+X132+X139+X146+X153+X160+X167+X174+X181+X188+X195+X202+X209+X216+X223</f>
@@ -31440,7 +31438,7 @@
       <c r="H228" s="139"/>
       <c r="I228" s="114">
         <f t="shared" si="195"/>
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="J228" s="114">
         <f t="shared" si="195"/>
@@ -31448,19 +31446,19 @@
       </c>
       <c r="K228" s="114">
         <f t="shared" si="196"/>
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="L228" s="139">
         <f t="shared" ref="L228" si="198">K228*43.13</f>
-        <v>96913.11</v>
+        <v>96956.24</v>
       </c>
       <c r="M228" s="139">
         <f>I228*43.13+J228*86.26</f>
-        <v>131848.41</v>
+        <v>131891.54</v>
       </c>
       <c r="N228" s="139">
         <f t="shared" si="197"/>
-        <v>13712234.640000001</v>
+        <v>13716720.16</v>
       </c>
       <c r="O228" s="124"/>
       <c r="W228" s="124"/>
@@ -31553,7 +31551,7 @@
       <c r="H230" s="139"/>
       <c r="I230" s="114">
         <f t="shared" si="195"/>
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J230" s="114">
         <f t="shared" si="195"/>
@@ -31561,19 +31559,19 @@
       </c>
       <c r="K230" s="114">
         <f t="shared" si="196"/>
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="L230" s="139">
         <f>K230*29.11</f>
-        <v>17407.78</v>
+        <v>17378.669999999998</v>
       </c>
       <c r="M230" s="139">
         <f>I230*29.11+J230*58.22</f>
-        <v>18688.62</v>
+        <v>18659.509999999998</v>
       </c>
       <c r="N230" s="139">
         <f t="shared" si="197"/>
-        <v>1943616.48</v>
+        <v>1940589.0399999998</v>
       </c>
       <c r="O230" s="124"/>
       <c r="W230" s="124"/>
@@ -31765,15 +31763,15 @@
       </c>
       <c r="L234" s="284">
         <f>SUM(L227:L233)</f>
-        <v>232003.42</v>
+        <v>232017.44</v>
       </c>
       <c r="M234" s="284">
         <f>SUM(M227:M233)</f>
-        <v>304953.26000000007</v>
+        <v>304967.28000000009</v>
       </c>
       <c r="N234" s="284">
         <f>SUM(N227:N233)</f>
-        <v>31715139.040000007</v>
+        <v>31716597.120000005</v>
       </c>
       <c r="P234"/>
       <c r="Q234"/>
@@ -31826,10 +31824,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="352" t="s">
+      <c r="B237" s="375" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="353"/>
+      <c r="C237" s="376"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -32012,16 +32010,14 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="X225:X226"/>
-    <mergeCell ref="W225:W226"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="T225:V225"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="P225:S225"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B225:G225"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="M3:M4"/>
@@ -32035,14 +32031,16 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B225:G225"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="X225:X226"/>
+    <mergeCell ref="W225:W226"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="T225:V225"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="P225:S225"/>
   </mergeCells>
   <conditionalFormatting sqref="D26:D31 D47:D54">
     <cfRule type="expression" dxfId="32" priority="28">
@@ -41245,6 +41243,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BL1:BM1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
@@ -41261,22 +41275,6 @@
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -46024,15 +46022,15 @@
       </c>
       <c r="D25" s="12">
         <f>'KM-Servicio'!$W$160</f>
-        <v>12399.460000000001</v>
+        <v>12413.480000000001</v>
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>217854.71000000002</v>
+        <v>217868.73000000004</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O160</f>
-        <v>95.56423892100193</v>
+        <v>95.672292870905594</v>
       </c>
       <c r="G25" s="167">
         <f>SUM('KM-Servicio'!B160:C160)</f>
@@ -46070,7 +46068,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>224324.21000000002</v>
+        <v>224338.23000000004</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O167</f>
@@ -46112,7 +46110,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>229178.90000000002</v>
+        <v>229192.92000000004</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O174</f>
@@ -46154,7 +46152,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>241478.08000000002</v>
+        <v>241492.10000000003</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O181</f>
@@ -46196,7 +46194,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>253963.80000000002</v>
+        <v>253977.82000000004</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O188</f>
@@ -46238,7 +46236,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>266349.24</v>
+        <v>266363.26</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O195</f>
@@ -46280,7 +46278,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>278770.14</v>
+        <v>278784.16000000003</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O202</f>
@@ -46322,7 +46320,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>291191.04000000004</v>
+        <v>291205.06000000006</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O209</f>
@@ -46364,7 +46362,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>297703.67000000004</v>
+        <v>297717.69000000006</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -46408,7 +46406,7 @@
       </c>
       <c r="E34" s="12">
         <f t="shared" ref="E34" si="3">D34+E33</f>
-        <v>302620.49000000005</v>
+        <v>302634.51000000007</v>
       </c>
       <c r="F34" s="171">
         <f>'KM-Servicio'!O223</f>
@@ -46464,15 +46462,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>302620.49000000005</v>
+        <v>302634.51000000007</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4791323.0100000007</v>
+        <v>4791463.21</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>96.863858080012676</v>
+        <v>96.867343691299894</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -46516,12 +46514,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="382" t="s">
+      <c r="A3" s="381" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="383"/>
-      <c r="C3" s="383"/>
-      <c r="D3" s="384"/>
+      <c r="B3" s="382"/>
+      <c r="C3" s="382"/>
+      <c r="D3" s="383"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -46577,11 +46575,11 @@
       </c>
       <c r="B7" s="129">
         <f>C7/30</f>
-        <v>10165.108666666669</v>
+        <v>10165.576000000003</v>
       </c>
       <c r="C7" s="130">
         <f>'KM-Servicio'!M234</f>
-        <v>304953.26000000007</v>
+        <v>304967.28000000009</v>
       </c>
       <c r="D7" s="130">
         <f>'KM-Servicio'!F234</f>
@@ -46594,11 +46592,11 @@
       </c>
       <c r="B8" s="129">
         <f>C8/30</f>
-        <v>7733.4473333333335</v>
+        <v>7733.9146666666666</v>
       </c>
       <c r="C8" s="130">
         <f>'KM-Servicio'!L234</f>
-        <v>232003.42</v>
+        <v>232017.44</v>
       </c>
       <c r="D8" s="130">
         <f>'KM-Servicio'!E234</f>
@@ -46611,11 +46609,11 @@
       </c>
       <c r="B9" s="129">
         <f>C9/30</f>
-        <v>1057171.3013333336</v>
+        <v>1057219.9040000001</v>
       </c>
       <c r="C9" s="130">
         <f>'KM-Servicio'!N234</f>
-        <v>31715139.040000007</v>
+        <v>31716597.120000005</v>
       </c>
       <c r="D9" s="130">
         <f>'KM-Servicio'!G234</f>
@@ -46667,12 +46665,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="385" t="s">
+      <c r="A13" s="384" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="386"/>
-      <c r="C13" s="386"/>
-      <c r="D13" s="387"/>
+      <c r="B13" s="385"/>
+      <c r="C13" s="385"/>
+      <c r="D13" s="386"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -46719,8 +46717,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="381"/>
-      <c r="H16" s="381"/>
+      <c r="G16" s="390"/>
+      <c r="H16" s="390"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -46735,8 +46733,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="381"/>
-      <c r="H17" s="381"/>
+      <c r="G17" s="390"/>
+      <c r="H17" s="390"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -46751,8 +46749,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="381"/>
-      <c r="H18" s="381"/>
+      <c r="G18" s="390"/>
+      <c r="H18" s="390"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -46766,8 +46764,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="381"/>
-      <c r="H19" s="381"/>
+      <c r="G19" s="390"/>
+      <c r="H19" s="390"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -46781,8 +46779,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="381"/>
-      <c r="H20" s="381"/>
+      <c r="G20" s="390"/>
+      <c r="H20" s="390"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -46796,8 +46794,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="381"/>
-      <c r="H21" s="381"/>
+      <c r="G21" s="390"/>
+      <c r="H21" s="390"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -46822,9 +46820,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="388"/>
-      <c r="C23" s="389"/>
-      <c r="D23" s="390"/>
+      <c r="B23" s="387"/>
+      <c r="C23" s="388"/>
+      <c r="D23" s="389"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -46836,10 +46834,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="385"/>
-      <c r="B24" s="386"/>
-      <c r="C24" s="386"/>
-      <c r="D24" s="387"/>
+      <c r="A24" s="384"/>
+      <c r="B24" s="385"/>
+      <c r="C24" s="385"/>
+      <c r="D24" s="386"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -46952,9 +46950,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="388"/>
-      <c r="C34" s="389"/>
-      <c r="D34" s="390"/>
+      <c r="B34" s="387"/>
+      <c r="C34" s="388"/>
+      <c r="D34" s="389"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -47087,17 +47085,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -47118,15 +47116,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -47373,6 +47362,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB550D0-58EE-498C-B38E-9B72F9C57DDA}">
   <ds:schemaRefs>
@@ -47387,14 +47385,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F53AD24-439F-44F1-8272-A2184D6C79E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -47412,4 +47402,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5E3D1A5-9383-405D-B1EF-97C8A11D2625}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>